--- a/Result/checksun_type/玻璃.xlsx
+++ b/Result/checksun_type/玻璃.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,37 +1668,37 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>58.8</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>58.83</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>56.49</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>58.83</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>56.49</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2650,37 +2654,37 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>58.7</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>56.41</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>56.41</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3632,37 +3640,37 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>59.02</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>56.32</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>59.02</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>56.32</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4614,37 +4626,37 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>58.21</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>59.06</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>56.19</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>59.06</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>56.19</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5596,37 +5612,37 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>58.27</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>59.22</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>56.17</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>59.22</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>56.17</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6578,37 +6598,37 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>58.39</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>59.26</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>56.23</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>59.26</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>56.23</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7560,37 +7584,37 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>58.65</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>56.34</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>59.37</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>56.34</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8542,37 +8570,37 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>58.76000000000001</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>59.33</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>56.42</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>59.33</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>56.42</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9524,37 +9556,37 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>58.82000000000001</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>59.17</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>56.5</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>59.17</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>

--- a/Result/checksun_type/玻璃.xlsx
+++ b/Result/checksun_type/玻璃.xlsx
@@ -1433,7 +1433,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12062.573</t>
+          <t>23093.784</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.28003130372797114</t>
+          <t>-0.11135316584249741</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -1523,62 +1523,62 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>空頭</t>
+          <t>弱勢整理</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 20&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.86500000000001</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>61.04677812673398</t>
+          <t>61.08858174787246</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>56.61322187326602</t>
+          <t>56.64141825212756</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.07536216647064348</t>
+          <t>0.07554851772266885</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.001103659054249029</t>
+          <t>0.0005949345571989451</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.003568597122044825</t>
+          <t>0.0006847801378488949</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.06377897240356267</t>
+          <t>0.002472742767799962</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.3194321177608941</t>
+          <t>0.3185244881259408</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.7611408795638696</t>
+          <t>0.7911038446557226</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1623,24 +1623,24 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AQ2" t="inlineStr">
         <is>
           <t>False</t>
@@ -1673,22 +1673,22 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4040506.0</t>
+          <t>6786190.0</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>723111.0</t>
+          <t>987073.0</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>4657617.0</t>
+          <t>7667263.0</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1849,320 +1849,320 @@
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>226</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>1.12</v>
+        <v>0.47</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>58.88000000000001</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.87</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.59</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.78</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
+          <t>52.50166666666667</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>0.003059143439837042</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>0.001360544217687387</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>0.0005949345571989451</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>0.001770193482147464</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>-0.0007730477931574553</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>0.002286891537705671</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>-95.18</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>5648900594.207143</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>1391651459.0</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>978592810.6</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>1101216786.0</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>1410351796.1</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>1501930217.1</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>2534452706.925</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>-106948730.6812849</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>-60231869.45079255</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>1391651459.0</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>0.006500171057133075</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>0.001703577512776722</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>-0.001103659054249029</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>0.001382660025171623</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>-0.0005220569042025947</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>-2.31</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>-95.21</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>7427894012.401478</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>716628303.0</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>793132356.6</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>1101620613.1</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>1512236185.5</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>1491436510.72</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>2550447434.6375</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>-115442705.4717676</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>-106289824.1743681</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>716628303.0</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>68.95</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>23.33%</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>12.64%</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>73.12</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>172448</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>台玻-玻璃陶瓷-上市</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷右上上市</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
         <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>-1.98</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>69.19</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>23.33%</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>12.64%</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>74.17</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>173030</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>台玻-玻璃陶瓷-上市</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>58.8</t>
-        </is>
-      </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
@@ -2182,42 +2182,42 @@
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
@@ -2227,22 +2227,22 @@
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15496.264</t>
+          <t>12062.573</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2454,17 +2454,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.23927286091689726</t>
+          <t>-0.28003130372797114</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2524,47 +2524,47 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>58.895</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>61.26540969143974</t>
+          <t>61.04677812673161</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>56.52459030856025</t>
+          <t>56.61322187326839</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.08049612671499268</t>
+          <t>0.07536216647056303</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-0.00211792612673678</t>
+          <t>-0.001103659054249029</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.005781894342764105</t>
+          <t>-0.00356859712204749</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.08696589266449983</t>
+          <t>-0.06377897240368935</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.3194321177608941</t>
+          <t>0.3185244881259408</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.7815573182265803</t>
+          <t>0.7611408795635349</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -2609,142 +2609,142 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AP3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>6786190.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>17000.0</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>123000.0</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>-106000.0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>987073.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>7667263.0</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>4040506.0</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>17000.0</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>123000.0</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>-106000.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>723111.0</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>4657617.0</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -2814,191 +2814,191 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>226</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CK3" t="n">
-        <v>0.58</v>
+        <v>1.12</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.74</v>
+        <v>0.02</v>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>56.41</t>
+          <t>56.49</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>59.86</t>
+          <t>59.83</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52.38187500000001</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>2.220446049250313e-16</t>
+          <t>0.006500171057133075</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>0.004792879150975704</t>
+          <t>0.001703577512776722</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>-0.00211792612673678</t>
+          <t>-0.001103659054249029</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>0.001669063726273734</t>
+          <t>0.001382660025171623</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>-0.001834269575095582</t>
+          <t>-0.0005220569042025947</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.002527920765234448</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>-29.02</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="DB3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="DC3" t="n">
         <v>0.2</v>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>-95.18</t>
+          <t>-95.26</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/10/05</t>
         </is>
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>7427894012.401478</t>
+          <t>5648900594.207143</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>913096038.0</t>
+          <t>716628303.0</t>
         </is>
       </c>
       <c r="DI3" t="n">
-        <v>836051353.4</v>
+        <v>793132356.6</v>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>1099016073.5</t>
+          <t>1101620613.1</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>1537638652.2</t>
+          <t>1512236185.5</t>
         </is>
       </c>
       <c r="DL3" t="n">
-        <v>1496862031.52</v>
+        <v>1491436510.72</v>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>2578499982.6</t>
+          <t>2550447434.6375</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>-117106865.7076584</t>
+          <t>-115442705.4504653</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>-95966927.62467611</t>
+          <t>-106289824.1697955</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>913096038.0</t>
+          <t>716628303.0</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>68.95</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>73.12</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>173030</t>
+          <t>172448</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
@@ -3123,32 +3123,32 @@
       </c>
       <c r="EO3" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
@@ -3168,42 +3168,42 @@
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF3" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23784.387</t>
+          <t>15496.264</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.08663988999632684</t>
+          <t>-0.23927286091689726</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -3510,47 +3510,47 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>58.895</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>61.62169984918928</t>
+          <t>61.26540969143753</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>56.41830015081073</t>
+          <t>56.52459030856246</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.08816332935239829</t>
+          <t>0.08049612671491764</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.0007618725133327064</t>
+          <t>-0.002117926126736669</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.002243184610895566</t>
+          <t>-0.005781894342767324</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.03396950249456443</t>
+          <t>-0.08696589266464283</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.3194321177608941</t>
+          <t>0.3185244881259408</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.8245796448191481</t>
+          <t>0.7815573182263081</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -3595,77 +3595,77 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4040506.0</t>
+          <t>6786190.0</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>723111.0</t>
+          <t>987073.0</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>4657617.0</t>
+          <t>7667263.0</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -3800,17 +3800,17 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -3821,170 +3821,170 @@
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>226</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="CK4" t="n">
-        <v>2.46</v>
+        <v>0.58</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0.95</v>
+        <v>-0.74</v>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>58.45999999999999</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>56.32</t>
+          <t>56.41</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>59.97</t>
+          <t>59.86</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52.24979166666667</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>-0.0006837606837607479</t>
+          <t>2.220446049250313e-16</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>0.003607627555402892</t>
+          <t>0.004792879150975704</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>-0.0007618725133327064</t>
+          <t>-0.002117926126736669</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>0.002349297880292589</t>
+          <t>0.001669063726273734</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>-0.001872444892906611</t>
+          <t>-0.001834269575095582</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.002534327343953091</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>-33.32</t>
+          <t>-29.02</t>
         </is>
       </c>
       <c r="DB4" t="n">
         <v>0.15</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
         <is>
-          <t>-94.83</t>
+          <t>-95.24</t>
         </is>
       </c>
       <c r="DF4" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/10/05</t>
         </is>
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>7427894012.401478</t>
+          <t>5648900594.207143</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>1411506215.0</t>
+          <t>913096038.0</t>
         </is>
       </c>
       <c r="DI4" t="n">
-        <v>972212204</v>
+        <v>836051353.4</v>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>1064434710.2</t>
+          <t>1099016073.5</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>1565951673.033333</t>
+          <t>1537638652.2</t>
         </is>
       </c>
       <c r="DL4" t="n">
-        <v>1495033587.44</v>
+        <v>1496862031.52</v>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>2612782440.9375</t>
+          <t>2578499982.6</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>-120950490.8136552</t>
+          <t>-117106865.6833144</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>-98842656.74566317</t>
+          <t>-95966927.61945021</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
         <is>
-          <t>1411506215.0</t>
+          <t>913096038.0</t>
         </is>
       </c>
       <c r="DQ4" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="DZ4" t="inlineStr">
@@ -4049,17 +4049,17 @@
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>68.95</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>73.12</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
-          <t>173030</t>
+          <t>172448</t>
         </is>
       </c>
       <c r="EM4" t="inlineStr">
@@ -4109,32 +4109,32 @@
       </c>
       <c r="EO4" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP4" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="EQ4" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="ER4" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="ES4" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="ET4" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU4" t="inlineStr">
@@ -4154,42 +4154,42 @@
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FA4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF4" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7975.945</t>
+          <t>23784.387</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>59.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4426,17 +4426,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.06753878030510366</t>
+          <t>-0.08663988999632684</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4446,277 +4446,277 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>59.02</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>61.62169984918725</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>56.41830015081274</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.08816332935232991</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>-0.0007618725133330395</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-0.00224318461089712</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.03396950249461561</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.3185244881259408</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.8245796448189587</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>2026-04-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>59.065</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>61.76023946792896</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>56.36976053207103</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.09126350522065399</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>-0.002701561840439015</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-0.002804803302640768</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.00236677235579652</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.3194321177608941</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>0.8234794118947475</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>2026-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>6786190.0</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>17000.0</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>123000.0</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>-106000.0</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>987073.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>7667263.0</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>4040506.0</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>17000.0</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>123000.0</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>-106000.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>723111.0</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>4657617.0</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -4786,17 +4786,17 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -4807,252 +4807,252 @@
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>226</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="CK5" t="n">
-        <v>-1.54</v>
+        <v>2.46</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.96</v>
+        <v>-0.95</v>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.45999999999999</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>58.21</t>
+          <t>58.42</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.32</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>59.97</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
+          <t>52.11770833333333</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>-0.0006837606837607479</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>0.003607627555402892</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>-0.0007618725133330395</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>0.002349297880292589</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>-0.001872444892906611</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>0.00256085538180395</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>-33.32</t>
+        </is>
+      </c>
+      <c r="DB5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>-94.89</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>5648900594.207143</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>1411506215.0</t>
+        </is>
+      </c>
+      <c r="DI5" t="n">
+        <v>972212204</v>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>1064434710.2</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>1565951673.033333</t>
+        </is>
+      </c>
+      <c r="DL5" t="n">
+        <v>1495033587.44</v>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>2612782440.9375</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>-120950490.7858351</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>-98842656.73969078</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>1411506215.0</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU5" t="inlineStr">
-        <is>
-          <t>-0.004085801838610736</t>
-        </is>
-      </c>
-      <c r="CV5" t="inlineStr">
-        <is>
-          <t>-0.001029689377037957</t>
-        </is>
-      </c>
-      <c r="CW5" t="inlineStr">
-        <is>
-          <t>-0.002701561840439015</t>
-        </is>
-      </c>
-      <c r="CX5" t="inlineStr">
-        <is>
-          <t>0.0003560809728131442</t>
-        </is>
-      </c>
-      <c r="CY5" t="inlineStr">
-        <is>
-          <t>-0.002945599751076</t>
-        </is>
-      </c>
-      <c r="CZ5" t="inlineStr">
+      <c r="DR5" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>-1.32</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="DA5" t="inlineStr">
-        <is>
-          <t>-85.80</t>
-        </is>
-      </c>
-      <c r="DB5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="DD5" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE5" t="inlineStr">
-        <is>
-          <t>-94.40</t>
-        </is>
-      </c>
-      <c r="DF5" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="DG5" t="inlineStr">
-        <is>
-          <t>7427894012.401478</t>
-        </is>
-      </c>
-      <c r="DH5" t="inlineStr">
-        <is>
-          <t>460082038.0</t>
-        </is>
-      </c>
-      <c r="DI5" t="n">
-        <v>923803762.8</v>
-      </c>
-      <c r="DJ5" t="inlineStr">
-        <is>
-          <t>990715477.8</t>
-        </is>
-      </c>
-      <c r="DK5" t="inlineStr">
-        <is>
-          <t>1577592671.866667</t>
-        </is>
-      </c>
-      <c r="DL5" t="n">
-        <v>1503106536.6</v>
-      </c>
-      <c r="DM5" t="inlineStr">
-        <is>
-          <t>2650980248.8625</t>
-        </is>
-      </c>
-      <c r="DN5" t="inlineStr">
-        <is>
-          <t>-124970097.0078356</t>
-        </is>
-      </c>
-      <c r="DO5" t="inlineStr">
-        <is>
-          <t>-152821836.7132996</t>
-        </is>
-      </c>
-      <c r="DP5" t="inlineStr">
-        <is>
-          <t>460082038.0</t>
-        </is>
-      </c>
-      <c r="DQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR5" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="DS5" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT5" t="inlineStr">
-        <is>
-          <t>-5.11</t>
-        </is>
-      </c>
-      <c r="DU5" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV5" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW5" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY5" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="DZ5" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA5" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB5" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE5" t="inlineStr">
-        <is>
-          <t>3.24</t>
-        </is>
-      </c>
-      <c r="EF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG5" t="inlineStr">
         <is>
           <t>4.15</t>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>68.95</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>73.12</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>173030</t>
+          <t>172448</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
@@ -5095,32 +5095,32 @@
       </c>
       <c r="EO5" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>59.9</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
@@ -5140,42 +5140,42 @@
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FA5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF5" t="inlineStr">
@@ -5185,22 +5185,22 @@
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK5" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8054.096</t>
+          <t>7975.945</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5412,17 +5412,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.20773173479608792</t>
+          <t>-0.06753878030510366</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -5482,47 +5482,47 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.225</t>
+          <t>59.06500000000001</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>61.93395202110334</t>
+          <t>61.76023946792703</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>56.51604797889666</t>
+          <t>56.36976053207299</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.09148001759741133</t>
+          <t>0.09126350522058804</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.0006749346157091107</t>
+          <t>-0.002701561840438793</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.0001967952176192833</t>
+          <t>-0.002804803302640657</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0110545758825138</t>
+          <t>-0.002366772355803071</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.3194321177608941</t>
+          <t>0.3185244881259408</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.7820832597155659</t>
+          <t>0.8234794118945751</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -5567,142 +5567,142 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>6786190.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>17000.0</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>123000.0</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-106000.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>987073.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>7667263.0</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>4040506.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>17000.0</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>123000.0</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>-106000.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>723111.0</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>4657617.0</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -5772,17 +5772,17 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -5793,252 +5793,252 @@
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>226</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>55.28</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="CK6" t="n">
-        <v>-0.58</v>
+        <v>-1.54</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.82</v>
+        <v>-0.96</v>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>58.73999999999999</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>58.27</t>
+          <t>58.21</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.07</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>56.17</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
+          <t>51.98458333333333</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>-0.004085801838610736</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>-0.001029689377037957</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>-0.002701561840438793</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>0.0003560809728131442</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>-0.002945599751076</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>0.002426462908059479</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>-85.80</t>
+        </is>
+      </c>
+      <c r="DB6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>-94.46</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>5648900594.207143</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>460082038.0</t>
+        </is>
+      </c>
+      <c r="DI6" t="n">
+        <v>923803762.8</v>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>990715477.8</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>1577592671.866667</t>
+        </is>
+      </c>
+      <c r="DL6" t="n">
+        <v>1503106536.6</v>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>2650980248.8625</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>-124970096.9760432</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>-152821836.7064742</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>460082038.0</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU6" t="inlineStr">
-        <is>
-          <t>-0.0003403675970049536</t>
-        </is>
-      </c>
-      <c r="CV6" t="inlineStr">
-        <is>
-          <t>-0.00205514642918303</t>
-        </is>
-      </c>
-      <c r="CW6" t="inlineStr">
-        <is>
-          <t>-0.0006749346157091107</t>
-        </is>
-      </c>
-      <c r="CX6" t="inlineStr">
-        <is>
-          <t>-0.001173688047943156</t>
-        </is>
-      </c>
-      <c r="CY6" t="inlineStr">
-        <is>
-          <t>-0.00260688756245675</t>
-        </is>
-      </c>
-      <c r="CZ6" t="inlineStr">
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>-5.11</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="DA6" t="inlineStr">
-        <is>
-          <t>-57.25</t>
-        </is>
-      </c>
-      <c r="DB6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="DD6" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE6" t="inlineStr">
-        <is>
-          <t>-93.19</t>
-        </is>
-      </c>
-      <c r="DF6" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="DG6" t="inlineStr">
-        <is>
-          <t>7427894012.401478</t>
-        </is>
-      </c>
-      <c r="DH6" t="inlineStr">
-        <is>
-          <t>464349189.0</t>
-        </is>
-      </c>
-      <c r="DI6" t="n">
-        <v>1223840761.4</v>
-      </c>
-      <c r="DJ6" t="inlineStr">
-        <is>
-          <t>1013338249.0</t>
-        </is>
-      </c>
-      <c r="DK6" t="inlineStr">
-        <is>
-          <t>1611987982.833333</t>
-        </is>
-      </c>
-      <c r="DL6" t="n">
-        <v>1533541700.16</v>
-      </c>
-      <c r="DM6" t="inlineStr">
-        <is>
-          <t>2698659312.1</t>
-        </is>
-      </c>
-      <c r="DN6" t="inlineStr">
-        <is>
-          <t>-119906144.3341149</t>
-        </is>
-      </c>
-      <c r="DO6" t="inlineStr">
-        <is>
-          <t>-122538723.5344481</t>
-        </is>
-      </c>
-      <c r="DP6" t="inlineStr">
-        <is>
-          <t>464349189.0</t>
-        </is>
-      </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR6" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="DS6" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT6" t="inlineStr">
-        <is>
-          <t>-3.79</t>
-        </is>
-      </c>
-      <c r="DU6" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV6" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW6" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY6" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="DZ6" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA6" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB6" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE6" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
-      <c r="EF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG6" t="inlineStr">
         <is>
           <t>4.15</t>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>68.95</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>73.12</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>173030</t>
+          <t>172448</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
@@ -6081,12 +6081,12 @@
       </c>
       <c r="EO6" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
@@ -6096,17 +6096,17 @@
       </c>
       <c r="ER6" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="ES6" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU6" t="inlineStr">
@@ -6126,42 +6126,42 @@
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FA6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF6" t="inlineStr">
@@ -6171,22 +6171,22 @@
       </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK6" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16045.294</t>
+          <t>8054.096</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6398,17 +6398,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.37788535417800007</t>
+          <t>0.20773173479608792</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -6468,47 +6468,47 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>59.265</t>
+          <t>59.225</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>61.94614272574173</t>
+          <t>61.9339520211014</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>56.58385727425827</t>
+          <t>56.5160479788986</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.09047980176298757</t>
+          <t>0.09148001759734582</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.001768569984840873</t>
+          <t>-0.0006749346157092218</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.0001198607285648468</t>
+          <t>-0.0001967952176190613</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.04561581977771101</t>
+          <t>0.01105457588252956</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.3194321177608941</t>
+          <t>0.3185244881259408</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.720560497795359</t>
+          <t>0.7820832597153745</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -6563,64 +6563,64 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
       <c r="BA7" t="inlineStr">
         <is>
           <t>12.0</t>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4040506.0</t>
+          <t>6786190.0</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>723111.0</t>
+          <t>987073.0</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>4657617.0</t>
+          <t>7667263.0</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -6758,17 +6758,17 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -6779,252 +6779,252 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>226</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>68.31</t>
+          <t>55.28</t>
         </is>
       </c>
       <c r="CK7" t="n">
-        <v>-1.97</v>
+        <v>-0.58</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.85</v>
+        <v>-0.82</v>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>58.76000000000001</t>
+          <t>58.73999999999999</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>58.39</t>
+          <t>58.27</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>56.23</t>
+          <t>56.17</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
+          <t>51.85875</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>-0.0003403675970049536</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>-0.00205514642918303</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>-0.0006749346157092218</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>-0.001173688047943156</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>-0.00260688756245675</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>0.002597904759603198</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>-57.25</t>
+        </is>
+      </c>
+      <c r="DB7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DD7" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>-93.28</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>5648900594.207143</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>464349189.0</t>
+        </is>
+      </c>
+      <c r="DI7" t="n">
+        <v>1223840761.4</v>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>1013338249.0</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>1611987982.833333</t>
+        </is>
+      </c>
+      <c r="DL7" t="n">
+        <v>1533541700.16</v>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>2698659312.1</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>-119906144.297783</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>-122538723.5266478</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>464349189.0</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU7" t="inlineStr">
-        <is>
-          <t>-0.003053953172717838</t>
-        </is>
-      </c>
-      <c r="CV7" t="inlineStr">
-        <is>
-          <t>-0.00443307757885758</t>
-        </is>
-      </c>
-      <c r="CW7" t="inlineStr">
-        <is>
-          <t>-0.001768569984840873</t>
-        </is>
-      </c>
-      <c r="CX7" t="inlineStr">
-        <is>
-          <t>-0.001987754015440713</t>
-        </is>
-      </c>
-      <c r="CY7" t="inlineStr">
-        <is>
-          <t>-0.003545989630041935</t>
-        </is>
-      </c>
-      <c r="CZ7" t="inlineStr">
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>-3.79</t>
+        </is>
+      </c>
+      <c r="DU7" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV7" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE7" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EF7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="DA7" t="inlineStr">
-        <is>
-          <t>-53.11</t>
-        </is>
-      </c>
-      <c r="DB7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DD7" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE7" t="inlineStr">
-        <is>
-          <t>-92.22</t>
-        </is>
-      </c>
-      <c r="DF7" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="DG7" t="inlineStr">
-        <is>
-          <t>7427894012.401478</t>
-        </is>
-      </c>
-      <c r="DH7" t="inlineStr">
-        <is>
-          <t>931223287.0</t>
-        </is>
-      </c>
-      <c r="DI7" t="n">
-        <v>1410108869.6</v>
-      </c>
-      <c r="DJ7" t="inlineStr">
-        <is>
-          <t>1023386209.4</t>
-        </is>
-      </c>
-      <c r="DK7" t="inlineStr">
-        <is>
-          <t>1634858488.1</t>
-        </is>
-      </c>
-      <c r="DL7" t="n">
-        <v>1559387232.3</v>
-      </c>
-      <c r="DM7" t="inlineStr">
-        <is>
-          <t>2830262055.8375</t>
-        </is>
-      </c>
-      <c r="DN7" t="inlineStr">
-        <is>
-          <t>-119427493.5704179</t>
-        </is>
-      </c>
-      <c r="DO7" t="inlineStr">
-        <is>
-          <t>-75357945.045573</t>
-        </is>
-      </c>
-      <c r="DP7" t="inlineStr">
-        <is>
-          <t>931223287.0</t>
-        </is>
-      </c>
-      <c r="DQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR7" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="DS7" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT7" t="inlineStr">
-        <is>
-          <t>-5.11</t>
-        </is>
-      </c>
-      <c r="DU7" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV7" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW7" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY7" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="DZ7" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA7" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB7" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE7" t="inlineStr">
-        <is>
-          <t>3.24</t>
-        </is>
-      </c>
-      <c r="EF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG7" t="inlineStr">
         <is>
           <t>4.15</t>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>68.95</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>73.12</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>173030</t>
+          <t>172448</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
@@ -7067,32 +7067,32 @@
       </c>
       <c r="EO7" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="ES7" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="ET7" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU7" t="inlineStr">
@@ -7112,42 +7112,42 @@
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FA7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF7" t="inlineStr">
@@ -7157,22 +7157,22 @@
       </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK7" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26413.098</t>
+          <t>16045.294</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7384,17 +7384,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.35933081637068126</t>
+          <t>0.37788535417800007</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -7454,47 +7454,47 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.26500000000001</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>61.93871870579128</t>
+          <t>61.94614272573978</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>56.80128129420873</t>
+          <t>56.58385727426024</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.08653254862022154</t>
+          <t>0.09047980176292138</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.0006741951795043999</t>
+          <t>-0.00176856998484054</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.0003478106572433193</t>
+          <t>0.0001198607285666231</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.02405878993879684</t>
+          <t>0.04561581977777873</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.3194321177608941</t>
+          <t>0.3185244881259408</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.628287038417389</t>
+          <t>0.7205604977951365</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -7539,24 +7539,24 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AQ8" t="inlineStr">
         <is>
           <t>False</t>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4040506.0</t>
+          <t>6786190.0</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>723111.0</t>
+          <t>987073.0</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>4657617.0</t>
+          <t>7667263.0</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -7744,17 +7744,17 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -7765,252 +7765,252 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>226</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>68.29</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>77.53</t>
+          <t>68.31</t>
         </is>
       </c>
       <c r="CK8" t="n">
-        <v>-0.24</v>
+        <v>-1.97</v>
       </c>
       <c r="CL8" t="n">
-        <v>-0.72</v>
+        <v>-0.85</v>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>58.94</t>
+          <t>58.76000000000001</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>58.65</t>
+          <t>58.39</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.27</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>56.23</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>60.42</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
+          <t>51.724375</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>-0.003053953172717838</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>-0.00443307757885758</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>-0.00176856998484054</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>-0.001987754015440713</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>-0.003545989630041935</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>0.002333477325302091</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>-53.11</t>
+        </is>
+      </c>
+      <c r="DB8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>-92.32</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>5648900594.207143</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>931223287.0</t>
+        </is>
+      </c>
+      <c r="DI8" t="n">
+        <v>1410108869.6</v>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>1023386209.4</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>1634858488.1</t>
+        </is>
+      </c>
+      <c r="DL8" t="n">
+        <v>1559387232.3</v>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>2830262055.8375</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>-119427493.5288985</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>-75357945.03665853</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>931223287.0</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU8" t="inlineStr">
-        <is>
-          <t>0.00959232613908867</t>
-        </is>
-      </c>
-      <c r="CV8" t="inlineStr">
-        <is>
-          <t>-0.001872021783526301</t>
-        </is>
-      </c>
-      <c r="CW8" t="inlineStr">
-        <is>
-          <t>0.0006741951795043999</t>
-        </is>
-      </c>
-      <c r="CX8" t="inlineStr">
-        <is>
-          <t>-0.001240804750509583</t>
-        </is>
-      </c>
-      <c r="CY8" t="inlineStr">
-        <is>
-          <t>-0.00269345039219504</t>
-        </is>
-      </c>
-      <c r="CZ8" t="inlineStr">
+      <c r="DR8" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>-5.11</t>
+        </is>
+      </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="DA8" t="inlineStr">
-        <is>
-          <t>-26.77</t>
-        </is>
-      </c>
-      <c r="DB8" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="DD8" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE8" t="inlineStr">
-        <is>
-          <t>-91.19</t>
-        </is>
-      </c>
-      <c r="DF8" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="DG8" t="inlineStr">
-        <is>
-          <t>7427894012.401478</t>
-        </is>
-      </c>
-      <c r="DH8" t="inlineStr">
-        <is>
-          <t>1593900291.0</t>
-        </is>
-      </c>
-      <c r="DI8" t="n">
-        <v>1361980793.6</v>
-      </c>
-      <c r="DJ8" t="inlineStr">
-        <is>
-          <t>1001949471.9</t>
-        </is>
-      </c>
-      <c r="DK8" t="inlineStr">
-        <is>
-          <t>1677857345.333333</t>
-        </is>
-      </c>
-      <c r="DL8" t="n">
-        <v>1586577483.32</v>
-      </c>
-      <c r="DM8" t="inlineStr">
-        <is>
-          <t>2988357275.8875</t>
-        </is>
-      </c>
-      <c r="DN8" t="inlineStr">
-        <is>
-          <t>-127440138.7567534</t>
-        </is>
-      </c>
-      <c r="DO8" t="inlineStr">
-        <is>
-          <t>-55287702.52412391</t>
-        </is>
-      </c>
-      <c r="DP8" t="inlineStr">
-        <is>
-          <t>1593900291.0</t>
-        </is>
-      </c>
-      <c r="DQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR8" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="DS8" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT8" t="inlineStr">
-        <is>
-          <t>-3.13</t>
-        </is>
-      </c>
-      <c r="DU8" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV8" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW8" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY8" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="DZ8" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA8" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB8" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED8" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="EE8" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="EF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG8" t="inlineStr">
         <is>
           <t>4.15</t>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>68.95</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>73.12</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>173030</t>
+          <t>172448</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
@@ -8053,32 +8053,32 @@
       </c>
       <c r="EO8" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP8" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="EQ8" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="ER8" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="ES8" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="ET8" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU8" t="inlineStr">
@@ -8098,42 +8098,42 @@
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FA8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF8" t="inlineStr">
@@ -8143,22 +8143,22 @@
       </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK8" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19550.629</t>
+          <t>26413.098</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8370,17 +8370,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.21834356965752405</t>
+          <t>0.35933081637068126</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -8440,47 +8440,47 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>59.33000000000001</t>
+          <t>59.36999999999999</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>61.96026914772653</t>
+          <t>61.93871870578922</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>56.69973085227348</t>
+          <t>56.80128129421076</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.08866573900982716</t>
+          <t>0.08653254862015262</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.002704073009971442</t>
+          <t>0.0006741951795043999</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.000412204317197018</t>
+          <t>-0.0003478106572442075</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.06841491421606827</t>
+          <t>-0.0240587899388307</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.3194321177608941</t>
+          <t>0.3185244881259408</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.5836602541452416</t>
+          <t>0.6282870384171205</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -8535,14 +8535,14 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AQ9" t="inlineStr">
         <is>
           <t>False</t>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4040506.0</t>
+          <t>6786190.0</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>723111.0</t>
+          <t>987073.0</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>4657617.0</t>
+          <t>7667263.0</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -8730,17 +8730,17 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -8751,320 +8751,320 @@
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>226</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>97.62</t>
+          <t>68.29</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>77.53</t>
         </is>
       </c>
       <c r="CK9" t="n">
-        <v>2.95</v>
+        <v>-0.24</v>
       </c>
       <c r="CL9" t="n">
-        <v>-1.6</v>
+        <v>-0.72</v>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>58.38</t>
+          <t>58.94</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>58.76000000000001</t>
+          <t>58.65</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>59.33</t>
+          <t>59.37</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>56.42</t>
+          <t>56.34</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
+          <t>60.63</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>51.60395833333333</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>0.00959232613908867</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>-0.001872021783526301</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>0.0006741951795043999</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>-0.001240804750509583</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>-0.00269345039219504</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>0.002606707008560916</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>-26.77</t>
+        </is>
+      </c>
+      <c r="DB9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>-91.29</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>5648900594.207143</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>1593900291.0</t>
+        </is>
+      </c>
+      <c r="DI9" t="n">
+        <v>1361980793.6</v>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>1001949471.9</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>1677857345.333333</t>
+        </is>
+      </c>
+      <c r="DL9" t="n">
+        <v>1586577483.32</v>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>2988357275.8875</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>-127440138.7093058</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>-55287702.5139358</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>1593900291.0</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>-3.13</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>68.95</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr">
+        <is>
+          <t>23.33%</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
+          <t>12.64%</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>73.12</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t>172448</t>
+        </is>
+      </c>
+      <c r="EM9" t="inlineStr">
+        <is>
+          <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN9" t="inlineStr">
+        <is>
+          <t>台玻-玻璃陶瓷-上市</t>
+        </is>
+      </c>
+      <c r="EO9" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷右上上市</t>
+        </is>
+      </c>
+      <c r="EP9" t="inlineStr">
+        <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CU9" t="inlineStr">
-        <is>
-          <t>0.007941988950276091</t>
-        </is>
-      </c>
-      <c r="CV9" t="inlineStr">
-        <is>
-          <t>-0.001020061203672262</t>
-        </is>
-      </c>
-      <c r="CW9" t="inlineStr">
-        <is>
-          <t>0.002704073009971442</t>
-        </is>
-      </c>
-      <c r="CX9" t="inlineStr">
-        <is>
-          <t>-0.001451404499353992</t>
-        </is>
-      </c>
-      <c r="CY9" t="inlineStr">
-        <is>
-          <t>-0.002113275679890059</t>
-        </is>
-      </c>
-      <c r="CZ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA9" t="inlineStr">
-        <is>
-          <t>-24.84</t>
-        </is>
-      </c>
-      <c r="DB9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DD9" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE9" t="inlineStr">
-        <is>
-          <t>-90.60</t>
-        </is>
-      </c>
-      <c r="DF9" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="DG9" t="inlineStr">
-        <is>
-          <t>7427894012.401478</t>
-        </is>
-      </c>
-      <c r="DH9" t="inlineStr">
-        <is>
-          <t>1169464009.0</t>
-        </is>
-      </c>
-      <c r="DI9" t="n">
-        <v>1156657216.4</v>
-      </c>
-      <c r="DJ9" t="inlineStr">
-        <is>
-          <t>949368671.7</t>
-        </is>
-      </c>
-      <c r="DK9" t="inlineStr">
-        <is>
-          <t>1674339770.233333</t>
-        </is>
-      </c>
-      <c r="DL9" t="n">
-        <v>1613873208.76</v>
-      </c>
-      <c r="DM9" t="inlineStr">
-        <is>
-          <t>3038222859.6875</t>
-        </is>
-      </c>
-      <c r="DN9" t="inlineStr">
-        <is>
-          <t>-140558763.5263224</t>
-        </is>
-      </c>
-      <c r="DO9" t="inlineStr">
-        <is>
-          <t>-95642474.26047778</t>
-        </is>
-      </c>
-      <c r="DP9" t="inlineStr">
-        <is>
-          <t>1169464009.0</t>
-        </is>
-      </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR9" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="DS9" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT9" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="DU9" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV9" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW9" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY9" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="DZ9" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA9" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB9" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE9" t="inlineStr">
-        <is>
-          <t>3.38</t>
-        </is>
-      </c>
-      <c r="EF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="EG9" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="EH9" t="inlineStr">
-        <is>
-          <t>69.19</t>
-        </is>
-      </c>
-      <c r="EI9" t="inlineStr">
-        <is>
-          <t>23.33%</t>
-        </is>
-      </c>
-      <c r="EJ9" t="inlineStr">
-        <is>
-          <t>12.64%</t>
-        </is>
-      </c>
-      <c r="EK9" t="inlineStr">
-        <is>
-          <t>74.17</t>
-        </is>
-      </c>
-      <c r="EL9" t="inlineStr">
-        <is>
-          <t>173030</t>
-        </is>
-      </c>
-      <c r="EM9" t="inlineStr">
-        <is>
-          <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN9" t="inlineStr">
-        <is>
-          <t>台玻-玻璃陶瓷-上市</t>
-        </is>
-      </c>
-      <c r="EO9" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="EP9" t="inlineStr">
-        <is>
-          <t>59.3</t>
-        </is>
-      </c>
       <c r="EQ9" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="ER9" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="ES9" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="ET9" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU9" t="inlineStr">
@@ -9084,42 +9084,42 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF9" t="inlineStr">
@@ -9129,22 +9129,22 @@
       </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK9" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>33184.205</t>
+          <t>19550.629</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9356,17 +9356,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.09647287800346335</t>
+          <t>0.21834356965752405</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -9426,47 +9426,47 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>59.16999999999999</t>
+          <t>59.33</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>61.98581997032329</t>
+          <t>61.96026914772452</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>56.3541800296767</t>
+          <t>56.69973085227548</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.09517728478361659</t>
+          <t>0.08866573900975962</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.001015056673997483</t>
+          <t>0.00270407300997122</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.0003726729663900974</t>
+          <t>-0.0004122043171994605</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.02965383747479677</t>
+          <t>-0.06841491421615964</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.3194321177608941</t>
+          <t>0.3185244881259408</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.5719350287051813</t>
+          <t>0.5836602541449827</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -9511,24 +9511,24 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AQ10" t="inlineStr">
         <is>
           <t>False</t>
@@ -9606,7 +9606,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4040506.0</t>
+          <t>6786190.0</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>723111.0</t>
+          <t>987073.0</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>4657617.0</t>
+          <t>7667263.0</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -9737,252 +9737,252 @@
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>226</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>97.62</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="CK10" t="n">
-        <v>1.52</v>
+        <v>2.95</v>
       </c>
       <c r="CL10" t="n">
-        <v>-2.11</v>
+        <v>-1.6</v>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>57.92</t>
+          <t>58.38</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>58.82000000000001</t>
+          <t>58.76000000000001</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>59.33</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.42</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>60.92</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
+          <t>51.46979166666667</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>0.007941988950276091</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>-0.001020061203672262</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>0.00270407300997122</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>-0.001451404499353992</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>-0.002113275679890059</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>0.002772230610621262</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>-24.84</t>
+        </is>
+      </c>
+      <c r="DB10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>-90.71</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>5648900594.207143</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>1169464009.0</t>
+        </is>
+      </c>
+      <c r="DI10" t="n">
+        <v>1156657216.4</v>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>949368671.7</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>1674339770.233333</t>
+        </is>
+      </c>
+      <c r="DL10" t="n">
+        <v>1613873208.76</v>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>3038222859.6875</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>-140558763.4721003</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>-95642474.24883413</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>1169464009.0</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU10" t="inlineStr">
-        <is>
-          <t>0.00207612456747408</t>
-        </is>
-      </c>
-      <c r="CV10" t="inlineStr">
-        <is>
-          <t>-0.0005097706032284322</t>
-        </is>
-      </c>
-      <c r="CW10" t="inlineStr">
-        <is>
-          <t>0.001015056673997483</t>
-        </is>
-      </c>
-      <c r="CX10" t="inlineStr">
-        <is>
-          <t>-0.002190000176612972</t>
-        </is>
-      </c>
-      <c r="CY10" t="inlineStr">
-        <is>
-          <t>-0.002864186417618764</t>
-        </is>
-      </c>
-      <c r="CZ10" t="inlineStr">
+      <c r="DR10" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT10" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="DU10" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV10" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="DA10" t="inlineStr">
-        <is>
-          <t>-53.64</t>
-        </is>
-      </c>
-      <c r="DB10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="DD10" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE10" t="inlineStr">
-        <is>
-          <t>-90.01</t>
-        </is>
-      </c>
-      <c r="DF10" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="DG10" t="inlineStr">
-        <is>
-          <t>7427894012.401478</t>
-        </is>
-      </c>
-      <c r="DH10" t="inlineStr">
-        <is>
-          <t>1960267031.0</t>
-        </is>
-      </c>
-      <c r="DI10" t="n">
-        <v>1057627192.8</v>
-      </c>
-      <c r="DJ10" t="inlineStr">
-        <is>
-          <t>964572142.2</t>
-        </is>
-      </c>
-      <c r="DK10" t="inlineStr">
-        <is>
-          <t>1681979897.433333</t>
-        </is>
-      </c>
-      <c r="DL10" t="n">
-        <v>1660438563.74</v>
-      </c>
-      <c r="DM10" t="inlineStr">
-        <is>
-          <t>3162578562.8125</t>
-        </is>
-      </c>
-      <c r="DN10" t="inlineStr">
-        <is>
-          <t>-148725361.5746577</t>
-        </is>
-      </c>
-      <c r="DO10" t="inlineStr">
-        <is>
-          <t>-104401029.5888236</t>
-        </is>
-      </c>
-      <c r="DP10" t="inlineStr">
-        <is>
-          <t>1960267031.0</t>
-        </is>
-      </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR10" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="DS10" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT10" t="inlineStr">
-        <is>
-          <t>-3.13</t>
-        </is>
-      </c>
-      <c r="DU10" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV10" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW10" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY10" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="DZ10" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA10" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB10" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED10" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE10" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="EF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG10" t="inlineStr">
         <is>
           <t>4.15</t>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>68.95</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>73.12</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
-          <t>173030</t>
+          <t>172448</t>
         </is>
       </c>
       <c r="EM10" t="inlineStr">
@@ -10025,32 +10025,32 @@
       </c>
       <c r="EO10" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP10" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="EQ10" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="ER10" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="ES10" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="ET10" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU10" t="inlineStr">
@@ -10070,42 +10070,42 @@
       </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FA10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF10" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK10" t="inlineStr">

--- a/Result/checksun_type/玻璃.xlsx
+++ b/Result/checksun_type/玻璃.xlsx
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23093.784</t>
+          <t>23901.898</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.11135316584249741</t>
+          <t>0.11903274433361645</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1538,47 +1538,47 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>58.86500000000001</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>61.08858174787246</t>
+          <t>61.16088012671542</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>56.64141825212756</t>
+          <t>56.63911987328458</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.07554851772266885</t>
+          <t>0.0767701231482316</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.0005949345571989451</t>
+          <t>0.0005945808205216618</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.0006847801378488949</t>
+          <t>0.001183500693124673</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.002472742767799962</t>
+          <t>0.01616981328430134</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.3185244881259408</t>
+          <t>0.3168162812305134</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.7911038446557226</t>
+          <t>0.8235494318045389</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1623,22 +1623,22 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1673,32 +1673,32 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1718,32 +1718,32 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>6786190.0</t>
+          <t>14817876.0</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>17000.0</t>
+          <t>57000.0</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>123000.0</t>
+          <t>121000.0</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-106000.0</t>
+          <t>-64000.0</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>987073.0</t>
+          <t>1810703.0</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>7667263.0</t>
+          <t>16564579.0</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1849,58 +1849,58 @@
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>230</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>79.88</t>
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.26</v>
+        <v>0.95</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>59.46</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>58.88000000000001</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>58.87</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>56.59</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
@@ -1910,58 +1910,58 @@
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>52.50166666666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>0.003059143439837042</t>
+          <t>0.007455099966113155</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>0.001360544217687387</t>
+          <t>0.001698369565217073</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>0.0005949345571989451</t>
+          <t>0.0005945808205216618</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>0.001770193482147464</t>
+          <t>0.003110035164602287</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>-0.0007730477931574553</t>
+          <t>-6.272804257134723e-05</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>0.002286891537705671</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="DB2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DC2" t="n">
         <v>0.22</v>
       </c>
-      <c r="DC2" t="n">
-        <v>0.21</v>
-      </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>-95.18</t>
+          <t>-94.79</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
@@ -1971,48 +1971,48 @@
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>5648900594.207143</t>
+          <t>7376104763.473171</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>1391651459.0</t>
+          <t>1434343204.0</t>
         </is>
       </c>
       <c r="DI2" t="n">
-        <v>978592810.6</v>
+        <v>1173445043.8</v>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>1101216786.0</t>
+          <t>1048624403.3</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>1410351796.1</t>
+          <t>1411256752.533333</t>
         </is>
       </c>
       <c r="DL2" t="n">
-        <v>1501930217.1</v>
+        <v>1509531056.42</v>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>2534452706.925</t>
+          <t>2523130309.375</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>-106948730.6812849</t>
+          <t>-94077175.75220172</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>-60231869.45079255</t>
+          <t>-23283623.53972125</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>1391651459.0</t>
+          <t>1434343204.0</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>68.95</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>172448</t>
+          <t>173902</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
@@ -2137,32 +2137,32 @@
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
@@ -2182,67 +2182,67 @@
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FB2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FD2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12062.573</t>
+          <t>23093.784</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2454,17 +2454,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.28003130372797114</t>
+          <t>-0.11135316584249741</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -2509,242 +2509,242 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>弱勢整理</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 20&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>58.86499999999999</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>61.08858174787481</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>56.64141825212518</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.07554851772274902</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.000594934557198723</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.0006847801378484508</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.002472742767793745</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.3168162812305134</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.7911038446560315</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>58.83</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>61.04677812673161</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>56.61322187326839</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.07536216647056303</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>-0.001103659054249029</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-0.00356859712204749</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.06377897240368935</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.3185244881259408</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.7611408795635349</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2026-04-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>2026-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>14817876.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>57000.0</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>121000.0</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>-64000.0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>1810703.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>16564579.0</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>6786190.0</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>17000.0</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>123000.0</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>-106000.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>987073.0</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>7667263.0</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -2814,17 +2814,17 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -2835,119 +2835,119 @@
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>230</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CK3" t="n">
-        <v>1.12</v>
+        <v>0.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>58.88000000000001</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.86</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.59</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.78</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>52.38187500000001</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>0.006500171057133075</t>
+          <t>0.003059143439837042</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>0.001703577512776722</t>
+          <t>0.001360544217687387</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>-0.001103659054249029</t>
+          <t>0.000594934557198723</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>0.001382660025171623</t>
+          <t>0.001770193482147464</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>-0.0005220569042025947</t>
+          <t>-0.0007730477931574553</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>0.002527920765234448</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="DB3" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>-95.26</t>
+          <t>-95.12</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
@@ -2957,48 +2957,48 @@
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>5648900594.207143</t>
+          <t>7376104763.473171</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>716628303.0</t>
+          <t>1391651459.0</t>
         </is>
       </c>
       <c r="DI3" t="n">
-        <v>793132356.6</v>
+        <v>978592810.6</v>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>1101620613.1</t>
+          <t>1101216786.0</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>1512236185.5</t>
+          <t>1410351796.1</t>
         </is>
       </c>
       <c r="DL3" t="n">
-        <v>1491436510.72</v>
+        <v>1501930217.1</v>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>2550447434.6375</t>
+          <t>2534452706.925</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>-115442705.4504653</t>
+          <t>-106948730.6999255</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>-106289824.1697955</t>
+          <t>-60231869.45479345</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>716628303.0</t>
+          <t>1391651459.0</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>68.95</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>172448</t>
+          <t>173902</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
@@ -3123,32 +3123,32 @@
       </c>
       <c r="EO3" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
@@ -3168,67 +3168,67 @@
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FB3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FE3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15496.264</t>
+          <t>12062.573</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.23927286091689726</t>
+          <t>-0.28003130372797114</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -3495,242 +3495,242 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>58.83</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>61.04677812673398</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>56.61322187326602</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.07536216647064348</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-0.001103659054249029</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-0.003568597122044825</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.06377897240356267</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.3168162812305134</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.7611408795638696</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>58.895</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>61.26540969143753</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>56.52459030856246</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.08049612671491764</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>-0.002117926126736669</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-0.005781894342767324</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.08696589266464283</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.3185244881259408</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0.7815573182263081</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2026-04-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>2026-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>14817876.0</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>57000.0</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>121000.0</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>-64000.0</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>1810703.0</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>16564579.0</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>6786190.0</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>17000.0</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>123000.0</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>-106000.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>987073.0</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>7667263.0</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -3800,140 +3800,140 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>230</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CK4" t="n">
-        <v>0.58</v>
+        <v>1.12</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0.74</v>
+        <v>0.02</v>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>56.41</t>
+          <t>56.49</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>59.86</t>
+          <t>59.83</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>52.24979166666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>2.220446049250313e-16</t>
+          <t>0.006500171057133075</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>0.004792879150975704</t>
+          <t>0.001703577512776722</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>-0.002117926126736669</t>
+          <t>-0.001103659054249029</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>0.001669063726273734</t>
+          <t>0.001382660025171623</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>-0.001834269575095582</t>
+          <t>-0.0005220569042025947</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>0.002534327343953091</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>-29.02</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="DB4" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="DC4" t="n">
         <v>0.2</v>
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
         <is>
-          <t>-95.24</t>
+          <t>-95.21</t>
         </is>
       </c>
       <c r="DF4" t="inlineStr">
@@ -3943,48 +3943,48 @@
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>5648900594.207143</t>
+          <t>7376104763.473171</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>913096038.0</t>
+          <t>716628303.0</t>
         </is>
       </c>
       <c r="DI4" t="n">
-        <v>836051353.4</v>
+        <v>793132356.6</v>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>1099016073.5</t>
+          <t>1101620613.1</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>1537638652.2</t>
+          <t>1512236185.5</t>
         </is>
       </c>
       <c r="DL4" t="n">
-        <v>1496862031.52</v>
+        <v>1491436510.72</v>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>2578499982.6</t>
+          <t>2550447434.6375</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>-117106865.6833144</t>
+          <t>-115442705.4717676</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>-95966927.61945021</t>
+          <t>-106289824.1743681</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
         <is>
-          <t>913096038.0</t>
+          <t>716628303.0</t>
         </is>
       </c>
       <c r="DQ4" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
@@ -4049,17 +4049,17 @@
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>68.95</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
-          <t>172448</t>
+          <t>173902</t>
         </is>
       </c>
       <c r="EM4" t="inlineStr">
@@ -4109,32 +4109,32 @@
       </c>
       <c r="EO4" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="EQ4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="ER4" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="ES4" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="ET4" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU4" t="inlineStr">
@@ -4154,67 +4154,67 @@
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="EZ4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="FA4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EZ4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="FA4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FE4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23784.387</t>
+          <t>15496.264</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4426,17 +4426,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.08663988999632684</t>
+          <t>-0.23927286091689726</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4481,242 +4481,242 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>58.895</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>61.26540969143974</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>56.52459030856025</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.08049612671499268</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>-0.00211792612673678</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-0.005781894342764105</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.08696589266449983</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.3168162812305134</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.7815573182265803</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>59.02</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>61.62169984918725</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>56.41830015081274</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.08816332935232991</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>-0.0007618725133330395</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-0.00224318461089712</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.03396950249461561</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.3185244881259408</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>0.8245796448189587</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>2026-04-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>2026-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>14817876.0</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>57000.0</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>121000.0</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>-64000.0</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>1810703.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>16564579.0</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>6786190.0</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>17000.0</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>123000.0</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>-106000.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>987073.0</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>7667263.0</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -4786,17 +4786,17 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -4807,119 +4807,119 @@
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>230</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="CK5" t="n">
-        <v>2.46</v>
+        <v>0.58</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.95</v>
+        <v>-0.74</v>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>58.45999999999999</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>56.32</t>
+          <t>56.41</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>59.97</t>
+          <t>59.86</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>52.11770833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>-0.0006837606837607479</t>
+          <t>2.220446049250313e-16</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>0.003607627555402892</t>
+          <t>0.004792879150975704</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>-0.0007618725133330395</t>
+          <t>-0.00211792612673678</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>0.002349297880292589</t>
+          <t>0.001669063726273734</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>-0.001872444892906611</t>
+          <t>-0.001834269575095582</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>0.00256085538180395</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>-33.32</t>
+          <t>-29.02</t>
         </is>
       </c>
       <c r="DB5" t="n">
         <v>0.15</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>-94.89</t>
+          <t>-95.18</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
@@ -4929,48 +4929,48 @@
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>5648900594.207143</t>
+          <t>7376104763.473171</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>1411506215.0</t>
+          <t>913096038.0</t>
         </is>
       </c>
       <c r="DI5" t="n">
-        <v>972212204</v>
+        <v>836051353.4</v>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>1064434710.2</t>
+          <t>1099016073.5</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>1565951673.033333</t>
+          <t>1537638652.2</t>
         </is>
       </c>
       <c r="DL5" t="n">
-        <v>1495033587.44</v>
+        <v>1496862031.52</v>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>2612782440.9375</t>
+          <t>2578499982.6</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>-120950490.7858351</t>
+          <t>-117106865.7076584</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>-98842656.73969078</t>
+          <t>-95966927.62467611</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>1411506215.0</t>
+          <t>913096038.0</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
@@ -5035,17 +5035,17 @@
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>68.95</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>172448</t>
+          <t>173902</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
@@ -5095,32 +5095,32 @@
       </c>
       <c r="EO5" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
@@ -5140,67 +5140,67 @@
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="FA5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EZ5" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="FA5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK5" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7975.945</t>
+          <t>23784.387</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>59.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5412,17 +5412,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.06753878030510366</t>
+          <t>-0.08663988999632684</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -5467,242 +5467,242 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>59.02</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>61.62169984918928</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>56.41830015081073</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.08816332935239829</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>-0.0007618725133327064</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-0.002243184610895566</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.03396950249456443</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.3168162812305134</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.8245796448191481</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>59.06500000000001</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>61.76023946792703</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>56.36976053207299</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.09126350522058804</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>-0.002701561840438793</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-0.002804803302640657</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.002366772355803071</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.3185244881259408</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>0.8234794118945751</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2026-04-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>2026-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>14817876.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>57000.0</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>121000.0</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-64000.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>1810703.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>16564579.0</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>6786190.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>17000.0</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>123000.0</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>-106000.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>987073.0</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>7667263.0</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -5772,17 +5772,17 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -5793,119 +5793,119 @@
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>230</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="CK6" t="n">
-        <v>-1.54</v>
+        <v>2.46</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.96</v>
+        <v>-0.95</v>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.45999999999999</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>58.21</t>
+          <t>58.42</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>59.07</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.32</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>59.97</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>51.98458333333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>-0.004085801838610736</t>
+          <t>-0.0006837606837607479</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>-0.001029689377037957</t>
+          <t>0.003607627555402892</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>-0.002701561840438793</t>
+          <t>-0.0007618725133327064</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>0.0003560809728131442</t>
+          <t>0.002349297880292589</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>-0.002945599751076</t>
+          <t>-0.001872444892906611</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>0.002426462908059479</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>-85.80</t>
+          <t>-33.32</t>
         </is>
       </c>
       <c r="DB6" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE6" t="inlineStr">
         <is>
-          <t>-94.46</t>
+          <t>-94.83</t>
         </is>
       </c>
       <c r="DF6" t="inlineStr">
@@ -5915,48 +5915,48 @@
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>5648900594.207143</t>
+          <t>7376104763.473171</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>460082038.0</t>
+          <t>1411506215.0</t>
         </is>
       </c>
       <c r="DI6" t="n">
-        <v>923803762.8</v>
+        <v>972212204</v>
       </c>
       <c r="DJ6" t="inlineStr">
         <is>
-          <t>990715477.8</t>
+          <t>1064434710.2</t>
         </is>
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>1577592671.866667</t>
+          <t>1565951673.033333</t>
         </is>
       </c>
       <c r="DL6" t="n">
-        <v>1503106536.6</v>
+        <v>1495033587.44</v>
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>2650980248.8625</t>
+          <t>2612782440.9375</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>-124970096.9760432</t>
+          <t>-120950490.8136552</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>-152821836.7064742</t>
+          <t>-98842656.74566317</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
         <is>
-          <t>460082038.0</t>
+          <t>1411506215.0</t>
         </is>
       </c>
       <c r="DQ6" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
@@ -6021,17 +6021,17 @@
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>68.95</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>172448</t>
+          <t>173902</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="EO6" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="ES6" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>59.9</t>
         </is>
       </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU6" t="inlineStr">
@@ -6126,67 +6126,67 @@
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="FA6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EZ6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="FA6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK6" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8054.096</t>
+          <t>7975.945</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6398,17 +6398,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.20773173479608792</t>
+          <t>-0.06753878030510366</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -6453,242 +6453,242 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>59.065</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>61.76023946792896</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>56.36976053207103</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.09126350522065399</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>-0.002701561840439015</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-0.002804803302640768</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.00236677235579652</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.3168162812305134</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.8234794118947475</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>59.225</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>61.9339520211014</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>56.5160479788986</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.09148001759734582</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>-0.0006749346157092218</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-0.0001967952176190613</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>0.01105457588252956</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.3185244881259408</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0.7820832597153745</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2026-04-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>2026-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>14817876.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>57000.0</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>121000.0</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>-64000.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>1810703.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>16564579.0</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>6786190.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>17000.0</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>123000.0</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>-106000.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>987073.0</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>7667263.0</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -6758,17 +6758,17 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -6779,119 +6779,119 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>230</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>55.28</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="CK7" t="n">
-        <v>-0.58</v>
+        <v>-1.54</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.82</v>
+        <v>-0.96</v>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>58.73999999999999</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>58.27</t>
+          <t>58.21</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>56.17</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>51.85875</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>-0.0003403675970049536</t>
+          <t>-0.004085801838610736</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>-0.00205514642918303</t>
+          <t>-0.001029689377037957</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>-0.0006749346157092218</t>
+          <t>-0.002701561840439015</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>-0.001173688047943156</t>
+          <t>0.0003560809728131442</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>-0.00260688756245675</t>
+          <t>-0.002945599751076</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>0.002597904759603198</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>-57.25</t>
+          <t>-85.80</t>
         </is>
       </c>
       <c r="DB7" t="n">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="DD7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE7" t="inlineStr">
         <is>
-          <t>-93.28</t>
+          <t>-94.40</t>
         </is>
       </c>
       <c r="DF7" t="inlineStr">
@@ -6901,48 +6901,48 @@
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>5648900594.207143</t>
+          <t>7376104763.473171</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>464349189.0</t>
+          <t>460082038.0</t>
         </is>
       </c>
       <c r="DI7" t="n">
-        <v>1223840761.4</v>
+        <v>923803762.8</v>
       </c>
       <c r="DJ7" t="inlineStr">
         <is>
-          <t>1013338249.0</t>
+          <t>990715477.8</t>
         </is>
       </c>
       <c r="DK7" t="inlineStr">
         <is>
-          <t>1611987982.833333</t>
+          <t>1577592671.866667</t>
         </is>
       </c>
       <c r="DL7" t="n">
-        <v>1533541700.16</v>
+        <v>1503106536.6</v>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>2698659312.1</t>
+          <t>2650980248.8625</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>-119906144.297783</t>
+          <t>-124970097.0078356</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>-122538723.5266478</t>
+          <t>-152821836.7132996</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
         <is>
-          <t>464349189.0</t>
+          <t>460082038.0</t>
         </is>
       </c>
       <c r="DQ7" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>68.95</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>172448</t>
+          <t>173902</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="EO7" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
@@ -7082,17 +7082,17 @@
       </c>
       <c r="ER7" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="ES7" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="ET7" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU7" t="inlineStr">
@@ -7112,67 +7112,67 @@
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="FA7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EZ7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="FA7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK7" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16045.294</t>
+          <t>8054.096</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7384,17 +7384,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.37788535417800007</t>
+          <t>0.20773173479608792</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -7439,242 +7439,242 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>59.225</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>61.93395202110334</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>56.51604797889666</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.09148001759741133</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>-0.0006749346157091107</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-0.0001967952176192833</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.0110545758825138</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.3168162812305134</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0.7820832597155659</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>59.26500000000001</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>61.94614272573978</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>56.58385727426024</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0.09047980176292138</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>-0.00176856998484054</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>0.0001198607285666231</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>0.04561581977777873</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0.3185244881259408</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>0.7205604977951365</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>2026-04-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>2026-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>14817876.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>57000.0</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>121000.0</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-64000.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>1810703.0</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>16564579.0</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>6786190.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>17000.0</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>123000.0</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>-106000.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>987073.0</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>7667263.0</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -7744,17 +7744,17 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -7765,119 +7765,119 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>230</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>68.31</t>
+          <t>55.28</t>
         </is>
       </c>
       <c r="CK8" t="n">
-        <v>-1.97</v>
+        <v>-0.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>-0.85</v>
+        <v>-0.82</v>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>58.76000000000001</t>
+          <t>58.73999999999999</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>58.39</t>
+          <t>58.27</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>59.27</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>56.23</t>
+          <t>56.17</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>51.724375</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
         <is>
-          <t>-0.003053953172717838</t>
+          <t>-0.0003403675970049536</t>
         </is>
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>-0.00443307757885758</t>
+          <t>-0.00205514642918303</t>
         </is>
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>-0.00176856998484054</t>
+          <t>-0.0006749346157091107</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>-0.001987754015440713</t>
+          <t>-0.001173688047943156</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>-0.003545989630041935</t>
+          <t>-0.00260688756245675</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>0.002333477325302091</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>-53.11</t>
+          <t>-57.25</t>
         </is>
       </c>
       <c r="DB8" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DD8" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE8" t="inlineStr">
         <is>
-          <t>-92.32</t>
+          <t>-93.19</t>
         </is>
       </c>
       <c r="DF8" t="inlineStr">
@@ -7887,48 +7887,48 @@
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>5648900594.207143</t>
+          <t>7376104763.473171</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>931223287.0</t>
+          <t>464349189.0</t>
         </is>
       </c>
       <c r="DI8" t="n">
-        <v>1410108869.6</v>
+        <v>1223840761.4</v>
       </c>
       <c r="DJ8" t="inlineStr">
         <is>
-          <t>1023386209.4</t>
+          <t>1013338249.0</t>
         </is>
       </c>
       <c r="DK8" t="inlineStr">
         <is>
-          <t>1634858488.1</t>
+          <t>1611987982.833333</t>
         </is>
       </c>
       <c r="DL8" t="n">
-        <v>1559387232.3</v>
+        <v>1533541700.16</v>
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>2830262055.8375</t>
+          <t>2698659312.1</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>-119427493.5288985</t>
+          <t>-119906144.3341149</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>-75357945.03665853</t>
+          <t>-122538723.5344481</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
         <is>
-          <t>931223287.0</t>
+          <t>464349189.0</t>
         </is>
       </c>
       <c r="DQ8" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="DT8" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="DU8" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>68.95</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>172448</t>
+          <t>173902</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
@@ -8053,32 +8053,32 @@
       </c>
       <c r="EO8" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP8" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="EQ8" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="ER8" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="ES8" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="ET8" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU8" t="inlineStr">
@@ -8098,67 +8098,67 @@
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="FA8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EZ8" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="FA8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK8" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26413.098</t>
+          <t>16045.294</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8370,17 +8370,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.35933081637068126</t>
+          <t>0.37788535417800007</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -8425,242 +8425,242 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>59.265</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>61.94614272574173</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>56.58385727425827</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.09047980176298757</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>-0.001768569984840873</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.0001198607285648468</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.04561581977771101</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.3168162812305134</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.720560497795359</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>59.36999999999999</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>61.93871870578922</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>56.80128129421076</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0.08653254862015262</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0.0006741951795043999</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>-0.0003478106572442075</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.0240587899388307</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0.3185244881259408</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>0.6282870384171205</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>2026-04-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>2026-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>14817876.0</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>57000.0</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>121000.0</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>-64000.0</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>1810703.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>16564579.0</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>6786190.0</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>17000.0</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>123000.0</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>-106000.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>987073.0</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>7667263.0</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -8730,17 +8730,17 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -8751,119 +8751,119 @@
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>230</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>68.29</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>77.53</t>
+          <t>68.31</t>
         </is>
       </c>
       <c r="CK9" t="n">
-        <v>-0.24</v>
+        <v>-1.97</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0.72</v>
+        <v>-0.85</v>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>58.94</t>
+          <t>58.76000000000001</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>58.65</t>
+          <t>58.39</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>56.23</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>60.42</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>51.60395833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>0.00959232613908867</t>
+          <t>-0.003053953172717838</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>-0.001872021783526301</t>
+          <t>-0.00443307757885758</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>0.0006741951795043999</t>
+          <t>-0.001768569984840873</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>-0.001240804750509583</t>
+          <t>-0.001987754015440713</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>-0.00269345039219504</t>
+          <t>-0.003545989630041935</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>0.002606707008560916</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>-26.77</t>
+          <t>-53.11</t>
         </is>
       </c>
       <c r="DB9" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="DD9" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE9" t="inlineStr">
         <is>
-          <t>-91.29</t>
+          <t>-92.22</t>
         </is>
       </c>
       <c r="DF9" t="inlineStr">
@@ -8873,48 +8873,48 @@
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>5648900594.207143</t>
+          <t>7376104763.473171</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>1593900291.0</t>
+          <t>931223287.0</t>
         </is>
       </c>
       <c r="DI9" t="n">
-        <v>1361980793.6</v>
+        <v>1410108869.6</v>
       </c>
       <c r="DJ9" t="inlineStr">
         <is>
-          <t>1001949471.9</t>
+          <t>1023386209.4</t>
         </is>
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>1677857345.333333</t>
+          <t>1634858488.1</t>
         </is>
       </c>
       <c r="DL9" t="n">
-        <v>1586577483.32</v>
+        <v>1559387232.3</v>
       </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>2988357275.8875</t>
+          <t>2830262055.8375</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>-127440138.7093058</t>
+          <t>-119427493.5704179</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>-55287702.5139358</t>
+          <t>-75357945.045573</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
         <is>
-          <t>1593900291.0</t>
+          <t>931223287.0</t>
         </is>
       </c>
       <c r="DQ9" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>68.95</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>172448</t>
+          <t>173902</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
@@ -9039,32 +9039,32 @@
       </c>
       <c r="EO9" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP9" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="EQ9" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="ER9" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="ES9" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="ET9" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU9" t="inlineStr">
@@ -9084,67 +9084,67 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="FA9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EZ9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="FA9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK9" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19550.629</t>
+          <t>26413.098</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9356,17 +9356,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.21834356965752405</t>
+          <t>0.35933081637068126</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -9411,242 +9411,242 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>59.37</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>61.93871870579128</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>56.80128129420873</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.08653254862022154</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.0006741951795043999</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>-0.0003478106572433193</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-0.02405878993879684</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.3168162812305134</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0.628287038417389</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>59.33</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>61.96026914772452</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>56.69973085227548</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0.08866573900975962</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.00270407300997122</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>-0.0004122043171994605</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>-0.06841491421615964</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>0.3185244881259408</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>0.5836602541449827</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>2026-04-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>2026-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>14817876.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>57000.0</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>121000.0</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-64000.0</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>1810703.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>16564579.0</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>6786190.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>17000.0</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>123000.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>-106000.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>987073.0</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>7667263.0</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -9737,320 +9737,320 @@
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>230</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>97.62</t>
+          <t>68.29</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>77.53</t>
         </is>
       </c>
       <c r="CK10" t="n">
-        <v>2.95</v>
+        <v>-0.24</v>
       </c>
       <c r="CL10" t="n">
-        <v>-1.6</v>
+        <v>-0.72</v>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>58.38</t>
+          <t>58.94</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>58.76000000000001</t>
+          <t>58.65</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>59.33</t>
+          <t>59.37</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>56.42</t>
+          <t>56.34</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
+          <t>60.63</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>0.00959232613908867</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>-0.001872021783526301</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>0.0006741951795043999</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>-0.001240804750509583</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>-0.00269345039219504</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>-26.77</t>
+        </is>
+      </c>
+      <c r="DB10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>-91.19</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>7376104763.473171</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>1593900291.0</t>
+        </is>
+      </c>
+      <c r="DI10" t="n">
+        <v>1361980793.6</v>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>1001949471.9</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>1677857345.333333</t>
+        </is>
+      </c>
+      <c r="DL10" t="n">
+        <v>1586577483.32</v>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>2988357275.8875</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>-127440138.7567534</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>-55287702.52412391</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>1593900291.0</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DR10" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT10" t="inlineStr">
+        <is>
+          <t>-3.13</t>
+        </is>
+      </c>
+      <c r="DU10" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV10" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>69.53</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
+          <t>23.33%</t>
+        </is>
+      </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
+          <t>12.64%</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>71.29</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
+          <t>173902</t>
+        </is>
+      </c>
+      <c r="EM10" t="inlineStr">
+        <is>
+          <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN10" t="inlineStr">
+        <is>
+          <t>台玻-玻璃陶瓷-上市</t>
+        </is>
+      </c>
+      <c r="EO10" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷平上市</t>
+        </is>
+      </c>
+      <c r="EP10" t="inlineStr">
+        <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="CT10" t="inlineStr">
-        <is>
-          <t>51.46979166666667</t>
-        </is>
-      </c>
-      <c r="CU10" t="inlineStr">
-        <is>
-          <t>0.007941988950276091</t>
-        </is>
-      </c>
-      <c r="CV10" t="inlineStr">
-        <is>
-          <t>-0.001020061203672262</t>
-        </is>
-      </c>
-      <c r="CW10" t="inlineStr">
-        <is>
-          <t>0.00270407300997122</t>
-        </is>
-      </c>
-      <c r="CX10" t="inlineStr">
-        <is>
-          <t>-0.001451404499353992</t>
-        </is>
-      </c>
-      <c r="CY10" t="inlineStr">
-        <is>
-          <t>-0.002113275679890059</t>
-        </is>
-      </c>
-      <c r="CZ10" t="inlineStr">
-        <is>
-          <t>0.002772230610621262</t>
-        </is>
-      </c>
-      <c r="DA10" t="inlineStr">
-        <is>
-          <t>-24.84</t>
-        </is>
-      </c>
-      <c r="DB10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DD10" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="DE10" t="inlineStr">
-        <is>
-          <t>-90.71</t>
-        </is>
-      </c>
-      <c r="DF10" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="DG10" t="inlineStr">
-        <is>
-          <t>5648900594.207143</t>
-        </is>
-      </c>
-      <c r="DH10" t="inlineStr">
-        <is>
-          <t>1169464009.0</t>
-        </is>
-      </c>
-      <c r="DI10" t="n">
-        <v>1156657216.4</v>
-      </c>
-      <c r="DJ10" t="inlineStr">
-        <is>
-          <t>949368671.7</t>
-        </is>
-      </c>
-      <c r="DK10" t="inlineStr">
-        <is>
-          <t>1674339770.233333</t>
-        </is>
-      </c>
-      <c r="DL10" t="n">
-        <v>1613873208.76</v>
-      </c>
-      <c r="DM10" t="inlineStr">
-        <is>
-          <t>3038222859.6875</t>
-        </is>
-      </c>
-      <c r="DN10" t="inlineStr">
-        <is>
-          <t>-140558763.4721003</t>
-        </is>
-      </c>
-      <c r="DO10" t="inlineStr">
-        <is>
-          <t>-95642474.24883413</t>
-        </is>
-      </c>
-      <c r="DP10" t="inlineStr">
-        <is>
-          <t>1169464009.0</t>
-        </is>
-      </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR10" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="DS10" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT10" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="DU10" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV10" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW10" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY10" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="DZ10" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA10" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB10" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED10" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE10" t="inlineStr">
-        <is>
-          <t>3.38</t>
-        </is>
-      </c>
-      <c r="EF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="EG10" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="EH10" t="inlineStr">
-        <is>
-          <t>68.95</t>
-        </is>
-      </c>
-      <c r="EI10" t="inlineStr">
-        <is>
-          <t>23.33%</t>
-        </is>
-      </c>
-      <c r="EJ10" t="inlineStr">
-        <is>
-          <t>12.64%</t>
-        </is>
-      </c>
-      <c r="EK10" t="inlineStr">
-        <is>
-          <t>73.12</t>
-        </is>
-      </c>
-      <c r="EL10" t="inlineStr">
-        <is>
-          <t>172448</t>
-        </is>
-      </c>
-      <c r="EM10" t="inlineStr">
-        <is>
-          <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN10" t="inlineStr">
-        <is>
-          <t>台玻-玻璃陶瓷-上市</t>
-        </is>
-      </c>
-      <c r="EO10" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷右上上市</t>
-        </is>
-      </c>
-      <c r="EP10" t="inlineStr">
-        <is>
-          <t>59.3</t>
-        </is>
-      </c>
       <c r="EQ10" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="ER10" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="ES10" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="ET10" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU10" t="inlineStr">
@@ -10070,67 +10070,67 @@
       </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="FA10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EZ10" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="FA10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK10" t="inlineStr">

--- a/Result/checksun_type/玻璃.xlsx
+++ b/Result/checksun_type/玻璃.xlsx
@@ -1433,7 +1433,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【b1】;【v】測試條件</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23901.898</t>
+          <t>108469.283</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.11903274433361645</t>
+          <t>0.40024406754507963</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1488,229 +1488,229 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>30.0</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>弱勢整理</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : True</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>59.15</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>62.8784115426783</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>55.4215884573217</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.1260663243509147</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.004244482173174857</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.0280821893407488</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.6421274212056256</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.3172205465981546</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>1.342500795257151</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 20&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>61.16088012671542</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>56.63911987328458</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.0767701231482316</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.0005945808205216618</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0.001183500693124673</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0.01616981328430134</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.3168162812305134</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.8235494318045389</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2026-04-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-08-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
           <t>盤整</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
       <c r="BE2" t="inlineStr">
         <is>
           <t>91.7</t>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>14817876.0</t>
+          <t>26385807.0</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1728,22 +1728,22 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>121000.0</t>
+          <t>20000.0</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-64000.0</t>
+          <t>37000.0</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>1810703.0</t>
+          <t>7734109.0</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>16564579.0</t>
+          <t>34156916.0</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1828,273 +1828,273 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>21.98</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1,174</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>108469</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>79.88</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>0.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.95</v>
+        <v>2.49</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>60.62</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>59.54</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>57.03</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>59.78</t>
+          <t>59.86</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
+          <t>52.76041666666666</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>0.01950891355533146</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>0.009494743981010467</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>0.004244482173174857</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>0.004650589250797088</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>0.001338282189346174</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>0.002688352977974429</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>135.54</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>-92.21</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>5652291899.884943</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>6893350654.0</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>2269813931.6</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>1621013067.8</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>1606583762.933333</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>1631995189.58</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>2571721274.6625</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>-16128718.24692487</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>412587797.9423854</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>6893350654.0</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>0.007455099966113155</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>0.001698369565217073</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>0.0005945808205216618</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>0.003110035164602287</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>-6.272804257134723e-05</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>8.24</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>25.54</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>-94.79</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>7376104763.473171</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>1434343204.0</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>1173445043.8</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>1048624403.3</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>1411256752.533333</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>1509531056.42</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>2523130309.375</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>-94077175.75220172</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>-23283623.53972125</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>1434343204.0</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>-1.48</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG2" t="inlineStr">
         <is>
           <t>4.15</t>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>74.59</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>173902</t>
+          <t>191060</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
@@ -2137,32 +2137,32 @@
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
@@ -2182,42 +2182,42 @@
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
@@ -2227,22 +2227,22 @@
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23093.784</t>
+          <t>23901.898</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2454,17 +2454,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.11135316584249741</t>
+          <t>0.11903274433361645</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2524,47 +2524,47 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>58.86499999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>61.08858174787481</t>
+          <t>61.1608801267131</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>56.64141825212518</t>
+          <t>56.63911987328689</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.07554851772274902</t>
+          <t>0.07677012314815294</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.000594934557198723</t>
+          <t>0.0005945808205214398</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0006847801378484508</t>
+          <t>0.001183500693125117</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.002472742767793745</t>
+          <t>0.01616981328433842</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.3168162812305134</t>
+          <t>0.3172205465981546</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.7911038446560315</t>
+          <t>0.8235494318042734</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2026-04-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2604,147 +2604,147 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-08-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AP3" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>26385807.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>57000.0</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>20000.0</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>37000.0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>7734109.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>34156916.0</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>14817876.0</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>57000.0</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>121000.0</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>-64000.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>1810703.0</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>16564579.0</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -2814,17 +2814,17 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -2835,58 +2835,58 @@
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1,174</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>108469</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>79.88</t>
         </is>
       </c>
       <c r="CK3" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.26</v>
+        <v>0.95</v>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>59.46</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>58.88000000000001</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>58.86</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>56.59</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -2896,259 +2896,259 @@
       </c>
       <c r="CT3" t="inlineStr">
         <is>
+          <t>52.61895833333334</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>0.007455099966113155</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>0.001698369565217073</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>0.0005945808205214398</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>0.003110035164602287</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>-6.272804257134723e-05</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>0.002234056061712453</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>25.54</t>
+        </is>
+      </c>
+      <c r="DB3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>-94.85</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>5652291899.884943</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>1434343204.0</t>
+        </is>
+      </c>
+      <c r="DI3" t="n">
+        <v>1173445043.8</v>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>1048624403.3</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>1411256752.533333</t>
+        </is>
+      </c>
+      <c r="DL3" t="n">
+        <v>1509531056.42</v>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>2523130309.375</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>-94077175.73589039</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>-23283623.53622055</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>1434343204.0</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU3" t="inlineStr">
-        <is>
-          <t>0.003059143439837042</t>
-        </is>
-      </c>
-      <c r="CV3" t="inlineStr">
-        <is>
-          <t>0.001360544217687387</t>
-        </is>
-      </c>
-      <c r="CW3" t="inlineStr">
-        <is>
-          <t>0.000594934557198723</t>
-        </is>
-      </c>
-      <c r="CX3" t="inlineStr">
-        <is>
-          <t>0.001770193482147464</t>
-        </is>
-      </c>
-      <c r="CY3" t="inlineStr">
-        <is>
-          <t>-0.0007730477931574553</t>
-        </is>
-      </c>
-      <c r="CZ3" t="inlineStr">
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="DA3" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="DB3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DD3" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE3" t="inlineStr">
-        <is>
-          <t>-95.12</t>
-        </is>
-      </c>
-      <c r="DF3" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="DG3" t="inlineStr">
-        <is>
-          <t>7376104763.473171</t>
-        </is>
-      </c>
-      <c r="DH3" t="inlineStr">
-        <is>
-          <t>1391651459.0</t>
-        </is>
-      </c>
-      <c r="DI3" t="n">
-        <v>978592810.6</v>
-      </c>
-      <c r="DJ3" t="inlineStr">
-        <is>
-          <t>1101216786.0</t>
-        </is>
-      </c>
-      <c r="DK3" t="inlineStr">
-        <is>
-          <t>1410351796.1</t>
-        </is>
-      </c>
-      <c r="DL3" t="n">
-        <v>1501930217.1</v>
-      </c>
-      <c r="DM3" t="inlineStr">
-        <is>
-          <t>2534452706.925</t>
-        </is>
-      </c>
-      <c r="DN3" t="inlineStr">
-        <is>
-          <t>-106948730.6999255</t>
-        </is>
-      </c>
-      <c r="DO3" t="inlineStr">
-        <is>
-          <t>-60231869.45479345</t>
-        </is>
-      </c>
-      <c r="DP3" t="inlineStr">
-        <is>
-          <t>1391651459.0</t>
-        </is>
-      </c>
-      <c r="DQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR3" t="inlineStr">
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>23.33%</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>12.64%</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>74.59</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>191060</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>台玻-玻璃陶瓷-上市</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷右上上市</t>
+        </is>
+      </c>
+      <c r="EP3" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
         <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="DS3" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT3" t="inlineStr">
-        <is>
-          <t>-2.31</t>
-        </is>
-      </c>
-      <c r="DU3" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV3" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW3" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY3" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="DZ3" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA3" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB3" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE3" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
-      <c r="EF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="EG3" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="EH3" t="inlineStr">
-        <is>
-          <t>69.53</t>
-        </is>
-      </c>
-      <c r="EI3" t="inlineStr">
-        <is>
-          <t>23.33%</t>
-        </is>
-      </c>
-      <c r="EJ3" t="inlineStr">
-        <is>
-          <t>12.64%</t>
-        </is>
-      </c>
-      <c r="EK3" t="inlineStr">
-        <is>
-          <t>71.29</t>
-        </is>
-      </c>
-      <c r="EL3" t="inlineStr">
-        <is>
-          <t>173902</t>
-        </is>
-      </c>
-      <c r="EM3" t="inlineStr">
-        <is>
-          <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN3" t="inlineStr">
-        <is>
-          <t>台玻-玻璃陶瓷-上市</t>
-        </is>
-      </c>
-      <c r="EO3" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="EP3" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="EQ3" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
       <c r="ER3" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
@@ -3168,42 +3168,42 @@
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF3" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12062.573</t>
+          <t>23093.784</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.28003130372797114</t>
+          <t>-0.11135316584249741</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -3495,62 +3495,62 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>空頭</t>
+          <t>弱勢整理</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 20&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.86500000000001</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>61.04677812673398</t>
+          <t>61.08858174787246</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>56.61322187326602</t>
+          <t>56.64141825212756</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.07536216647064348</t>
+          <t>0.07554851772266885</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.001103659054249029</t>
+          <t>0.0005949345571989451</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.003568597122044825</t>
+          <t>0.0006847801378488949</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.06377897240356267</t>
+          <t>0.002472742767799962</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.3168162812305134</t>
+          <t>0.3172205465981546</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.7611408795638696</t>
+          <t>0.7911038446557226</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2026-04-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-08-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AQ4" t="inlineStr">
         <is>
           <t>False</t>
@@ -3645,22 +3645,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>14817876.0</t>
+          <t>26385807.0</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -3700,22 +3700,22 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>121000.0</t>
+          <t>20000.0</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-64000.0</t>
+          <t>37000.0</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>1810703.0</t>
+          <t>7734109.0</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>16564579.0</t>
+          <t>34156916.0</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -3800,17 +3800,17 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -3821,320 +3821,320 @@
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1,174</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>108469</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CK4" t="n">
-        <v>1.12</v>
+        <v>0.47</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>58.88000000000001</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.87</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.59</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.78</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
+          <t>52.50166666666667</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>0.003059143439837042</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>0.001360544217687387</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>0.0005949345571989451</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>0.001770193482147464</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>-0.0007730477931574553</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>0.002286891537705671</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="DB4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>-95.18</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>5652291899.884943</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>1391651459.0</t>
+        </is>
+      </c>
+      <c r="DI4" t="n">
+        <v>978592810.6</v>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>1101216786.0</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>1410351796.1</t>
+        </is>
+      </c>
+      <c r="DL4" t="n">
+        <v>1501930217.1</v>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>2534452706.925</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>-106948730.6812849</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>-60231869.45079255</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>1391651459.0</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU4" t="inlineStr">
-        <is>
-          <t>0.006500171057133075</t>
-        </is>
-      </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>0.001703577512776722</t>
-        </is>
-      </c>
-      <c r="CW4" t="inlineStr">
-        <is>
-          <t>-0.001103659054249029</t>
-        </is>
-      </c>
-      <c r="CX4" t="inlineStr">
-        <is>
-          <t>0.001382660025171623</t>
-        </is>
-      </c>
-      <c r="CY4" t="inlineStr">
-        <is>
-          <t>-0.0005220569042025947</t>
-        </is>
-      </c>
-      <c r="CZ4" t="inlineStr">
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>-2.31</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="DA4" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
-      <c r="DB4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DD4" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE4" t="inlineStr">
-        <is>
-          <t>-95.21</t>
-        </is>
-      </c>
-      <c r="DF4" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="DG4" t="inlineStr">
-        <is>
-          <t>7376104763.473171</t>
-        </is>
-      </c>
-      <c r="DH4" t="inlineStr">
-        <is>
-          <t>716628303.0</t>
-        </is>
-      </c>
-      <c r="DI4" t="n">
-        <v>793132356.6</v>
-      </c>
-      <c r="DJ4" t="inlineStr">
-        <is>
-          <t>1101620613.1</t>
-        </is>
-      </c>
-      <c r="DK4" t="inlineStr">
-        <is>
-          <t>1512236185.5</t>
-        </is>
-      </c>
-      <c r="DL4" t="n">
-        <v>1491436510.72</v>
-      </c>
-      <c r="DM4" t="inlineStr">
-        <is>
-          <t>2550447434.6375</t>
-        </is>
-      </c>
-      <c r="DN4" t="inlineStr">
-        <is>
-          <t>-115442705.4717676</t>
-        </is>
-      </c>
-      <c r="DO4" t="inlineStr">
-        <is>
-          <t>-106289824.1743681</t>
-        </is>
-      </c>
-      <c r="DP4" t="inlineStr">
-        <is>
-          <t>716628303.0</t>
-        </is>
-      </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR4" t="inlineStr">
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>23.33%</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>12.64%</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>74.59</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>191060</t>
+        </is>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN4" t="inlineStr">
+        <is>
+          <t>台玻-玻璃陶瓷-上市</t>
+        </is>
+      </c>
+      <c r="EO4" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷右上上市</t>
+        </is>
+      </c>
+      <c r="EP4" t="inlineStr">
         <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="DS4" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT4" t="inlineStr">
-        <is>
-          <t>-1.98</t>
-        </is>
-      </c>
-      <c r="DU4" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV4" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW4" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY4" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="DZ4" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA4" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB4" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED4" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="EE4" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="EF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="EG4" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="EH4" t="inlineStr">
-        <is>
-          <t>69.53</t>
-        </is>
-      </c>
-      <c r="EI4" t="inlineStr">
-        <is>
-          <t>23.33%</t>
-        </is>
-      </c>
-      <c r="EJ4" t="inlineStr">
-        <is>
-          <t>12.64%</t>
-        </is>
-      </c>
-      <c r="EK4" t="inlineStr">
-        <is>
-          <t>71.29</t>
-        </is>
-      </c>
-      <c r="EL4" t="inlineStr">
-        <is>
-          <t>173902</t>
-        </is>
-      </c>
-      <c r="EM4" t="inlineStr">
-        <is>
-          <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN4" t="inlineStr">
-        <is>
-          <t>台玻-玻璃陶瓷-上市</t>
-        </is>
-      </c>
-      <c r="EO4" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="EP4" t="inlineStr">
-        <is>
-          <t>58.8</t>
-        </is>
-      </c>
       <c r="EQ4" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="ER4" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="ES4" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="ET4" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU4" t="inlineStr">
@@ -4154,42 +4154,42 @@
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="EZ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FA4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF4" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15496.264</t>
+          <t>12062.573</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4426,17 +4426,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.23927286091689726</t>
+          <t>-0.28003130372797114</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -4496,47 +4496,47 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>58.895</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>61.26540969143974</t>
+          <t>61.04677812673161</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>56.52459030856025</t>
+          <t>56.61322187326839</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.08049612671499268</t>
+          <t>0.07536216647056303</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.00211792612673678</t>
+          <t>-0.001103659054249029</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.005781894342764105</t>
+          <t>-0.00356859712204749</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.08696589266449983</t>
+          <t>-0.06377897240368935</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.3168162812305134</t>
+          <t>0.3172205465981546</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.7815573182265803</t>
+          <t>0.7611408795635349</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2026-04-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -4576,147 +4576,147 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-08-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AP5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>26385807.0</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>57000.0</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>20000.0</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>37000.0</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>7734109.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>34156916.0</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>14817876.0</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>57000.0</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>121000.0</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>-64000.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>1810703.0</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>16564579.0</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -4786,140 +4786,140 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1,174</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>108469</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CK5" t="n">
-        <v>0.58</v>
+        <v>1.12</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.74</v>
+        <v>0.02</v>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>56.41</t>
+          <t>56.49</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>59.86</t>
+          <t>59.83</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52.38187500000001</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>2.220446049250313e-16</t>
+          <t>0.006500171057133075</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>0.004792879150975704</t>
+          <t>0.001703577512776722</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>-0.00211792612673678</t>
+          <t>-0.001103659054249029</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>0.001669063726273734</t>
+          <t>0.001382660025171623</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>-0.001834269575095582</t>
+          <t>-0.0005220569042025947</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.002527920765234448</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>-29.02</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="DB5" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="DC5" t="n">
         <v>0.2</v>
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>-95.18</t>
+          <t>-95.26</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
@@ -4929,48 +4929,48 @@
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>7376104763.473171</t>
+          <t>5652291899.884943</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>913096038.0</t>
+          <t>716628303.0</t>
         </is>
       </c>
       <c r="DI5" t="n">
-        <v>836051353.4</v>
+        <v>793132356.6</v>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>1099016073.5</t>
+          <t>1101620613.1</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>1537638652.2</t>
+          <t>1512236185.5</t>
         </is>
       </c>
       <c r="DL5" t="n">
-        <v>1496862031.52</v>
+        <v>1491436510.72</v>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>2578499982.6</t>
+          <t>2550447434.6375</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>-117106865.7076584</t>
+          <t>-115442705.4504653</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>-95966927.62467611</t>
+          <t>-106289824.1697955</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>913096038.0</t>
+          <t>716628303.0</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
@@ -5035,17 +5035,17 @@
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>74.59</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>173902</t>
+          <t>191060</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
@@ -5095,32 +5095,32 @@
       </c>
       <c r="EO5" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
@@ -5140,42 +5140,42 @@
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FA5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF5" t="inlineStr">
@@ -5185,22 +5185,22 @@
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK5" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23784.387</t>
+          <t>15496.264</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5412,17 +5412,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.08663988999632684</t>
+          <t>-0.23927286091689726</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -5482,47 +5482,47 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>58.895</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>61.62169984918928</t>
+          <t>61.26540969143753</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>56.41830015081073</t>
+          <t>56.52459030856246</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.08816332935239829</t>
+          <t>0.08049612671491764</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.0007618725133327064</t>
+          <t>-0.002117926126736669</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.002243184610895566</t>
+          <t>-0.005781894342767324</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.03396950249456443</t>
+          <t>-0.08696589266464283</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.3168162812305134</t>
+          <t>0.3172205465981546</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.8245796448191481</t>
+          <t>0.7815573182263081</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2026-04-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -5562,82 +5562,82 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-08-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>14817876.0</t>
+          <t>26385807.0</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -5672,22 +5672,22 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>121000.0</t>
+          <t>20000.0</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-64000.0</t>
+          <t>37000.0</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>1810703.0</t>
+          <t>7734109.0</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>16564579.0</t>
+          <t>34156916.0</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -5772,17 +5772,17 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -5793,119 +5793,119 @@
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1,174</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>108469</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="CK6" t="n">
-        <v>2.46</v>
+        <v>0.58</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.95</v>
+        <v>-0.74</v>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>58.45999999999999</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>56.32</t>
+          <t>56.41</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>59.97</t>
+          <t>59.86</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52.24979166666667</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>-0.0006837606837607479</t>
+          <t>2.220446049250313e-16</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>0.003607627555402892</t>
+          <t>0.004792879150975704</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>-0.0007618725133327064</t>
+          <t>-0.002117926126736669</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>0.002349297880292589</t>
+          <t>0.001669063726273734</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>-0.001872444892906611</t>
+          <t>-0.001834269575095582</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.002534327343953091</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>-33.32</t>
+          <t>-29.02</t>
         </is>
       </c>
       <c r="DB6" t="n">
         <v>0.15</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="DE6" t="inlineStr">
         <is>
-          <t>-94.83</t>
+          <t>-95.24</t>
         </is>
       </c>
       <c r="DF6" t="inlineStr">
@@ -5915,48 +5915,48 @@
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>7376104763.473171</t>
+          <t>5652291899.884943</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>1411506215.0</t>
+          <t>913096038.0</t>
         </is>
       </c>
       <c r="DI6" t="n">
-        <v>972212204</v>
+        <v>836051353.4</v>
       </c>
       <c r="DJ6" t="inlineStr">
         <is>
-          <t>1064434710.2</t>
+          <t>1099016073.5</t>
         </is>
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>1565951673.033333</t>
+          <t>1537638652.2</t>
         </is>
       </c>
       <c r="DL6" t="n">
-        <v>1495033587.44</v>
+        <v>1496862031.52</v>
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>2612782440.9375</t>
+          <t>2578499982.6</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>-120950490.8136552</t>
+          <t>-117106865.6833144</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>-98842656.74566317</t>
+          <t>-95966927.61945021</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
         <is>
-          <t>1411506215.0</t>
+          <t>913096038.0</t>
         </is>
       </c>
       <c r="DQ6" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
@@ -6021,17 +6021,17 @@
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>74.59</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>173902</t>
+          <t>191060</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="EO6" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="ES6" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU6" t="inlineStr">
@@ -6126,42 +6126,42 @@
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FA6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF6" t="inlineStr">
@@ -6171,22 +6171,22 @@
       </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK6" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7975.945</t>
+          <t>23784.387</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>59.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6398,17 +6398,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.06753878030510366</t>
+          <t>-0.08663988999632684</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6418,277 +6418,277 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>59.02</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>61.62169984918725</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>56.41830015081274</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.08816332935232991</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>-0.0007618725133330395</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-0.00224318461089712</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.03396950249461561</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.3172205465981546</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.8245796448189587</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>59.065</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>61.76023946792896</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>56.36976053207103</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.09126350522065399</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>-0.002701561840439015</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-0.002804803302640768</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.00236677235579652</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.3168162812305134</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0.8234794118947475</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>2026-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>26385807.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>57000.0</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>20000.0</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>37000.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>7734109.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>34156916.0</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>14817876.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>57000.0</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>121000.0</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>-64000.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>1810703.0</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>16564579.0</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -6758,17 +6758,17 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -6779,252 +6779,252 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1,174</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>108469</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="CK7" t="n">
-        <v>-1.54</v>
+        <v>2.46</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.96</v>
+        <v>-0.95</v>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.45999999999999</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>58.21</t>
+          <t>58.42</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.32</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>59.97</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
+          <t>52.11770833333333</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>-0.0006837606837607479</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>0.003607627555402892</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>-0.0007618725133330395</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>0.002349297880292589</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>-0.001872444892906611</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>0.00256085538180395</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>-33.32</t>
+        </is>
+      </c>
+      <c r="DB7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DD7" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>-94.89</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>5652291899.884943</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>1411506215.0</t>
+        </is>
+      </c>
+      <c r="DI7" t="n">
+        <v>972212204</v>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>1064434710.2</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>1565951673.033333</t>
+        </is>
+      </c>
+      <c r="DL7" t="n">
+        <v>1495033587.44</v>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>2612782440.9375</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>-120950490.7858351</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>-98842656.73969078</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>1411506215.0</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU7" t="inlineStr">
-        <is>
-          <t>-0.004085801838610736</t>
-        </is>
-      </c>
-      <c r="CV7" t="inlineStr">
-        <is>
-          <t>-0.001029689377037957</t>
-        </is>
-      </c>
-      <c r="CW7" t="inlineStr">
-        <is>
-          <t>-0.002701561840439015</t>
-        </is>
-      </c>
-      <c r="CX7" t="inlineStr">
-        <is>
-          <t>0.0003560809728131442</t>
-        </is>
-      </c>
-      <c r="CY7" t="inlineStr">
-        <is>
-          <t>-0.002945599751076</t>
-        </is>
-      </c>
-      <c r="CZ7" t="inlineStr">
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>-1.32</t>
+        </is>
+      </c>
+      <c r="DU7" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV7" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="EE7" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EF7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="DA7" t="inlineStr">
-        <is>
-          <t>-85.80</t>
-        </is>
-      </c>
-      <c r="DB7" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="DD7" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE7" t="inlineStr">
-        <is>
-          <t>-94.40</t>
-        </is>
-      </c>
-      <c r="DF7" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="DG7" t="inlineStr">
-        <is>
-          <t>7376104763.473171</t>
-        </is>
-      </c>
-      <c r="DH7" t="inlineStr">
-        <is>
-          <t>460082038.0</t>
-        </is>
-      </c>
-      <c r="DI7" t="n">
-        <v>923803762.8</v>
-      </c>
-      <c r="DJ7" t="inlineStr">
-        <is>
-          <t>990715477.8</t>
-        </is>
-      </c>
-      <c r="DK7" t="inlineStr">
-        <is>
-          <t>1577592671.866667</t>
-        </is>
-      </c>
-      <c r="DL7" t="n">
-        <v>1503106536.6</v>
-      </c>
-      <c r="DM7" t="inlineStr">
-        <is>
-          <t>2650980248.8625</t>
-        </is>
-      </c>
-      <c r="DN7" t="inlineStr">
-        <is>
-          <t>-124970097.0078356</t>
-        </is>
-      </c>
-      <c r="DO7" t="inlineStr">
-        <is>
-          <t>-152821836.7132996</t>
-        </is>
-      </c>
-      <c r="DP7" t="inlineStr">
-        <is>
-          <t>460082038.0</t>
-        </is>
-      </c>
-      <c r="DQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR7" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="DS7" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT7" t="inlineStr">
-        <is>
-          <t>-5.11</t>
-        </is>
-      </c>
-      <c r="DU7" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV7" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW7" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY7" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="DZ7" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA7" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB7" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE7" t="inlineStr">
-        <is>
-          <t>3.24</t>
-        </is>
-      </c>
-      <c r="EF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG7" t="inlineStr">
         <is>
           <t>4.15</t>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>74.59</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>173902</t>
+          <t>191060</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
@@ -7067,32 +7067,32 @@
       </c>
       <c r="EO7" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="ES7" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>59.9</t>
         </is>
       </c>
       <c r="ET7" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU7" t="inlineStr">
@@ -7112,42 +7112,42 @@
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FA7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF7" t="inlineStr">
@@ -7157,22 +7157,22 @@
       </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK7" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8054.096</t>
+          <t>7975.945</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7384,17 +7384,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.20773173479608792</t>
+          <t>-0.06753878030510366</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -7454,47 +7454,47 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>59.225</t>
+          <t>59.06500000000001</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>61.93395202110334</t>
+          <t>61.76023946792703</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>56.51604797889666</t>
+          <t>56.36976053207299</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.09148001759741133</t>
+          <t>0.09126350522058804</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.0006749346157091107</t>
+          <t>-0.002701561840438793</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.0001967952176192833</t>
+          <t>-0.002804803302640657</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0110545758825138</t>
+          <t>-0.002366772355803071</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.3168162812305134</t>
+          <t>0.3172205465981546</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.7820832597155659</t>
+          <t>0.8234794118945751</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2026-04-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -7534,147 +7534,147 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-08-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>26385807.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>57000.0</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>20000.0</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>37000.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>7734109.0</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>34156916.0</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>14817876.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>57000.0</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>121000.0</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>-64000.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>1810703.0</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>16564579.0</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -7744,17 +7744,17 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -7765,252 +7765,252 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1,174</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>108469</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>55.28</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="CK8" t="n">
-        <v>-0.58</v>
+        <v>-1.54</v>
       </c>
       <c r="CL8" t="n">
-        <v>-0.82</v>
+        <v>-0.96</v>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>58.73999999999999</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>58.27</t>
+          <t>58.21</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.07</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>56.17</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
+          <t>51.98458333333333</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>-0.004085801838610736</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>-0.001029689377037957</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>-0.002701561840438793</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>0.0003560809728131442</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>-0.002945599751076</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>0.002426462908059479</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>-85.80</t>
+        </is>
+      </c>
+      <c r="DB8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>-94.46</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>5652291899.884943</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>460082038.0</t>
+        </is>
+      </c>
+      <c r="DI8" t="n">
+        <v>923803762.8</v>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>990715477.8</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>1577592671.866667</t>
+        </is>
+      </c>
+      <c r="DL8" t="n">
+        <v>1503106536.6</v>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>2650980248.8625</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>-124970096.9760432</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>-152821836.7064742</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>460082038.0</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU8" t="inlineStr">
-        <is>
-          <t>-0.0003403675970049536</t>
-        </is>
-      </c>
-      <c r="CV8" t="inlineStr">
-        <is>
-          <t>-0.00205514642918303</t>
-        </is>
-      </c>
-      <c r="CW8" t="inlineStr">
-        <is>
-          <t>-0.0006749346157091107</t>
-        </is>
-      </c>
-      <c r="CX8" t="inlineStr">
-        <is>
-          <t>-0.001173688047943156</t>
-        </is>
-      </c>
-      <c r="CY8" t="inlineStr">
-        <is>
-          <t>-0.00260688756245675</t>
-        </is>
-      </c>
-      <c r="CZ8" t="inlineStr">
+      <c r="DR8" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>-5.11</t>
+        </is>
+      </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="DA8" t="inlineStr">
-        <is>
-          <t>-57.25</t>
-        </is>
-      </c>
-      <c r="DB8" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="DD8" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE8" t="inlineStr">
-        <is>
-          <t>-93.19</t>
-        </is>
-      </c>
-      <c r="DF8" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="DG8" t="inlineStr">
-        <is>
-          <t>7376104763.473171</t>
-        </is>
-      </c>
-      <c r="DH8" t="inlineStr">
-        <is>
-          <t>464349189.0</t>
-        </is>
-      </c>
-      <c r="DI8" t="n">
-        <v>1223840761.4</v>
-      </c>
-      <c r="DJ8" t="inlineStr">
-        <is>
-          <t>1013338249.0</t>
-        </is>
-      </c>
-      <c r="DK8" t="inlineStr">
-        <is>
-          <t>1611987982.833333</t>
-        </is>
-      </c>
-      <c r="DL8" t="n">
-        <v>1533541700.16</v>
-      </c>
-      <c r="DM8" t="inlineStr">
-        <is>
-          <t>2698659312.1</t>
-        </is>
-      </c>
-      <c r="DN8" t="inlineStr">
-        <is>
-          <t>-119906144.3341149</t>
-        </is>
-      </c>
-      <c r="DO8" t="inlineStr">
-        <is>
-          <t>-122538723.5344481</t>
-        </is>
-      </c>
-      <c r="DP8" t="inlineStr">
-        <is>
-          <t>464349189.0</t>
-        </is>
-      </c>
-      <c r="DQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR8" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="DS8" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT8" t="inlineStr">
-        <is>
-          <t>-3.79</t>
-        </is>
-      </c>
-      <c r="DU8" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV8" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW8" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY8" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="DZ8" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA8" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB8" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED8" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="EE8" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
-      <c r="EF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG8" t="inlineStr">
         <is>
           <t>4.15</t>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>74.59</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>173902</t>
+          <t>191060</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
@@ -8053,12 +8053,12 @@
       </c>
       <c r="EO8" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP8" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="EQ8" t="inlineStr">
@@ -8068,17 +8068,17 @@
       </c>
       <c r="ER8" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="ES8" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="ET8" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU8" t="inlineStr">
@@ -8098,42 +8098,42 @@
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FA8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF8" t="inlineStr">
@@ -8143,22 +8143,22 @@
       </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK8" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16045.294</t>
+          <t>8054.096</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8370,17 +8370,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.37788535417800007</t>
+          <t>0.20773173479608792</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -8440,47 +8440,47 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>59.265</t>
+          <t>59.225</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>61.94614272574173</t>
+          <t>61.9339520211014</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>56.58385727425827</t>
+          <t>56.5160479788986</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.09047980176298757</t>
+          <t>0.09148001759734582</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.001768569984840873</t>
+          <t>-0.0006749346157092218</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.0001198607285648468</t>
+          <t>-0.0001967952176190613</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.04561581977771101</t>
+          <t>0.01105457588252956</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.3168162812305134</t>
+          <t>0.3172205465981546</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.720560497795359</t>
+          <t>0.7820832597153745</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2026-04-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-08-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -8535,64 +8535,64 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
       <c r="BA9" t="inlineStr">
         <is>
           <t>12.0</t>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>14817876.0</t>
+          <t>26385807.0</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -8630,22 +8630,22 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>121000.0</t>
+          <t>20000.0</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-64000.0</t>
+          <t>37000.0</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>1810703.0</t>
+          <t>7734109.0</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>16564579.0</t>
+          <t>34156916.0</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -8730,17 +8730,17 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -8751,252 +8751,252 @@
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1,174</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>108469</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>68.31</t>
+          <t>55.28</t>
         </is>
       </c>
       <c r="CK9" t="n">
-        <v>-1.97</v>
+        <v>-0.58</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0.85</v>
+        <v>-0.82</v>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>58.76000000000001</t>
+          <t>58.73999999999999</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>58.39</t>
+          <t>58.27</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>56.23</t>
+          <t>56.17</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
+          <t>51.85875</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>-0.0003403675970049536</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>-0.00205514642918303</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>-0.0006749346157092218</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>-0.001173688047943156</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>-0.00260688756245675</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>0.002597904759603198</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>-57.25</t>
+        </is>
+      </c>
+      <c r="DB9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>-93.28</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>5652291899.884943</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>464349189.0</t>
+        </is>
+      </c>
+      <c r="DI9" t="n">
+        <v>1223840761.4</v>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>1013338249.0</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>1611987982.833333</t>
+        </is>
+      </c>
+      <c r="DL9" t="n">
+        <v>1533541700.16</v>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>2698659312.1</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>-119906144.297783</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>-122538723.5266478</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>464349189.0</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU9" t="inlineStr">
-        <is>
-          <t>-0.003053953172717838</t>
-        </is>
-      </c>
-      <c r="CV9" t="inlineStr">
-        <is>
-          <t>-0.00443307757885758</t>
-        </is>
-      </c>
-      <c r="CW9" t="inlineStr">
-        <is>
-          <t>-0.001768569984840873</t>
-        </is>
-      </c>
-      <c r="CX9" t="inlineStr">
-        <is>
-          <t>-0.001987754015440713</t>
-        </is>
-      </c>
-      <c r="CY9" t="inlineStr">
-        <is>
-          <t>-0.003545989630041935</t>
-        </is>
-      </c>
-      <c r="CZ9" t="inlineStr">
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>-3.79</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="DA9" t="inlineStr">
-        <is>
-          <t>-53.11</t>
-        </is>
-      </c>
-      <c r="DB9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DD9" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE9" t="inlineStr">
-        <is>
-          <t>-92.22</t>
-        </is>
-      </c>
-      <c r="DF9" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="DG9" t="inlineStr">
-        <is>
-          <t>7376104763.473171</t>
-        </is>
-      </c>
-      <c r="DH9" t="inlineStr">
-        <is>
-          <t>931223287.0</t>
-        </is>
-      </c>
-      <c r="DI9" t="n">
-        <v>1410108869.6</v>
-      </c>
-      <c r="DJ9" t="inlineStr">
-        <is>
-          <t>1023386209.4</t>
-        </is>
-      </c>
-      <c r="DK9" t="inlineStr">
-        <is>
-          <t>1634858488.1</t>
-        </is>
-      </c>
-      <c r="DL9" t="n">
-        <v>1559387232.3</v>
-      </c>
-      <c r="DM9" t="inlineStr">
-        <is>
-          <t>2830262055.8375</t>
-        </is>
-      </c>
-      <c r="DN9" t="inlineStr">
-        <is>
-          <t>-119427493.5704179</t>
-        </is>
-      </c>
-      <c r="DO9" t="inlineStr">
-        <is>
-          <t>-75357945.045573</t>
-        </is>
-      </c>
-      <c r="DP9" t="inlineStr">
-        <is>
-          <t>931223287.0</t>
-        </is>
-      </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR9" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="DS9" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT9" t="inlineStr">
-        <is>
-          <t>-5.11</t>
-        </is>
-      </c>
-      <c r="DU9" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV9" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW9" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY9" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="DZ9" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA9" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB9" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE9" t="inlineStr">
-        <is>
-          <t>3.24</t>
-        </is>
-      </c>
-      <c r="EF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG9" t="inlineStr">
         <is>
           <t>4.15</t>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>74.59</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>173902</t>
+          <t>191060</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
@@ -9039,32 +9039,32 @@
       </c>
       <c r="EO9" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP9" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="EQ9" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="ER9" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="ES9" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="ET9" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU9" t="inlineStr">
@@ -9084,42 +9084,42 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF9" t="inlineStr">
@@ -9129,22 +9129,22 @@
       </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK9" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26413.098</t>
+          <t>16045.294</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9356,17 +9356,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.35933081637068126</t>
+          <t>0.37788535417800007</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -9426,47 +9426,47 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.26500000000001</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>61.93871870579128</t>
+          <t>61.94614272573978</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>56.80128129420873</t>
+          <t>56.58385727426024</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.08653254862022154</t>
+          <t>0.09047980176292138</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.0006741951795043999</t>
+          <t>-0.00176856998484054</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.0003478106572433193</t>
+          <t>0.0001198607285666231</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.02405878993879684</t>
+          <t>0.04561581977777873</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.3168162812305134</t>
+          <t>0.3172205465981546</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.628287038417389</t>
+          <t>0.7205604977951365</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2026-04-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -9506,147 +9506,147 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-08-14 00:00:00</t>
+          <t>2026-10-07 00:00:00</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>26385807.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>57000.0</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>20000.0</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>37000.0</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>7734109.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>34156916.0</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>14817876.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>57000.0</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>121000.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>-64000.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>1810703.0</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>16564579.0</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -9737,252 +9737,252 @@
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1,174</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>108469</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>68.29</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>77.53</t>
+          <t>68.31</t>
         </is>
       </c>
       <c r="CK10" t="n">
-        <v>-0.24</v>
+        <v>-1.97</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0.72</v>
+        <v>-0.85</v>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>58.94</t>
+          <t>58.76000000000001</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>58.65</t>
+          <t>58.39</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.27</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>56.23</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>60.42</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
+          <t>51.724375</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>-0.003053953172717838</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>-0.00443307757885758</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>-0.00176856998484054</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>-0.001987754015440713</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>-0.003545989630041935</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>0.002333477325302091</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>-53.11</t>
+        </is>
+      </c>
+      <c r="DB10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>-92.32</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>5652291899.884943</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>931223287.0</t>
+        </is>
+      </c>
+      <c r="DI10" t="n">
+        <v>1410108869.6</v>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>1023386209.4</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>1634858488.1</t>
+        </is>
+      </c>
+      <c r="DL10" t="n">
+        <v>1559387232.3</v>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>2830262055.8375</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>-119427493.5288985</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>-75357945.03665853</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>931223287.0</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU10" t="inlineStr">
-        <is>
-          <t>0.00959232613908867</t>
-        </is>
-      </c>
-      <c r="CV10" t="inlineStr">
-        <is>
-          <t>-0.001872021783526301</t>
-        </is>
-      </c>
-      <c r="CW10" t="inlineStr">
-        <is>
-          <t>0.0006741951795043999</t>
-        </is>
-      </c>
-      <c r="CX10" t="inlineStr">
-        <is>
-          <t>-0.001240804750509583</t>
-        </is>
-      </c>
-      <c r="CY10" t="inlineStr">
-        <is>
-          <t>-0.00269345039219504</t>
-        </is>
-      </c>
-      <c r="CZ10" t="inlineStr">
+      <c r="DR10" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="DT10" t="inlineStr">
+        <is>
+          <t>-5.11</t>
+        </is>
+      </c>
+      <c r="DU10" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DV10" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>-5.034791190033646</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>6.457567924179223</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>6.363949904140926</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="DA10" t="inlineStr">
-        <is>
-          <t>-26.77</t>
-        </is>
-      </c>
-      <c r="DB10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="DD10" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="DE10" t="inlineStr">
-        <is>
-          <t>-91.19</t>
-        </is>
-      </c>
-      <c r="DF10" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="DG10" t="inlineStr">
-        <is>
-          <t>7376104763.473171</t>
-        </is>
-      </c>
-      <c r="DH10" t="inlineStr">
-        <is>
-          <t>1593900291.0</t>
-        </is>
-      </c>
-      <c r="DI10" t="n">
-        <v>1361980793.6</v>
-      </c>
-      <c r="DJ10" t="inlineStr">
-        <is>
-          <t>1001949471.9</t>
-        </is>
-      </c>
-      <c r="DK10" t="inlineStr">
-        <is>
-          <t>1677857345.333333</t>
-        </is>
-      </c>
-      <c r="DL10" t="n">
-        <v>1586577483.32</v>
-      </c>
-      <c r="DM10" t="inlineStr">
-        <is>
-          <t>2988357275.8875</t>
-        </is>
-      </c>
-      <c r="DN10" t="inlineStr">
-        <is>
-          <t>-127440138.7567534</t>
-        </is>
-      </c>
-      <c r="DO10" t="inlineStr">
-        <is>
-          <t>-55287702.52412391</t>
-        </is>
-      </c>
-      <c r="DP10" t="inlineStr">
-        <is>
-          <t>1593900291.0</t>
-        </is>
-      </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR10" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="DS10" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="DT10" t="inlineStr">
-        <is>
-          <t>-3.13</t>
-        </is>
-      </c>
-      <c r="DU10" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DV10" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="DW10" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="DX10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY10" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="DZ10" t="inlineStr">
-        <is>
-          <t>-5.034791190033646</t>
-        </is>
-      </c>
-      <c r="EA10" t="inlineStr">
-        <is>
-          <t>6.457567924179223</t>
-        </is>
-      </c>
-      <c r="EB10" t="inlineStr">
-        <is>
-          <t>6.363949904140926</t>
-        </is>
-      </c>
-      <c r="EC10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED10" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE10" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="EF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG10" t="inlineStr">
         <is>
           <t>4.15</t>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>74.59</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
-          <t>173902</t>
+          <t>191060</t>
         </is>
       </c>
       <c r="EM10" t="inlineStr">
@@ -10025,32 +10025,32 @@
       </c>
       <c r="EO10" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
+          <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
       <c r="EP10" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="EQ10" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="ER10" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="ES10" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="ET10" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="EU10" t="inlineStr">
@@ -10070,42 +10070,42 @@
       </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FA10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF10" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK10" t="inlineStr">

--- a/Result/checksun_type/玻璃.xlsx
+++ b/Result/checksun_type/玻璃.xlsx
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>108469.283</t>
+          <t>160355.371</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.40024406754507963</t>
+          <t>0.664642390213131</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1538,47 +1538,47 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.35</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>62.8784115426783</t>
+          <t>63.63534835530604</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>55.4215884573217</t>
+          <t>55.06465164469397</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.1260663243509147</t>
+          <t>0.1444093801282573</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.004244482173174857</t>
+          <t>0.003381234150464874</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.0280821893407488</t>
+          <t>0.01203810328625354</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.6421274212056256</t>
+          <t>0.1455032172289632</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.3172205465981546</t>
+          <t>0.3148845958157165</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1.342500795257151</t>
+          <t>1.506097240232647</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1593,172 +1593,172 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>24130542.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>5601529.0</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>29910071.0</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>26385807.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>57000.0</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>20000.0</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>37000.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>7734109.0</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>34156916.0</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1823,22 +1823,22 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-10-08 00:00:00</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>32.50</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1849,58 +1849,58 @@
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>1,174</t>
+          <t>1,118</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>108469</t>
+          <t>160355</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>91.14</t>
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>8.380000000000001</v>
+        <v>3.67</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.49</v>
+        <v>3.86</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>60.62</t>
+          <t>61.64</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>59.54</t>
+          <t>60.05</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.35</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>57.03</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
@@ -1910,58 +1910,58 @@
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>52.76041666666666</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>0.01950891355533146</t>
+          <t>0.01682612999010225</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>0.009494743981010467</t>
+          <t>0.00856567013772258</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>0.004244482173174857</t>
+          <t>0.003381234150464874</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>0.004650589250797088</t>
+          <t>0.005523311883011139</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>0.001338282189346174</t>
+          <t>-4.176542449352283e-05</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>0.002688352977974429</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>135.54</t>
+          <t>118.12</t>
         </is>
       </c>
       <c r="DB2" t="n">
-        <v>0.79</v>
+        <v>1.04</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.34</v>
+        <v>0.48</v>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-88.81</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
@@ -1971,48 +1971,48 @@
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>5652291899.884943</t>
+          <t>7429528372.217391</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>6893350654.0</t>
+          <t>10313913704.0</t>
         </is>
       </c>
       <c r="DI2" t="n">
-        <v>2269813931.6</v>
+        <v>4149977464.8</v>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>1621013067.8</t>
+          <t>2493014409.1</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>1606583762.933333</t>
+          <t>1911570172.5</t>
         </is>
       </c>
       <c r="DL2" t="n">
-        <v>1631995189.58</v>
+        <v>1816992502.44</v>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>2571721274.6625</t>
+          <t>2665649447.2</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>-16128718.24692487</t>
+          <t>134648827.1291662</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>412587797.9423854</t>
+          <t>963925326.7761698</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>6893350654.0</t>
+          <t>10313913704.0</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>74.59</t>
+          <t>73.07</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>191060</t>
+          <t>185825</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
@@ -2142,27 +2142,27 @@
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
@@ -2182,67 +2182,67 @@
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.170978353032447</t>
         </is>
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23901.898</t>
+          <t>108469.283</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2454,17 +2454,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.11903274433361645</t>
+          <t>0.40024406754507963</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2504,247 +2504,247 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>弱勢整理</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : True</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>59.15</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>62.87841154267971</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>55.42158845732029</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.1260663243509623</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.004244482173174857</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.02808218934073281</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.6421274212045627</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.3148845958157165</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>1.342500795256727</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 20&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>61.1608801267131</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>56.63911987328689</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.07677012314815294</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.0005945808205214398</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.001183500693125117</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.01616981328433842</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.3172205465981546</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.8235494318042734</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>24130542.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>5601529.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>29910071.0</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>26385807.0</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>57000.0</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>20000.0</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>37000.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>7734109.0</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>34156916.0</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -2809,145 +2809,145 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-10-08 00:00:00</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>21.98</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>1,174</t>
+          <t>1,118</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>108469</t>
+          <t>160355</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>79.88</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="CK3" t="n">
-        <v>0.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.95</v>
+        <v>2.49</v>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>60.62</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>59.54</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>57.03</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>59.78</t>
+          <t>59.86</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>52.61895833333334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>0.007455099966113155</t>
+          <t>0.01950891355533146</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>0.001698369565217073</t>
+          <t>0.009494743981010467</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>0.0005945808205214398</t>
+          <t>0.004244482173174857</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>0.003110035164602287</t>
+          <t>0.004650589250797088</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>-6.272804257134723e-05</t>
+          <t>0.001338282189346174</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>0.002234056061712453</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>135.54</t>
         </is>
       </c>
       <c r="DB3" t="n">
-        <v>0.28</v>
+        <v>0.79</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>-94.85</t>
+          <t>-92.11</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
@@ -2957,48 +2957,48 @@
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>5652291899.884943</t>
+          <t>7429528372.217391</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>1434343204.0</t>
+          <t>6893350654.0</t>
         </is>
       </c>
       <c r="DI3" t="n">
-        <v>1173445043.8</v>
+        <v>2269813931.6</v>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>1048624403.3</t>
+          <t>1621013067.8</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>1411256752.533333</t>
+          <t>1606583762.933333</t>
         </is>
       </c>
       <c r="DL3" t="n">
-        <v>1509531056.42</v>
+        <v>1631995189.58</v>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>2523130309.375</t>
+          <t>2571721274.6625</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>-94077175.73589039</t>
+          <t>-16128718.26119804</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>-23283623.53622055</t>
+          <t>412587797.9393222</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>1434343204.0</t>
+          <t>6893350654.0</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>74.59</t>
+          <t>73.07</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>191060</t>
+          <t>185825</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
@@ -3128,27 +3128,27 @@
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
@@ -3168,67 +3168,67 @@
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FB3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FD3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FE3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23093.784</t>
+          <t>23901.898</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.11135316584249741</t>
+          <t>0.11903274433361645</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -3510,47 +3510,47 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>58.86500000000001</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>61.08858174787246</t>
+          <t>61.16088012671542</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>56.64141825212756</t>
+          <t>56.63911987328458</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.07554851772266885</t>
+          <t>0.0767701231482316</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.0005949345571989451</t>
+          <t>0.0005945808205216618</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.0006847801378488949</t>
+          <t>0.001183500693124673</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.002472742767799962</t>
+          <t>0.01616981328430134</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.3172205465981546</t>
+          <t>0.3148845958157165</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.7911038446557226</t>
+          <t>0.8235494318045389</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -3590,27 +3590,27 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:00</t>
+          <t>2026-10-08 00:00:00</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -3645,32 +3645,32 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3690,32 +3690,32 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>26385807.0</t>
+          <t>24130542.0</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>57000.0</t>
+          <t>178000.0</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>20000.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>37000.0</t>
+          <t>178000.0</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>7734109.0</t>
+          <t>5601529.0</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>34156916.0</t>
+          <t>29910071.0</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -3795,22 +3795,22 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-10-08 00:00:00</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -3821,58 +3821,58 @@
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1,174</t>
+          <t>1,118</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>108469</t>
+          <t>160355</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>79.88</t>
         </is>
       </c>
       <c r="CK4" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.26</v>
+        <v>0.95</v>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>59.46</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>58.88000000000001</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>58.87</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>56.59</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
@@ -3882,58 +3882,58 @@
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>52.50166666666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>0.003059143439837042</t>
+          <t>0.007455099966113155</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>0.001360544217687387</t>
+          <t>0.001698369565217073</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>0.0005949345571989451</t>
+          <t>0.0005945808205216618</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>0.001770193482147464</t>
+          <t>0.003110035164602287</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>-0.0007730477931574553</t>
+          <t>-6.272804257134723e-05</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>0.002286891537705671</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="DB4" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DC4" t="n">
         <v>0.22</v>
       </c>
-      <c r="DC4" t="n">
-        <v>0.21</v>
-      </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
         <is>
-          <t>-95.18</t>
+          <t>-94.79</t>
         </is>
       </c>
       <c r="DF4" t="inlineStr">
@@ -3943,48 +3943,48 @@
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>5652291899.884943</t>
+          <t>7429528372.217391</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>1391651459.0</t>
+          <t>1434343204.0</t>
         </is>
       </c>
       <c r="DI4" t="n">
-        <v>978592810.6</v>
+        <v>1173445043.8</v>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>1101216786.0</t>
+          <t>1048624403.3</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>1410351796.1</t>
+          <t>1411256752.533333</t>
         </is>
       </c>
       <c r="DL4" t="n">
-        <v>1501930217.1</v>
+        <v>1509531056.42</v>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>2534452706.925</t>
+          <t>2523130309.375</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>-106948730.6812849</t>
+          <t>-94077175.75220172</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>-60231869.45079255</t>
+          <t>-23283623.53972125</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
         <is>
-          <t>1391651459.0</t>
+          <t>1434343204.0</t>
         </is>
       </c>
       <c r="DQ4" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>74.59</t>
+          <t>73.07</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
-          <t>191060</t>
+          <t>185825</t>
         </is>
       </c>
       <c r="EM4" t="inlineStr">
@@ -4109,32 +4109,32 @@
       </c>
       <c r="EO4" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP4" t="inlineStr">
         <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="EQ4" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
       <c r="ER4" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="ES4" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="ET4" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU4" t="inlineStr">
@@ -4154,67 +4154,67 @@
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EZ4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FA4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FB4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FD4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FE4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
@@ -4391,7 +4391,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12062.573</t>
+          <t>23093.784</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4426,17 +4426,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.28003130372797114</t>
+          <t>-0.11135316584249741</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -4481,242 +4481,242 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>弱勢整理</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 20&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>58.86499999999999</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>61.08858174787481</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>56.64141825212518</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.07554851772274902</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.000594934557198723</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.0006847801378484508</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.002472742767793745</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.3148845958157165</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.7911038446560315</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>58.83</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>61.04677812673161</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>56.61322187326839</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.07536216647056303</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>-0.001103659054249029</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-0.00356859712204749</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.06377897240368935</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.3172205465981546</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>0.7611408795635349</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>24130542.0</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>5601529.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>29910071.0</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>26385807.0</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>57000.0</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>20000.0</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>37000.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>7734109.0</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>34156916.0</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -4781,22 +4781,22 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-10-08 00:00:00</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -4807,119 +4807,119 @@
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>1,174</t>
+          <t>1,118</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>108469</t>
+          <t>160355</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CK5" t="n">
-        <v>1.12</v>
+        <v>0.47</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>58.88000000000001</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.86</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>56.59</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.78</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>52.38187500000001</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>0.006500171057133075</t>
+          <t>0.003059143439837042</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>0.001703577512776722</t>
+          <t>0.001360544217687387</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>-0.001103659054249029</t>
+          <t>0.000594934557198723</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>0.001382660025171623</t>
+          <t>0.001770193482147464</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>-0.0005220569042025947</t>
+          <t>-0.0007730477931574553</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>0.002527920765234448</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="DB5" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>-95.26</t>
+          <t>-95.12</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
@@ -4929,48 +4929,48 @@
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>5652291899.884943</t>
+          <t>7429528372.217391</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>716628303.0</t>
+          <t>1391651459.0</t>
         </is>
       </c>
       <c r="DI5" t="n">
-        <v>793132356.6</v>
+        <v>978592810.6</v>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>1101620613.1</t>
+          <t>1101216786.0</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>1512236185.5</t>
+          <t>1410351796.1</t>
         </is>
       </c>
       <c r="DL5" t="n">
-        <v>1491436510.72</v>
+        <v>1501930217.1</v>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>2550447434.6375</t>
+          <t>2534452706.925</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>-115442705.4504653</t>
+          <t>-106948730.6999255</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>-106289824.1697955</t>
+          <t>-60231869.45479345</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>716628303.0</t>
+          <t>1391651459.0</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>74.59</t>
+          <t>73.07</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>191060</t>
+          <t>185825</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
@@ -5095,32 +5095,32 @@
       </c>
       <c r="EO5" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
@@ -5140,67 +5140,67 @@
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FA5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FB5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FE5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK5" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15496.264</t>
+          <t>12062.573</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5412,17 +5412,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.23927286091689726</t>
+          <t>-0.28003130372797114</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -5467,242 +5467,242 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>58.83</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>61.04677812673398</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>56.61322187326602</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.07536216647064348</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>-0.001103659054249029</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-0.003568597122044825</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.06377897240356267</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.3148845958157165</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.7611408795638696</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>58.895</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>61.26540969143753</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>56.52459030856246</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.08049612671491764</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>-0.002117926126736669</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-0.005781894342767324</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.08696589266464283</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.3172205465981546</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>0.7815573182263081</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>24130542.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>5601529.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>29910071.0</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>26385807.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>57000.0</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>20000.0</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>37000.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>7734109.0</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>34156916.0</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -5767,145 +5767,145 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-10-08 00:00:00</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>1,174</t>
+          <t>1,118</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>108469</t>
+          <t>160355</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CK6" t="n">
-        <v>0.58</v>
+        <v>1.12</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.74</v>
+        <v>0.02</v>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>56.41</t>
+          <t>56.49</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>59.86</t>
+          <t>59.83</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>52.24979166666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>2.220446049250313e-16</t>
+          <t>0.006500171057133075</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>0.004792879150975704</t>
+          <t>0.001703577512776722</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>-0.002117926126736669</t>
+          <t>-0.001103659054249029</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>0.001669063726273734</t>
+          <t>0.001382660025171623</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>-0.001834269575095582</t>
+          <t>-0.0005220569042025947</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>0.002534327343953091</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>-29.02</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="DB6" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="DC6" t="n">
         <v>0.2</v>
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE6" t="inlineStr">
         <is>
-          <t>-95.24</t>
+          <t>-95.21</t>
         </is>
       </c>
       <c r="DF6" t="inlineStr">
@@ -5915,48 +5915,48 @@
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>5652291899.884943</t>
+          <t>7429528372.217391</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>913096038.0</t>
+          <t>716628303.0</t>
         </is>
       </c>
       <c r="DI6" t="n">
-        <v>836051353.4</v>
+        <v>793132356.6</v>
       </c>
       <c r="DJ6" t="inlineStr">
         <is>
-          <t>1099016073.5</t>
+          <t>1101620613.1</t>
         </is>
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>1537638652.2</t>
+          <t>1512236185.5</t>
         </is>
       </c>
       <c r="DL6" t="n">
-        <v>1496862031.52</v>
+        <v>1491436510.72</v>
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>2578499982.6</t>
+          <t>2550447434.6375</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>-117106865.6833144</t>
+          <t>-115442705.4717676</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>-95966927.61945021</t>
+          <t>-106289824.1743681</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
         <is>
-          <t>913096038.0</t>
+          <t>716628303.0</t>
         </is>
       </c>
       <c r="DQ6" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
@@ -6021,17 +6021,17 @@
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>74.59</t>
+          <t>73.07</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>191060</t>
+          <t>185825</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="EO6" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="ES6" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU6" t="inlineStr">
@@ -6126,67 +6126,67 @@
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="EZ6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="FA6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EZ6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="FA6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FE6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK6" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23784.387</t>
+          <t>15496.264</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6398,17 +6398,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.08663988999632684</t>
+          <t>-0.23927286091689726</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -6453,242 +6453,242 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>58.895</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>61.26540969143974</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>56.52459030856025</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.08049612671499268</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>-0.00211792612673678</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-0.005781894342764105</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.08696589266449983</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.3148845958157165</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.7815573182265803</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>59.02</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>61.62169984918725</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>56.41830015081274</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.08816332935232991</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>-0.0007618725133330395</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-0.00224318461089712</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.03396950249461561</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.3172205465981546</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0.8245796448189587</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>24130542.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>5601529.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>29910071.0</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>26385807.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>57000.0</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>20000.0</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>37000.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>7734109.0</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>34156916.0</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -6753,22 +6753,22 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-10-08 00:00:00</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -6779,119 +6779,119 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>1,174</t>
+          <t>1,118</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>108469</t>
+          <t>160355</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="CK7" t="n">
-        <v>2.46</v>
+        <v>0.58</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.95</v>
+        <v>-0.74</v>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>58.45999999999999</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>56.32</t>
+          <t>56.41</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>59.97</t>
+          <t>59.86</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>52.11770833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>-0.0006837606837607479</t>
+          <t>2.220446049250313e-16</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>0.003607627555402892</t>
+          <t>0.004792879150975704</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>-0.0007618725133330395</t>
+          <t>-0.00211792612673678</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>0.002349297880292589</t>
+          <t>0.001669063726273734</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>-0.001872444892906611</t>
+          <t>-0.001834269575095582</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>0.00256085538180395</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>-33.32</t>
+          <t>-29.02</t>
         </is>
       </c>
       <c r="DB7" t="n">
         <v>0.15</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DD7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE7" t="inlineStr">
         <is>
-          <t>-94.89</t>
+          <t>-95.18</t>
         </is>
       </c>
       <c r="DF7" t="inlineStr">
@@ -6901,48 +6901,48 @@
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>5652291899.884943</t>
+          <t>7429528372.217391</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>1411506215.0</t>
+          <t>913096038.0</t>
         </is>
       </c>
       <c r="DI7" t="n">
-        <v>972212204</v>
+        <v>836051353.4</v>
       </c>
       <c r="DJ7" t="inlineStr">
         <is>
-          <t>1064434710.2</t>
+          <t>1099016073.5</t>
         </is>
       </c>
       <c r="DK7" t="inlineStr">
         <is>
-          <t>1565951673.033333</t>
+          <t>1537638652.2</t>
         </is>
       </c>
       <c r="DL7" t="n">
-        <v>1495033587.44</v>
+        <v>1496862031.52</v>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>2612782440.9375</t>
+          <t>2578499982.6</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>-120950490.7858351</t>
+          <t>-117106865.7076584</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>-98842656.73969078</t>
+          <t>-95966927.62467611</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
         <is>
-          <t>1411506215.0</t>
+          <t>913096038.0</t>
         </is>
       </c>
       <c r="DQ7" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
@@ -7007,17 +7007,17 @@
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>74.59</t>
+          <t>73.07</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>191060</t>
+          <t>185825</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
@@ -7067,32 +7067,32 @@
       </c>
       <c r="EO7" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="ES7" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="ET7" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU7" t="inlineStr">
@@ -7112,67 +7112,67 @@
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="FA7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EZ7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="FA7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK7" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7975.945</t>
+          <t>23784.387</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>59.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7384,17 +7384,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.06753878030510366</t>
+          <t>-0.08663988999632684</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -7439,242 +7439,242 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>59.02</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>61.62169984918928</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>56.41830015081073</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.08816332935239829</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>-0.0007618725133327064</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-0.002243184610895566</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.03396950249456443</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.3148845958157165</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0.8245796448191481</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>59.06500000000001</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>61.76023946792703</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>56.36976053207299</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0.09126350522058804</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>-0.002701561840438793</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>-0.002804803302640657</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.002366772355803071</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0.3172205465981546</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>0.8234794118945751</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>24130542.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>5601529.0</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>29910071.0</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>26385807.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>57000.0</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>20000.0</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>37000.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>7734109.0</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>34156916.0</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -7739,22 +7739,22 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-10-08 00:00:00</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -7765,119 +7765,119 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>1,174</t>
+          <t>1,118</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>108469</t>
+          <t>160355</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="CK8" t="n">
-        <v>-1.54</v>
+        <v>2.46</v>
       </c>
       <c r="CL8" t="n">
-        <v>-0.96</v>
+        <v>-0.95</v>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.45999999999999</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>58.21</t>
+          <t>58.42</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>59.07</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>56.32</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>59.97</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>51.98458333333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
         <is>
-          <t>-0.004085801838610736</t>
+          <t>-0.0006837606837607479</t>
         </is>
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>-0.001029689377037957</t>
+          <t>0.003607627555402892</t>
         </is>
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>-0.002701561840438793</t>
+          <t>-0.0007618725133327064</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>0.0003560809728131442</t>
+          <t>0.002349297880292589</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>-0.002945599751076</t>
+          <t>-0.001872444892906611</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>0.002426462908059479</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>-85.80</t>
+          <t>-33.32</t>
         </is>
       </c>
       <c r="DB8" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DD8" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE8" t="inlineStr">
         <is>
-          <t>-94.46</t>
+          <t>-94.83</t>
         </is>
       </c>
       <c r="DF8" t="inlineStr">
@@ -7887,48 +7887,48 @@
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>5652291899.884943</t>
+          <t>7429528372.217391</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>460082038.0</t>
+          <t>1411506215.0</t>
         </is>
       </c>
       <c r="DI8" t="n">
-        <v>923803762.8</v>
+        <v>972212204</v>
       </c>
       <c r="DJ8" t="inlineStr">
         <is>
-          <t>990715477.8</t>
+          <t>1064434710.2</t>
         </is>
       </c>
       <c r="DK8" t="inlineStr">
         <is>
-          <t>1577592671.866667</t>
+          <t>1565951673.033333</t>
         </is>
       </c>
       <c r="DL8" t="n">
-        <v>1503106536.6</v>
+        <v>1495033587.44</v>
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>2650980248.8625</t>
+          <t>2612782440.9375</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>-124970096.9760432</t>
+          <t>-120950490.8136552</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>-152821836.7064742</t>
+          <t>-98842656.74566317</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
         <is>
-          <t>460082038.0</t>
+          <t>1411506215.0</t>
         </is>
       </c>
       <c r="DQ8" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="DT8" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="DU8" t="inlineStr">
@@ -7993,17 +7993,17 @@
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>74.59</t>
+          <t>73.07</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>191060</t>
+          <t>185825</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
@@ -8053,32 +8053,32 @@
       </c>
       <c r="EO8" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP8" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="EQ8" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="ER8" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="ES8" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>59.9</t>
         </is>
       </c>
       <c r="ET8" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU8" t="inlineStr">
@@ -8098,67 +8098,67 @@
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="FA8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EZ8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="FA8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK8" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8054.096</t>
+          <t>7975.945</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8370,17 +8370,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.20773173479608792</t>
+          <t>-0.06753878030510366</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -8425,242 +8425,242 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>59.065</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>61.76023946792896</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>56.36976053207103</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.09126350522065399</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>-0.002701561840439015</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>-0.002804803302640768</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-0.00236677235579652</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.3148845958157165</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.8234794118947475</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>59.225</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>61.9339520211014</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>56.5160479788986</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0.09148001759734582</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>-0.0006749346157092218</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>-0.0001967952176190613</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>0.01105457588252956</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0.3172205465981546</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>0.7820832597153745</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>24130542.0</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>5601529.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>29910071.0</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>26385807.0</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>57000.0</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>20000.0</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>37000.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>7734109.0</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>34156916.0</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -8725,22 +8725,22 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-10-08 00:00:00</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -8751,119 +8751,119 @@
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>1,174</t>
+          <t>1,118</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>108469</t>
+          <t>160355</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>55.28</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="CK9" t="n">
-        <v>-0.58</v>
+        <v>-1.54</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0.82</v>
+        <v>-0.96</v>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>58.73999999999999</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>58.27</t>
+          <t>58.21</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>56.17</t>
+          <t>56.19</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>51.85875</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>-0.0003403675970049536</t>
+          <t>-0.004085801838610736</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>-0.00205514642918303</t>
+          <t>-0.001029689377037957</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>-0.0006749346157092218</t>
+          <t>-0.002701561840439015</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>-0.001173688047943156</t>
+          <t>0.0003560809728131442</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>-0.00260688756245675</t>
+          <t>-0.002945599751076</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>0.002597904759603198</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>-57.25</t>
+          <t>-85.80</t>
         </is>
       </c>
       <c r="DB9" t="n">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="DD9" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE9" t="inlineStr">
         <is>
-          <t>-93.28</t>
+          <t>-94.40</t>
         </is>
       </c>
       <c r="DF9" t="inlineStr">
@@ -8873,48 +8873,48 @@
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>5652291899.884943</t>
+          <t>7429528372.217391</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>464349189.0</t>
+          <t>460082038.0</t>
         </is>
       </c>
       <c r="DI9" t="n">
-        <v>1223840761.4</v>
+        <v>923803762.8</v>
       </c>
       <c r="DJ9" t="inlineStr">
         <is>
-          <t>1013338249.0</t>
+          <t>990715477.8</t>
         </is>
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>1611987982.833333</t>
+          <t>1577592671.866667</t>
         </is>
       </c>
       <c r="DL9" t="n">
-        <v>1533541700.16</v>
+        <v>1503106536.6</v>
       </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>2698659312.1</t>
+          <t>2650980248.8625</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>-119906144.297783</t>
+          <t>-124970097.0078356</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>-122538723.5266478</t>
+          <t>-152821836.7132996</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
         <is>
-          <t>464349189.0</t>
+          <t>460082038.0</t>
         </is>
       </c>
       <c r="DQ9" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>74.59</t>
+          <t>73.07</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>191060</t>
+          <t>185825</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="EO9" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP9" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="EQ9" t="inlineStr">
@@ -9054,17 +9054,17 @@
       </c>
       <c r="ER9" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="ES9" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="ET9" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU9" t="inlineStr">
@@ -9084,67 +9084,67 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="FA9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EZ9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="FA9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK9" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16045.294</t>
+          <t>8054.096</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9356,17 +9356,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.37788535417800007</t>
+          <t>0.20773173479608792</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -9411,242 +9411,242 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>59.225</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>61.93395202110334</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>56.51604797889666</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.09148001759741133</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>-0.0006749346157091107</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>-0.0001967952176192833</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.0110545758825138</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.3148845958157165</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0.7820832597155659</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>59.26500000000001</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>61.94614272573978</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>56.58385727426024</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0.09047980176292138</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>-0.00176856998484054</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.0001198607285666231</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.04561581977777873</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>0.3172205465981546</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>0.7205604977951365</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>2026-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>24130542.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>178000.0</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>5601529.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>29910071.0</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>26385807.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>57000.0</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>20000.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>37000.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>7734109.0</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>34156916.0</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -9711,22 +9711,22 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-10-08 00:00:00</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -9737,119 +9737,119 @@
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>1,174</t>
+          <t>1,118</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>108469</t>
+          <t>160355</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>68.31</t>
+          <t>55.28</t>
         </is>
       </c>
       <c r="CK10" t="n">
-        <v>-1.97</v>
+        <v>-0.58</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0.85</v>
+        <v>-0.82</v>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>58.76000000000001</t>
+          <t>58.73999999999999</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>58.39</t>
+          <t>58.27</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>59.27</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>56.23</t>
+          <t>56.17</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>51.724375</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
         <is>
-          <t>-0.003053953172717838</t>
+          <t>-0.0003403675970049536</t>
         </is>
       </c>
       <c r="CV10" t="inlineStr">
         <is>
-          <t>-0.00443307757885758</t>
+          <t>-0.00205514642918303</t>
         </is>
       </c>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>-0.00176856998484054</t>
+          <t>-0.0006749346157091107</t>
         </is>
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>-0.001987754015440713</t>
+          <t>-0.001173688047943156</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>-0.003545989630041935</t>
+          <t>-0.00260688756245675</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>0.002333477325302091</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>-53.11</t>
+          <t>-57.25</t>
         </is>
       </c>
       <c r="DB10" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DD10" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DE10" t="inlineStr">
         <is>
-          <t>-92.32</t>
+          <t>-93.19</t>
         </is>
       </c>
       <c r="DF10" t="inlineStr">
@@ -9859,48 +9859,48 @@
       </c>
       <c r="DG10" t="inlineStr">
         <is>
-          <t>5652291899.884943</t>
+          <t>7429528372.217391</t>
         </is>
       </c>
       <c r="DH10" t="inlineStr">
         <is>
-          <t>931223287.0</t>
+          <t>464349189.0</t>
         </is>
       </c>
       <c r="DI10" t="n">
-        <v>1410108869.6</v>
+        <v>1223840761.4</v>
       </c>
       <c r="DJ10" t="inlineStr">
         <is>
-          <t>1023386209.4</t>
+          <t>1013338249.0</t>
         </is>
       </c>
       <c r="DK10" t="inlineStr">
         <is>
-          <t>1634858488.1</t>
+          <t>1611987982.833333</t>
         </is>
       </c>
       <c r="DL10" t="n">
-        <v>1559387232.3</v>
+        <v>1533541700.16</v>
       </c>
       <c r="DM10" t="inlineStr">
         <is>
-          <t>2830262055.8375</t>
+          <t>2698659312.1</t>
         </is>
       </c>
       <c r="DN10" t="inlineStr">
         <is>
-          <t>-119427493.5288985</t>
+          <t>-119906144.3341149</t>
         </is>
       </c>
       <c r="DO10" t="inlineStr">
         <is>
-          <t>-75357945.03665853</t>
+          <t>-122538723.5344481</t>
         </is>
       </c>
       <c r="DP10" t="inlineStr">
         <is>
-          <t>931223287.0</t>
+          <t>464349189.0</t>
         </is>
       </c>
       <c r="DQ10" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="DT10" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="DU10" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="EE10" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="EF10" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>74.59</t>
+          <t>73.07</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
-          <t>191060</t>
+          <t>185825</t>
         </is>
       </c>
       <c r="EM10" t="inlineStr">
@@ -10025,32 +10025,32 @@
       </c>
       <c r="EO10" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷平上市</t>
         </is>
       </c>
       <c r="EP10" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="EQ10" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="ER10" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="ES10" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="ET10" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="EU10" t="inlineStr">
@@ -10070,67 +10070,67 @@
       </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="FA10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FB10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FC10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="FE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FF10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="EZ10" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="FA10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FB10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FC10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FD10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="FE10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="FF10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK10" t="inlineStr">

--- a/Result/checksun_type/玻璃.xlsx
+++ b/Result/checksun_type/玻璃.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GR10"/>
+  <dimension ref="A1:GS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,610 +821,615 @@
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
+          <t>voc_cross</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
           <t>voc_cross_d</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>MA_5</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>MA_10</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>MA_20</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>MA_50</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>MA_80</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>MA_240</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>MA_5_斜率</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>MA_10_斜率</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>MA_20_斜率</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>MA_50_斜率</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>MA_80_斜率</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>MA_240_斜率</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_5</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_10</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_30</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_50</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_80</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>成交金額_補值</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>最小收盤價</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>盤整震盪_前15日次數</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>多頭排列_前5日次數</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>下跌帶量_前15日次數</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>MA_break_前15日次數</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>抄底訊號_前15日次數</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>黃金交叉_前15日次數</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>量起點_前15日次數</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>價過5日_前15日次數</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>量短5長30比</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前10日次數</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前5日次數</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前2日次數</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前1日次數</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>季別</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>營業收入</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>營業成本</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>營業毛利</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>毛利率</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>營業利益</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>營益率</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>業外收支</t>
         </is>
       </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>稅前淨利</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>稅後淨利</t>
         </is>
       </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>EPS(元)</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>EPS_前8季全為正</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>去年同季比較</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>EPS_MA_8</t>
         </is>
       </c>
-      <c r="FY1" s="1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>GM_MA_8</t>
         </is>
       </c>
-      <c r="FZ1" s="1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>EPS_維持</t>
         </is>
       </c>
-      <c r="GA1" s="1" t="inlineStr">
+      <c r="GB1" s="1" t="inlineStr">
         <is>
           <t>毛利率_維持</t>
         </is>
       </c>
-      <c r="GB1" s="1" t="inlineStr">
+      <c r="GC1" s="1" t="inlineStr">
         <is>
           <t>EPS_創新高</t>
         </is>
       </c>
-      <c r="GC1" s="1" t="inlineStr">
+      <c r="GD1" s="1" t="inlineStr">
         <is>
           <t>毛利率_創新高</t>
         </is>
       </c>
-      <c r="GD1" s="1" t="inlineStr">
+      <c r="GE1" s="1" t="inlineStr">
         <is>
           <t>財報健康</t>
         </is>
       </c>
-      <c r="GE1" s="1" t="inlineStr">
+      <c r="GF1" s="1" t="inlineStr">
         <is>
           <t>財報強勢</t>
         </is>
       </c>
-      <c r="GF1" s="1" t="inlineStr">
+      <c r="GG1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ</t>
         </is>
       </c>
-      <c r="GG1" s="1" t="inlineStr">
+      <c r="GH1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ_%</t>
         </is>
       </c>
-      <c r="GH1" s="1" t="inlineStr">
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ</t>
         </is>
       </c>
-      <c r="GI1" s="1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ_%</t>
         </is>
       </c>
-      <c r="GJ1" s="1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY</t>
         </is>
       </c>
-      <c r="GK1" s="1" t="inlineStr">
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY_%</t>
         </is>
       </c>
-      <c r="GL1" s="1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY</t>
         </is>
       </c>
-      <c r="GM1" s="1" t="inlineStr">
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY_%</t>
         </is>
       </c>
-      <c r="GN1" s="1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
         <is>
           <t>EPS_成長</t>
         </is>
       </c>
-      <c r="GO1" s="1" t="inlineStr">
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY成長</t>
         </is>
       </c>
-      <c r="GP1" s="1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>毛利率成長</t>
         </is>
       </c>
-      <c r="GQ1" s="1" t="inlineStr">
+      <c r="GR1" s="1" t="inlineStr">
         <is>
           <t>毛利率YoY成長</t>
         </is>
       </c>
-      <c r="GR1" s="1" t="inlineStr">
+      <c r="GS1" s="1" t="inlineStr">
         <is>
           <t>財報動能強</t>
         </is>
@@ -1823,383 +1828,383 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
           <t>2026-10-08 00:00:00</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>32.50</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>-2.46</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr"/>
-      <c r="CG2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr">
         <is>
           <t>1,118</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>160355</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>77.78</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>91.14</t>
         </is>
       </c>
-      <c r="CK2" t="n">
+      <c r="CL2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CM2" t="n">
         <v>3.86</v>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>3.49</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>-4.19</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>61.64</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>60.05</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>59.35</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>57.35</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>59.86</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
           <t>0.01682612999010225</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>0.00856567013772258</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>0.003381234150464874</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>0.005523311883011139</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>-4.176542449352283e-05</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
           <t>118.12</t>
         </is>
       </c>
-      <c r="DB2" t="n">
+      <c r="DC2" t="n">
         <v>1.04</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="DD2" t="n">
         <v>0.48</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>4.25</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>-88.81</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>7429528372.217391</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>10313913704.0</t>
         </is>
       </c>
-      <c r="DI2" t="n">
+      <c r="DJ2" t="n">
         <v>4149977464.8</v>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>2493014409.1</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>1911570172.5</t>
         </is>
       </c>
-      <c r="DL2" t="n">
+      <c r="DM2" t="n">
         <v>1816992502.44</v>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>2665649447.2</t>
         </is>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>134648827.1291662</t>
         </is>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>963925326.7761698</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>10313913704.0</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="DS2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>2026/09/07</t>
         </is>
       </c>
-      <c r="DT2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>5.27</t>
         </is>
       </c>
-      <c r="DU2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DV2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DW2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>-5.034791190033646</t>
         </is>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>6.457567924179223</t>
         </is>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>6.363949904140926</t>
         </is>
       </c>
-      <c r="EC2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="EE2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
           <t>4.15</t>
         </is>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="EI2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>23.33%</t>
         </is>
       </c>
-      <c r="EJ2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="EK2" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>73.07</t>
         </is>
       </c>
-      <c r="EL2" t="inlineStr">
+      <c r="EM2" t="inlineStr">
         <is>
           <t>185825</t>
         </is>
       </c>
-      <c r="EM2" t="inlineStr">
+      <c r="EN2" t="inlineStr">
         <is>
           <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
         </is>
       </c>
-      <c r="EN2" t="inlineStr">
+      <c r="EO2" t="inlineStr">
         <is>
           <t>台玻-玻璃陶瓷-上市</t>
         </is>
       </c>
-      <c r="EO2" t="inlineStr">
+      <c r="EP2" t="inlineStr">
         <is>
           <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
-      <c r="EP2" t="inlineStr">
+      <c r="EQ2" t="inlineStr">
         <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="EQ2" t="inlineStr">
+      <c r="ER2" t="inlineStr">
         <is>
           <t>66.8</t>
         </is>
       </c>
-      <c r="ER2" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>62.6</t>
         </is>
       </c>
-      <c r="ES2" t="inlineStr">
+      <c r="ET2" t="inlineStr">
         <is>
           <t>63.9</t>
         </is>
       </c>
-      <c r="ET2" t="inlineStr">
+      <c r="EU2" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="EU2" t="inlineStr">
+      <c r="EV2" t="inlineStr">
         <is>
           <t>17.77</t>
         </is>
       </c>
-      <c r="EV2" t="inlineStr">
+      <c r="EW2" t="inlineStr">
         <is>
           <t>** 印刷電路板 - 玻璃纖維/玻纖布** 建材營造 - 建材原料</t>
         </is>
       </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX2" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="EY2" t="inlineStr">
+      <c r="EZ2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ2" t="inlineStr">
+      <c r="FA2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="FA2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2207,124 +2212,124 @@
       </c>
       <c r="FC2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FD2" t="inlineStr">
+      <c r="FE2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE2" t="inlineStr">
+      <c r="FF2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="FF2" t="inlineStr">
+      <c r="FG2" t="inlineStr">
         <is>
           <t>2.170978353032447</t>
         </is>
       </c>
-      <c r="FG2" t="inlineStr">
+      <c r="FH2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FH2" t="inlineStr">
+      <c r="FI2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FI2" t="inlineStr">
+      <c r="FJ2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FJ2" t="inlineStr">
+      <c r="FK2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FK2" t="inlineStr">
+      <c r="FL2" t="inlineStr">
         <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL2" t="inlineStr">
+      <c r="FM2" t="inlineStr">
         <is>
           <t>12062.0</t>
         </is>
       </c>
-      <c r="FM2" t="inlineStr">
+      <c r="FN2" t="inlineStr">
         <is>
           <t>9248.0</t>
         </is>
       </c>
-      <c r="FN2" t="inlineStr">
+      <c r="FO2" t="inlineStr">
         <is>
           <t>2813.0</t>
         </is>
       </c>
-      <c r="FO2" t="inlineStr">
+      <c r="FP2" t="inlineStr">
         <is>
           <t>23.33</t>
         </is>
       </c>
-      <c r="FP2" t="inlineStr">
+      <c r="FQ2" t="inlineStr">
         <is>
           <t>1524.0</t>
         </is>
       </c>
-      <c r="FQ2" t="inlineStr">
+      <c r="FR2" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="FR2" t="inlineStr">
+      <c r="FS2" t="inlineStr">
         <is>
           <t>-195.0</t>
         </is>
       </c>
-      <c r="FS2" t="inlineStr">
+      <c r="FT2" t="inlineStr">
         <is>
           <t>1330.0</t>
         </is>
       </c>
-      <c r="FT2" t="inlineStr">
+      <c r="FU2" t="inlineStr">
         <is>
           <t>1267.0</t>
         </is>
       </c>
-      <c r="FU2" t="inlineStr">
+      <c r="FV2" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="FV2" t="inlineStr">
+      <c r="FW2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FW2" t="inlineStr">
+      <c r="FX2" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX2" t="inlineStr">
+      <c r="FY2" t="inlineStr">
         <is>
           <t>0.004999999999999991</t>
         </is>
       </c>
-      <c r="FY2" t="inlineStr">
+      <c r="FZ2" t="inlineStr">
         <is>
           <t>12.88125</t>
         </is>
       </c>
-      <c r="FZ2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GA2" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -2352,49 +2357,49 @@
       </c>
       <c r="GF2" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GG2" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="GG2" t="inlineStr">
+      <c r="GH2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="GH2" t="inlineStr">
+      <c r="GI2" t="inlineStr">
         <is>
           <t>4.099999999999998</t>
         </is>
       </c>
-      <c r="GI2" t="inlineStr">
+      <c r="GJ2" t="inlineStr">
         <is>
           <t>0.2132085283411336</t>
         </is>
       </c>
-      <c r="GJ2" t="inlineStr">
+      <c r="GK2" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="GK2" t="inlineStr">
+      <c r="GL2" t="inlineStr">
         <is>
           <t>-2.466666666666667</t>
         </is>
       </c>
-      <c r="GL2" t="inlineStr">
+      <c r="GM2" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="GM2" t="inlineStr">
+      <c r="GN2" t="inlineStr">
         <is>
           <t>1.333</t>
         </is>
       </c>
-      <c r="GN2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GO2" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -2411,6 +2416,11 @@
         </is>
       </c>
       <c r="GR2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GS2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -2809,383 +2819,383 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
           <t>2026-10-08 00:00:00</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>21.98</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>9.87</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr"/>
-      <c r="CG3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr">
         <is>
           <t>1,118</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>160355</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>87.88</t>
         </is>
       </c>
-      <c r="CK3" t="n">
+      <c r="CL3" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="CL3" t="n">
+      <c r="CM3" t="n">
         <v>2.49</v>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>-4.72</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>60.62</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>59.54</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>59.15</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>57.03</t>
         </is>
       </c>
-      <c r="CS3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>59.86</t>
         </is>
       </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
           <t>0.01950891355533146</t>
         </is>
       </c>
-      <c r="CV3" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>0.009494743981010467</t>
         </is>
       </c>
-      <c r="CW3" t="inlineStr">
+      <c r="CX3" t="inlineStr">
         <is>
           <t>0.004244482173174857</t>
         </is>
       </c>
-      <c r="CX3" t="inlineStr">
+      <c r="CY3" t="inlineStr">
         <is>
           <t>0.004650589250797088</t>
         </is>
       </c>
-      <c r="CY3" t="inlineStr">
+      <c r="CZ3" t="inlineStr">
         <is>
           <t>0.001338282189346174</t>
         </is>
       </c>
-      <c r="CZ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
           <t>135.54</t>
         </is>
       </c>
-      <c r="DB3" t="n">
+      <c r="DC3" t="n">
         <v>0.79</v>
       </c>
-      <c r="DC3" t="n">
+      <c r="DD3" t="n">
         <v>0.34</v>
       </c>
-      <c r="DD3" t="inlineStr">
+      <c r="DE3" t="inlineStr">
         <is>
           <t>4.25</t>
         </is>
       </c>
-      <c r="DE3" t="inlineStr">
+      <c r="DF3" t="inlineStr">
         <is>
           <t>-92.11</t>
         </is>
       </c>
-      <c r="DF3" t="inlineStr">
+      <c r="DG3" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
-      <c r="DG3" t="inlineStr">
+      <c r="DH3" t="inlineStr">
         <is>
           <t>7429528372.217391</t>
         </is>
       </c>
-      <c r="DH3" t="inlineStr">
+      <c r="DI3" t="inlineStr">
         <is>
           <t>6893350654.0</t>
         </is>
       </c>
-      <c r="DI3" t="n">
+      <c r="DJ3" t="n">
         <v>2269813931.6</v>
       </c>
-      <c r="DJ3" t="inlineStr">
+      <c r="DK3" t="inlineStr">
         <is>
           <t>1621013067.8</t>
         </is>
       </c>
-      <c r="DK3" t="inlineStr">
+      <c r="DL3" t="inlineStr">
         <is>
           <t>1606583762.933333</t>
         </is>
       </c>
-      <c r="DL3" t="n">
+      <c r="DM3" t="n">
         <v>1631995189.58</v>
       </c>
-      <c r="DM3" t="inlineStr">
+      <c r="DN3" t="inlineStr">
         <is>
           <t>2571721274.6625</t>
         </is>
       </c>
-      <c r="DN3" t="inlineStr">
+      <c r="DO3" t="inlineStr">
         <is>
           <t>-16128718.26119804</t>
         </is>
       </c>
-      <c r="DO3" t="inlineStr">
+      <c r="DP3" t="inlineStr">
         <is>
           <t>412587797.9393222</t>
         </is>
       </c>
-      <c r="DP3" t="inlineStr">
+      <c r="DQ3" t="inlineStr">
         <is>
           <t>6893350654.0</t>
         </is>
       </c>
-      <c r="DQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="DS3" t="inlineStr">
+      <c r="DT3" t="inlineStr">
         <is>
           <t>2026/09/07</t>
         </is>
       </c>
-      <c r="DT3" t="inlineStr">
+      <c r="DU3" t="inlineStr">
         <is>
           <t>8.24</t>
         </is>
       </c>
-      <c r="DU3" t="inlineStr">
+      <c r="DV3" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DV3" t="inlineStr">
+      <c r="DW3" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DW3" t="inlineStr">
+      <c r="DX3" t="inlineStr">
         <is>
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="DX3" t="inlineStr">
+      <c r="DY3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY3" t="inlineStr">
+      <c r="DZ3" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="DZ3" t="inlineStr">
+      <c r="EA3" t="inlineStr">
         <is>
           <t>-5.034791190033646</t>
         </is>
       </c>
-      <c r="EA3" t="inlineStr">
+      <c r="EB3" t="inlineStr">
         <is>
           <t>6.457567924179223</t>
         </is>
       </c>
-      <c r="EB3" t="inlineStr">
+      <c r="EC3" t="inlineStr">
         <is>
           <t>6.363949904140926</t>
         </is>
       </c>
-      <c r="EC3" t="inlineStr">
+      <c r="ED3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED3" t="inlineStr">
+      <c r="EE3" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="EE3" t="inlineStr">
+      <c r="EF3" t="inlineStr">
         <is>
           <t>3.70</t>
         </is>
       </c>
-      <c r="EF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
           <t>4.15</t>
         </is>
       </c>
-      <c r="EH3" t="inlineStr">
+      <c r="EI3" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="EI3" t="inlineStr">
+      <c r="EJ3" t="inlineStr">
         <is>
           <t>23.33%</t>
         </is>
       </c>
-      <c r="EJ3" t="inlineStr">
+      <c r="EK3" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="EK3" t="inlineStr">
+      <c r="EL3" t="inlineStr">
         <is>
           <t>73.07</t>
         </is>
       </c>
-      <c r="EL3" t="inlineStr">
+      <c r="EM3" t="inlineStr">
         <is>
           <t>185825</t>
         </is>
       </c>
-      <c r="EM3" t="inlineStr">
+      <c r="EN3" t="inlineStr">
         <is>
           <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
         </is>
       </c>
-      <c r="EN3" t="inlineStr">
+      <c r="EO3" t="inlineStr">
         <is>
           <t>台玻-玻璃陶瓷-上市</t>
         </is>
       </c>
-      <c r="EO3" t="inlineStr">
+      <c r="EP3" t="inlineStr">
         <is>
           <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
-      <c r="EP3" t="inlineStr">
+      <c r="EQ3" t="inlineStr">
         <is>
           <t>60.1</t>
         </is>
       </c>
-      <c r="EQ3" t="inlineStr">
+      <c r="ER3" t="inlineStr">
         <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="ER3" t="inlineStr">
+      <c r="ES3" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="ES3" t="inlineStr">
+      <c r="ET3" t="inlineStr">
         <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="ET3" t="inlineStr">
+      <c r="EU3" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="EU3" t="inlineStr">
+      <c r="EV3" t="inlineStr">
         <is>
           <t>17.77</t>
         </is>
       </c>
-      <c r="EV3" t="inlineStr">
+      <c r="EW3" t="inlineStr">
         <is>
           <t>** 印刷電路板 - 玻璃纖維/玻纖布** 建材營造 - 建材原料</t>
         </is>
       </c>
-      <c r="EW3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY3" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="EY3" t="inlineStr">
+      <c r="EZ3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="EZ3" t="inlineStr">
+      <c r="FA3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="FA3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB3" t="inlineStr">
         <is>
           <t>0</t>
@@ -3193,14 +3203,14 @@
       </c>
       <c r="FC3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FE3" t="inlineStr">
         <is>
           <t>0</t>
@@ -3208,14 +3218,14 @@
       </c>
       <c r="FF3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FG3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FH3" t="inlineStr">
         <is>
           <t>0</t>
@@ -3233,84 +3243,84 @@
       </c>
       <c r="FK3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL3" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL3" t="inlineStr">
+      <c r="FM3" t="inlineStr">
         <is>
           <t>12062.0</t>
         </is>
       </c>
-      <c r="FM3" t="inlineStr">
+      <c r="FN3" t="inlineStr">
         <is>
           <t>9248.0</t>
         </is>
       </c>
-      <c r="FN3" t="inlineStr">
+      <c r="FO3" t="inlineStr">
         <is>
           <t>2813.0</t>
         </is>
       </c>
-      <c r="FO3" t="inlineStr">
+      <c r="FP3" t="inlineStr">
         <is>
           <t>23.33</t>
         </is>
       </c>
-      <c r="FP3" t="inlineStr">
+      <c r="FQ3" t="inlineStr">
         <is>
           <t>1524.0</t>
         </is>
       </c>
-      <c r="FQ3" t="inlineStr">
+      <c r="FR3" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="FR3" t="inlineStr">
+      <c r="FS3" t="inlineStr">
         <is>
           <t>-195.0</t>
         </is>
       </c>
-      <c r="FS3" t="inlineStr">
+      <c r="FT3" t="inlineStr">
         <is>
           <t>1330.0</t>
         </is>
       </c>
-      <c r="FT3" t="inlineStr">
+      <c r="FU3" t="inlineStr">
         <is>
           <t>1267.0</t>
         </is>
       </c>
-      <c r="FU3" t="inlineStr">
+      <c r="FV3" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="FV3" t="inlineStr">
+      <c r="FW3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FW3" t="inlineStr">
+      <c r="FX3" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX3" t="inlineStr">
+      <c r="FY3" t="inlineStr">
         <is>
           <t>0.004999999999999991</t>
         </is>
       </c>
-      <c r="FY3" t="inlineStr">
+      <c r="FZ3" t="inlineStr">
         <is>
           <t>12.88125</t>
         </is>
       </c>
-      <c r="FZ3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GA3" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -3338,49 +3348,49 @@
       </c>
       <c r="GF3" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GG3" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="GG3" t="inlineStr">
+      <c r="GH3" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="GH3" t="inlineStr">
+      <c r="GI3" t="inlineStr">
         <is>
           <t>4.099999999999998</t>
         </is>
       </c>
-      <c r="GI3" t="inlineStr">
+      <c r="GJ3" t="inlineStr">
         <is>
           <t>0.2132085283411336</t>
         </is>
       </c>
-      <c r="GJ3" t="inlineStr">
+      <c r="GK3" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="GK3" t="inlineStr">
+      <c r="GL3" t="inlineStr">
         <is>
           <t>-2.466666666666667</t>
         </is>
       </c>
-      <c r="GL3" t="inlineStr">
+      <c r="GM3" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="GM3" t="inlineStr">
+      <c r="GN3" t="inlineStr">
         <is>
           <t>1.333</t>
         </is>
       </c>
-      <c r="GN3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GO3" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -3397,6 +3407,11 @@
         </is>
       </c>
       <c r="GR3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GS3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -3795,383 +3810,383 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
           <t>2026-10-08 00:00:00</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>4.84</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr"/>
-      <c r="CG4" t="inlineStr">
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr">
         <is>
           <t>1,118</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>160355</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>95.65</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>79.88</t>
         </is>
       </c>
-      <c r="CK4" t="n">
+      <c r="CL4" t="n">
         <v>0.57</v>
       </c>
-      <c r="CL4" t="n">
+      <c r="CM4" t="n">
         <v>0.95</v>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>3.76</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>-5.04</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>59.46</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>58.98</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>56.77</t>
         </is>
       </c>
-      <c r="CS4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>59.78</t>
         </is>
       </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
           <t>0.007455099966113155</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
+      <c r="CW4" t="inlineStr">
         <is>
           <t>0.001698369565217073</t>
         </is>
       </c>
-      <c r="CW4" t="inlineStr">
+      <c r="CX4" t="inlineStr">
         <is>
           <t>0.0005945808205216618</t>
         </is>
       </c>
-      <c r="CX4" t="inlineStr">
+      <c r="CY4" t="inlineStr">
         <is>
           <t>0.003110035164602287</t>
         </is>
       </c>
-      <c r="CY4" t="inlineStr">
+      <c r="CZ4" t="inlineStr">
         <is>
           <t>-6.272804257134723e-05</t>
         </is>
       </c>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
           <t>25.54</t>
         </is>
       </c>
-      <c r="DB4" t="n">
+      <c r="DC4" t="n">
         <v>0.28</v>
       </c>
-      <c r="DC4" t="n">
+      <c r="DD4" t="n">
         <v>0.22</v>
       </c>
-      <c r="DD4" t="inlineStr">
+      <c r="DE4" t="inlineStr">
         <is>
           <t>4.25</t>
         </is>
       </c>
-      <c r="DE4" t="inlineStr">
+      <c r="DF4" t="inlineStr">
         <is>
           <t>-94.79</t>
         </is>
       </c>
-      <c r="DF4" t="inlineStr">
+      <c r="DG4" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
-      <c r="DG4" t="inlineStr">
+      <c r="DH4" t="inlineStr">
         <is>
           <t>7429528372.217391</t>
         </is>
       </c>
-      <c r="DH4" t="inlineStr">
+      <c r="DI4" t="inlineStr">
         <is>
           <t>1434343204.0</t>
         </is>
       </c>
-      <c r="DI4" t="n">
+      <c r="DJ4" t="n">
         <v>1173445043.8</v>
       </c>
-      <c r="DJ4" t="inlineStr">
+      <c r="DK4" t="inlineStr">
         <is>
           <t>1048624403.3</t>
         </is>
       </c>
-      <c r="DK4" t="inlineStr">
+      <c r="DL4" t="inlineStr">
         <is>
           <t>1411256752.533333</t>
         </is>
       </c>
-      <c r="DL4" t="n">
+      <c r="DM4" t="n">
         <v>1509531056.42</v>
       </c>
-      <c r="DM4" t="inlineStr">
+      <c r="DN4" t="inlineStr">
         <is>
           <t>2523130309.375</t>
         </is>
       </c>
-      <c r="DN4" t="inlineStr">
+      <c r="DO4" t="inlineStr">
         <is>
           <t>-94077175.75220172</t>
         </is>
       </c>
-      <c r="DO4" t="inlineStr">
+      <c r="DP4" t="inlineStr">
         <is>
           <t>-23283623.53972125</t>
         </is>
       </c>
-      <c r="DP4" t="inlineStr">
+      <c r="DQ4" t="inlineStr">
         <is>
           <t>1434343204.0</t>
         </is>
       </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="DS4" t="inlineStr">
+      <c r="DT4" t="inlineStr">
         <is>
           <t>2026/09/07</t>
         </is>
       </c>
-      <c r="DT4" t="inlineStr">
+      <c r="DU4" t="inlineStr">
         <is>
           <t>-1.48</t>
         </is>
       </c>
-      <c r="DU4" t="inlineStr">
+      <c r="DV4" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DV4" t="inlineStr">
+      <c r="DW4" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DW4" t="inlineStr">
+      <c r="DX4" t="inlineStr">
         <is>
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="DX4" t="inlineStr">
+      <c r="DY4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY4" t="inlineStr">
+      <c r="DZ4" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="DZ4" t="inlineStr">
+      <c r="EA4" t="inlineStr">
         <is>
           <t>-5.034791190033646</t>
         </is>
       </c>
-      <c r="EA4" t="inlineStr">
+      <c r="EB4" t="inlineStr">
         <is>
           <t>6.457567924179223</t>
         </is>
       </c>
-      <c r="EB4" t="inlineStr">
+      <c r="EC4" t="inlineStr">
         <is>
           <t>6.363949904140926</t>
         </is>
       </c>
-      <c r="EC4" t="inlineStr">
+      <c r="ED4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED4" t="inlineStr">
+      <c r="EE4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE4" t="inlineStr">
+      <c r="EF4" t="inlineStr">
         <is>
           <t>3.37</t>
         </is>
       </c>
-      <c r="EF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
           <t>4.15</t>
         </is>
       </c>
-      <c r="EH4" t="inlineStr">
+      <c r="EI4" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="EI4" t="inlineStr">
+      <c r="EJ4" t="inlineStr">
         <is>
           <t>23.33%</t>
         </is>
       </c>
-      <c r="EJ4" t="inlineStr">
+      <c r="EK4" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="EK4" t="inlineStr">
+      <c r="EL4" t="inlineStr">
         <is>
           <t>73.07</t>
         </is>
       </c>
-      <c r="EL4" t="inlineStr">
+      <c r="EM4" t="inlineStr">
         <is>
           <t>185825</t>
         </is>
       </c>
-      <c r="EM4" t="inlineStr">
+      <c r="EN4" t="inlineStr">
         <is>
           <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
         </is>
       </c>
-      <c r="EN4" t="inlineStr">
+      <c r="EO4" t="inlineStr">
         <is>
           <t>台玻-玻璃陶瓷-上市</t>
         </is>
       </c>
-      <c r="EO4" t="inlineStr">
+      <c r="EP4" t="inlineStr">
         <is>
           <t>玻璃陶瓷平上市</t>
         </is>
       </c>
-      <c r="EP4" t="inlineStr">
+      <c r="EQ4" t="inlineStr">
         <is>
           <t>60.0</t>
         </is>
       </c>
-      <c r="EQ4" t="inlineStr">
+      <c r="ER4" t="inlineStr">
         <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="ER4" t="inlineStr">
+      <c r="ES4" t="inlineStr">
         <is>
           <t>58.8</t>
         </is>
       </c>
-      <c r="ES4" t="inlineStr">
+      <c r="ET4" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="ET4" t="inlineStr">
+      <c r="EU4" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="EU4" t="inlineStr">
+      <c r="EV4" t="inlineStr">
         <is>
           <t>17.77</t>
         </is>
       </c>
-      <c r="EV4" t="inlineStr">
+      <c r="EW4" t="inlineStr">
         <is>
           <t>** 印刷電路板 - 玻璃纖維/玻纖布** 建材營造 - 建材原料</t>
         </is>
       </c>
-      <c r="EW4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX4" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY4" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="EY4" t="inlineStr">
+      <c r="EZ4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="EZ4" t="inlineStr">
+      <c r="FA4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="FA4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB4" t="inlineStr">
         <is>
           <t>0</t>
@@ -4179,14 +4194,14 @@
       </c>
       <c r="FC4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FE4" t="inlineStr">
         <is>
           <t>0</t>
@@ -4194,14 +4209,14 @@
       </c>
       <c r="FF4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FG4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FH4" t="inlineStr">
         <is>
           <t>0</t>
@@ -4219,84 +4234,84 @@
       </c>
       <c r="FK4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL4" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL4" t="inlineStr">
+      <c r="FM4" t="inlineStr">
         <is>
           <t>12062.0</t>
         </is>
       </c>
-      <c r="FM4" t="inlineStr">
+      <c r="FN4" t="inlineStr">
         <is>
           <t>9248.0</t>
         </is>
       </c>
-      <c r="FN4" t="inlineStr">
+      <c r="FO4" t="inlineStr">
         <is>
           <t>2813.0</t>
         </is>
       </c>
-      <c r="FO4" t="inlineStr">
+      <c r="FP4" t="inlineStr">
         <is>
           <t>23.33</t>
         </is>
       </c>
-      <c r="FP4" t="inlineStr">
+      <c r="FQ4" t="inlineStr">
         <is>
           <t>1524.0</t>
         </is>
       </c>
-      <c r="FQ4" t="inlineStr">
+      <c r="FR4" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="FR4" t="inlineStr">
+      <c r="FS4" t="inlineStr">
         <is>
           <t>-195.0</t>
         </is>
       </c>
-      <c r="FS4" t="inlineStr">
+      <c r="FT4" t="inlineStr">
         <is>
           <t>1330.0</t>
         </is>
       </c>
-      <c r="FT4" t="inlineStr">
+      <c r="FU4" t="inlineStr">
         <is>
           <t>1267.0</t>
         </is>
       </c>
-      <c r="FU4" t="inlineStr">
+      <c r="FV4" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="FV4" t="inlineStr">
+      <c r="FW4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FW4" t="inlineStr">
+      <c r="FX4" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX4" t="inlineStr">
+      <c r="FY4" t="inlineStr">
         <is>
           <t>0.004999999999999991</t>
         </is>
       </c>
-      <c r="FY4" t="inlineStr">
+      <c r="FZ4" t="inlineStr">
         <is>
           <t>12.88125</t>
         </is>
       </c>
-      <c r="FZ4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GA4" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -4324,49 +4339,49 @@
       </c>
       <c r="GF4" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GG4" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="GG4" t="inlineStr">
+      <c r="GH4" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="GH4" t="inlineStr">
+      <c r="GI4" t="inlineStr">
         <is>
           <t>4.099999999999998</t>
         </is>
       </c>
-      <c r="GI4" t="inlineStr">
+      <c r="GJ4" t="inlineStr">
         <is>
           <t>0.2132085283411336</t>
         </is>
       </c>
-      <c r="GJ4" t="inlineStr">
+      <c r="GK4" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="GK4" t="inlineStr">
+      <c r="GL4" t="inlineStr">
         <is>
           <t>-2.466666666666667</t>
         </is>
       </c>
-      <c r="GL4" t="inlineStr">
+      <c r="GM4" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="GM4" t="inlineStr">
+      <c r="GN4" t="inlineStr">
         <is>
           <t>1.333</t>
         </is>
       </c>
-      <c r="GN4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GO4" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -4383,6 +4398,11 @@
         </is>
       </c>
       <c r="GR4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GS4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -4781,383 +4801,383 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
           <t>2026-10-08 00:00:00</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>4.68</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>-3.54</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr"/>
-      <c r="CG5" t="inlineStr">
+      <c r="CG5" t="inlineStr"/>
+      <c r="CH5" t="inlineStr">
         <is>
           <t>1,118</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>160355</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>64.0</t>
         </is>
       </c>
-      <c r="CK5" t="n">
+      <c r="CL5" t="n">
         <v>0.47</v>
       </c>
-      <c r="CL5" t="n">
+      <c r="CM5" t="n">
         <v>0.26</v>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>4.02</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>-5.34</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>59.02</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>58.88000000000001</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>58.86</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>56.59</t>
         </is>
       </c>
-      <c r="CS5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>59.78</t>
         </is>
       </c>
-      <c r="CT5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
           <t>0.003059143439837042</t>
         </is>
       </c>
-      <c r="CV5" t="inlineStr">
+      <c r="CW5" t="inlineStr">
         <is>
           <t>0.001360544217687387</t>
         </is>
       </c>
-      <c r="CW5" t="inlineStr">
+      <c r="CX5" t="inlineStr">
         <is>
           <t>0.000594934557198723</t>
         </is>
       </c>
-      <c r="CX5" t="inlineStr">
+      <c r="CY5" t="inlineStr">
         <is>
           <t>0.001770193482147464</t>
         </is>
       </c>
-      <c r="CY5" t="inlineStr">
+      <c r="CZ5" t="inlineStr">
         <is>
           <t>-0.0007730477931574553</t>
         </is>
       </c>
-      <c r="CZ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
           <t>7.19</t>
         </is>
       </c>
-      <c r="DB5" t="n">
+      <c r="DC5" t="n">
         <v>0.22</v>
       </c>
-      <c r="DC5" t="n">
+      <c r="DD5" t="n">
         <v>0.21</v>
       </c>
-      <c r="DD5" t="inlineStr">
+      <c r="DE5" t="inlineStr">
         <is>
           <t>4.25</t>
         </is>
       </c>
-      <c r="DE5" t="inlineStr">
+      <c r="DF5" t="inlineStr">
         <is>
           <t>-95.12</t>
         </is>
       </c>
-      <c r="DF5" t="inlineStr">
+      <c r="DG5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
-      <c r="DG5" t="inlineStr">
+      <c r="DH5" t="inlineStr">
         <is>
           <t>7429528372.217391</t>
         </is>
       </c>
-      <c r="DH5" t="inlineStr">
+      <c r="DI5" t="inlineStr">
         <is>
           <t>1391651459.0</t>
         </is>
       </c>
-      <c r="DI5" t="n">
+      <c r="DJ5" t="n">
         <v>978592810.6</v>
       </c>
-      <c r="DJ5" t="inlineStr">
+      <c r="DK5" t="inlineStr">
         <is>
           <t>1101216786.0</t>
         </is>
       </c>
-      <c r="DK5" t="inlineStr">
+      <c r="DL5" t="inlineStr">
         <is>
           <t>1410351796.1</t>
         </is>
       </c>
-      <c r="DL5" t="n">
+      <c r="DM5" t="n">
         <v>1501930217.1</v>
       </c>
-      <c r="DM5" t="inlineStr">
+      <c r="DN5" t="inlineStr">
         <is>
           <t>2534452706.925</t>
         </is>
       </c>
-      <c r="DN5" t="inlineStr">
+      <c r="DO5" t="inlineStr">
         <is>
           <t>-106948730.6999255</t>
         </is>
       </c>
-      <c r="DO5" t="inlineStr">
+      <c r="DP5" t="inlineStr">
         <is>
           <t>-60231869.45479345</t>
         </is>
       </c>
-      <c r="DP5" t="inlineStr">
+      <c r="DQ5" t="inlineStr">
         <is>
           <t>1391651459.0</t>
         </is>
       </c>
-      <c r="DQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="DS5" t="inlineStr">
+      <c r="DT5" t="inlineStr">
         <is>
           <t>2026/09/07</t>
         </is>
       </c>
-      <c r="DT5" t="inlineStr">
+      <c r="DU5" t="inlineStr">
         <is>
           <t>-2.31</t>
         </is>
       </c>
-      <c r="DU5" t="inlineStr">
+      <c r="DV5" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DV5" t="inlineStr">
+      <c r="DW5" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DW5" t="inlineStr">
+      <c r="DX5" t="inlineStr">
         <is>
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="DX5" t="inlineStr">
+      <c r="DY5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY5" t="inlineStr">
+      <c r="DZ5" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="DZ5" t="inlineStr">
+      <c r="EA5" t="inlineStr">
         <is>
           <t>-5.034791190033646</t>
         </is>
       </c>
-      <c r="EA5" t="inlineStr">
+      <c r="EB5" t="inlineStr">
         <is>
           <t>6.457567924179223</t>
         </is>
       </c>
-      <c r="EB5" t="inlineStr">
+      <c r="EC5" t="inlineStr">
         <is>
           <t>6.363949904140926</t>
         </is>
       </c>
-      <c r="EC5" t="inlineStr">
+      <c r="ED5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED5" t="inlineStr">
+      <c r="EE5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE5" t="inlineStr">
+      <c r="EF5" t="inlineStr">
         <is>
           <t>3.34</t>
         </is>
       </c>
-      <c r="EF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
           <t>4.15</t>
         </is>
       </c>
-      <c r="EH5" t="inlineStr">
+      <c r="EI5" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="EI5" t="inlineStr">
+      <c r="EJ5" t="inlineStr">
         <is>
           <t>23.33%</t>
         </is>
       </c>
-      <c r="EJ5" t="inlineStr">
+      <c r="EK5" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="EK5" t="inlineStr">
+      <c r="EL5" t="inlineStr">
         <is>
           <t>73.07</t>
         </is>
       </c>
-      <c r="EL5" t="inlineStr">
+      <c r="EM5" t="inlineStr">
         <is>
           <t>185825</t>
         </is>
       </c>
-      <c r="EM5" t="inlineStr">
+      <c r="EN5" t="inlineStr">
         <is>
           <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
         </is>
       </c>
-      <c r="EN5" t="inlineStr">
+      <c r="EO5" t="inlineStr">
         <is>
           <t>台玻-玻璃陶瓷-上市</t>
         </is>
       </c>
-      <c r="EO5" t="inlineStr">
+      <c r="EP5" t="inlineStr">
         <is>
           <t>玻璃陶瓷平上市</t>
         </is>
       </c>
-      <c r="EP5" t="inlineStr">
+      <c r="EQ5" t="inlineStr">
         <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="EQ5" t="inlineStr">
+      <c r="ER5" t="inlineStr">
         <is>
           <t>61.4</t>
         </is>
       </c>
-      <c r="ER5" t="inlineStr">
+      <c r="ES5" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="ES5" t="inlineStr">
+      <c r="ET5" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="ET5" t="inlineStr">
+      <c r="EU5" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="EU5" t="inlineStr">
+      <c r="EV5" t="inlineStr">
         <is>
           <t>17.77</t>
         </is>
       </c>
-      <c r="EV5" t="inlineStr">
+      <c r="EW5" t="inlineStr">
         <is>
           <t>** 印刷電路板 - 玻璃纖維/玻纖布** 建材營造 - 建材原料</t>
         </is>
       </c>
-      <c r="EW5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX5" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="EY5" t="inlineStr">
+      <c r="EZ5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="EZ5" t="inlineStr">
+      <c r="FA5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="FA5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB5" t="inlineStr">
         <is>
           <t>0</t>
@@ -5165,14 +5185,14 @@
       </c>
       <c r="FC5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FE5" t="inlineStr">
         <is>
           <t>0</t>
@@ -5180,14 +5200,14 @@
       </c>
       <c r="FF5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FG5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FH5" t="inlineStr">
         <is>
           <t>0</t>
@@ -5205,84 +5225,84 @@
       </c>
       <c r="FK5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL5" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL5" t="inlineStr">
+      <c r="FM5" t="inlineStr">
         <is>
           <t>12062.0</t>
         </is>
       </c>
-      <c r="FM5" t="inlineStr">
+      <c r="FN5" t="inlineStr">
         <is>
           <t>9248.0</t>
         </is>
       </c>
-      <c r="FN5" t="inlineStr">
+      <c r="FO5" t="inlineStr">
         <is>
           <t>2813.0</t>
         </is>
       </c>
-      <c r="FO5" t="inlineStr">
+      <c r="FP5" t="inlineStr">
         <is>
           <t>23.33</t>
         </is>
       </c>
-      <c r="FP5" t="inlineStr">
+      <c r="FQ5" t="inlineStr">
         <is>
           <t>1524.0</t>
         </is>
       </c>
-      <c r="FQ5" t="inlineStr">
+      <c r="FR5" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="FR5" t="inlineStr">
+      <c r="FS5" t="inlineStr">
         <is>
           <t>-195.0</t>
         </is>
       </c>
-      <c r="FS5" t="inlineStr">
+      <c r="FT5" t="inlineStr">
         <is>
           <t>1330.0</t>
         </is>
       </c>
-      <c r="FT5" t="inlineStr">
+      <c r="FU5" t="inlineStr">
         <is>
           <t>1267.0</t>
         </is>
       </c>
-      <c r="FU5" t="inlineStr">
+      <c r="FV5" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="FV5" t="inlineStr">
+      <c r="FW5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FW5" t="inlineStr">
+      <c r="FX5" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX5" t="inlineStr">
+      <c r="FY5" t="inlineStr">
         <is>
           <t>0.004999999999999991</t>
         </is>
       </c>
-      <c r="FY5" t="inlineStr">
+      <c r="FZ5" t="inlineStr">
         <is>
           <t>12.88125</t>
         </is>
       </c>
-      <c r="FZ5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GA5" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -5310,49 +5330,49 @@
       </c>
       <c r="GF5" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GG5" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="GG5" t="inlineStr">
+      <c r="GH5" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="GH5" t="inlineStr">
+      <c r="GI5" t="inlineStr">
         <is>
           <t>4.099999999999998</t>
         </is>
       </c>
-      <c r="GI5" t="inlineStr">
+      <c r="GJ5" t="inlineStr">
         <is>
           <t>0.2132085283411336</t>
         </is>
       </c>
-      <c r="GJ5" t="inlineStr">
+      <c r="GK5" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="GK5" t="inlineStr">
+      <c r="GL5" t="inlineStr">
         <is>
           <t>-2.466666666666667</t>
         </is>
       </c>
-      <c r="GL5" t="inlineStr">
+      <c r="GM5" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="GM5" t="inlineStr">
+      <c r="GN5" t="inlineStr">
         <is>
           <t>1.333</t>
         </is>
       </c>
-      <c r="GN5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GO5" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -5369,6 +5389,11 @@
         </is>
       </c>
       <c r="GR5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GS5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -5767,383 +5792,383 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
           <t>2026-10-08 00:00:00</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>2.44</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr"/>
-      <c r="CG6" t="inlineStr">
+      <c r="CG6" t="inlineStr"/>
+      <c r="CH6" t="inlineStr">
         <is>
           <t>1,118</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>160355</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>76.0</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="CK6" t="n">
+      <c r="CL6" t="n">
         <v>1.12</v>
       </c>
-      <c r="CL6" t="n">
+      <c r="CM6" t="n">
         <v>0.02</v>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>4.14</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>-5.58</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>58.84</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>58.8</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>58.83</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>56.49</t>
         </is>
       </c>
-      <c r="CS6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>59.83</t>
         </is>
       </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
           <t>0.006500171057133075</t>
         </is>
       </c>
-      <c r="CV6" t="inlineStr">
+      <c r="CW6" t="inlineStr">
         <is>
           <t>0.001703577512776722</t>
         </is>
       </c>
-      <c r="CW6" t="inlineStr">
+      <c r="CX6" t="inlineStr">
         <is>
           <t>-0.001103659054249029</t>
         </is>
       </c>
-      <c r="CX6" t="inlineStr">
+      <c r="CY6" t="inlineStr">
         <is>
           <t>0.001382660025171623</t>
         </is>
       </c>
-      <c r="CY6" t="inlineStr">
+      <c r="CZ6" t="inlineStr">
         <is>
           <t>-0.0005220569042025947</t>
         </is>
       </c>
-      <c r="CZ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
           <t>-2.41</t>
         </is>
-      </c>
-      <c r="DB6" t="n">
-        <v>0.2</v>
       </c>
       <c r="DC6" t="n">
         <v>0.2</v>
       </c>
-      <c r="DD6" t="inlineStr">
+      <c r="DD6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DE6" t="inlineStr">
         <is>
           <t>4.25</t>
         </is>
       </c>
-      <c r="DE6" t="inlineStr">
+      <c r="DF6" t="inlineStr">
         <is>
           <t>-95.21</t>
         </is>
       </c>
-      <c r="DF6" t="inlineStr">
+      <c r="DG6" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
-      <c r="DG6" t="inlineStr">
+      <c r="DH6" t="inlineStr">
         <is>
           <t>7429528372.217391</t>
         </is>
       </c>
-      <c r="DH6" t="inlineStr">
+      <c r="DI6" t="inlineStr">
         <is>
           <t>716628303.0</t>
         </is>
       </c>
-      <c r="DI6" t="n">
+      <c r="DJ6" t="n">
         <v>793132356.6</v>
       </c>
-      <c r="DJ6" t="inlineStr">
+      <c r="DK6" t="inlineStr">
         <is>
           <t>1101620613.1</t>
         </is>
       </c>
-      <c r="DK6" t="inlineStr">
+      <c r="DL6" t="inlineStr">
         <is>
           <t>1512236185.5</t>
         </is>
       </c>
-      <c r="DL6" t="n">
+      <c r="DM6" t="n">
         <v>1491436510.72</v>
       </c>
-      <c r="DM6" t="inlineStr">
+      <c r="DN6" t="inlineStr">
         <is>
           <t>2550447434.6375</t>
         </is>
       </c>
-      <c r="DN6" t="inlineStr">
+      <c r="DO6" t="inlineStr">
         <is>
           <t>-115442705.4717676</t>
         </is>
       </c>
-      <c r="DO6" t="inlineStr">
+      <c r="DP6" t="inlineStr">
         <is>
           <t>-106289824.1743681</t>
         </is>
       </c>
-      <c r="DP6" t="inlineStr">
+      <c r="DQ6" t="inlineStr">
         <is>
           <t>716628303.0</t>
         </is>
       </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="DS6" t="inlineStr">
+      <c r="DT6" t="inlineStr">
         <is>
           <t>2026/09/07</t>
         </is>
       </c>
-      <c r="DT6" t="inlineStr">
+      <c r="DU6" t="inlineStr">
         <is>
           <t>-1.98</t>
         </is>
       </c>
-      <c r="DU6" t="inlineStr">
+      <c r="DV6" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DV6" t="inlineStr">
+      <c r="DW6" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DW6" t="inlineStr">
+      <c r="DX6" t="inlineStr">
         <is>
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="DX6" t="inlineStr">
+      <c r="DY6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY6" t="inlineStr">
+      <c r="DZ6" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="DZ6" t="inlineStr">
+      <c r="EA6" t="inlineStr">
         <is>
           <t>-5.034791190033646</t>
         </is>
       </c>
-      <c r="EA6" t="inlineStr">
+      <c r="EB6" t="inlineStr">
         <is>
           <t>6.457567924179223</t>
         </is>
       </c>
-      <c r="EB6" t="inlineStr">
+      <c r="EC6" t="inlineStr">
         <is>
           <t>6.363949904140926</t>
         </is>
       </c>
-      <c r="EC6" t="inlineStr">
+      <c r="ED6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED6" t="inlineStr">
+      <c r="EE6" t="inlineStr">
         <is>
           <t>價漲量-</t>
         </is>
       </c>
-      <c r="EE6" t="inlineStr">
+      <c r="EF6" t="inlineStr">
         <is>
           <t>3.35</t>
         </is>
       </c>
-      <c r="EF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
           <t>4.15</t>
         </is>
       </c>
-      <c r="EH6" t="inlineStr">
+      <c r="EI6" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="EI6" t="inlineStr">
+      <c r="EJ6" t="inlineStr">
         <is>
           <t>23.33%</t>
         </is>
       </c>
-      <c r="EJ6" t="inlineStr">
+      <c r="EK6" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="EK6" t="inlineStr">
+      <c r="EL6" t="inlineStr">
         <is>
           <t>73.07</t>
         </is>
       </c>
-      <c r="EL6" t="inlineStr">
+      <c r="EM6" t="inlineStr">
         <is>
           <t>185825</t>
         </is>
       </c>
-      <c r="EM6" t="inlineStr">
+      <c r="EN6" t="inlineStr">
         <is>
           <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
         </is>
       </c>
-      <c r="EN6" t="inlineStr">
+      <c r="EO6" t="inlineStr">
         <is>
           <t>台玻-玻璃陶瓷-上市</t>
         </is>
       </c>
-      <c r="EO6" t="inlineStr">
+      <c r="EP6" t="inlineStr">
         <is>
           <t>玻璃陶瓷平上市</t>
         </is>
       </c>
-      <c r="EP6" t="inlineStr">
+      <c r="EQ6" t="inlineStr">
         <is>
           <t>58.8</t>
         </is>
       </c>
-      <c r="EQ6" t="inlineStr">
+      <c r="ER6" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="ER6" t="inlineStr">
+      <c r="ES6" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="ES6" t="inlineStr">
+      <c r="ET6" t="inlineStr">
         <is>
           <t>59.5</t>
         </is>
       </c>
-      <c r="ET6" t="inlineStr">
+      <c r="EU6" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="EU6" t="inlineStr">
+      <c r="EV6" t="inlineStr">
         <is>
           <t>17.77</t>
         </is>
       </c>
-      <c r="EV6" t="inlineStr">
+      <c r="EW6" t="inlineStr">
         <is>
           <t>** 印刷電路板 - 玻璃纖維/玻纖布** 建材營造 - 建材原料</t>
         </is>
       </c>
-      <c r="EW6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX6" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="EY6" t="inlineStr">
+      <c r="EZ6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="EZ6" t="inlineStr">
+      <c r="FA6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FA6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB6" t="inlineStr">
         <is>
           <t>0</t>
@@ -6166,14 +6191,14 @@
       </c>
       <c r="FF6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FG6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FH6" t="inlineStr">
         <is>
           <t>0</t>
@@ -6191,84 +6216,84 @@
       </c>
       <c r="FK6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL6" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL6" t="inlineStr">
+      <c r="FM6" t="inlineStr">
         <is>
           <t>12062.0</t>
         </is>
       </c>
-      <c r="FM6" t="inlineStr">
+      <c r="FN6" t="inlineStr">
         <is>
           <t>9248.0</t>
         </is>
       </c>
-      <c r="FN6" t="inlineStr">
+      <c r="FO6" t="inlineStr">
         <is>
           <t>2813.0</t>
         </is>
       </c>
-      <c r="FO6" t="inlineStr">
+      <c r="FP6" t="inlineStr">
         <is>
           <t>23.33</t>
         </is>
       </c>
-      <c r="FP6" t="inlineStr">
+      <c r="FQ6" t="inlineStr">
         <is>
           <t>1524.0</t>
         </is>
       </c>
-      <c r="FQ6" t="inlineStr">
+      <c r="FR6" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="FR6" t="inlineStr">
+      <c r="FS6" t="inlineStr">
         <is>
           <t>-195.0</t>
         </is>
       </c>
-      <c r="FS6" t="inlineStr">
+      <c r="FT6" t="inlineStr">
         <is>
           <t>1330.0</t>
         </is>
       </c>
-      <c r="FT6" t="inlineStr">
+      <c r="FU6" t="inlineStr">
         <is>
           <t>1267.0</t>
         </is>
       </c>
-      <c r="FU6" t="inlineStr">
+      <c r="FV6" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="FV6" t="inlineStr">
+      <c r="FW6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FW6" t="inlineStr">
+      <c r="FX6" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX6" t="inlineStr">
+      <c r="FY6" t="inlineStr">
         <is>
           <t>0.004999999999999991</t>
         </is>
       </c>
-      <c r="FY6" t="inlineStr">
+      <c r="FZ6" t="inlineStr">
         <is>
           <t>12.88125</t>
         </is>
       </c>
-      <c r="FZ6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GA6" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -6296,49 +6321,49 @@
       </c>
       <c r="GF6" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GG6" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="GG6" t="inlineStr">
+      <c r="GH6" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="GH6" t="inlineStr">
+      <c r="GI6" t="inlineStr">
         <is>
           <t>4.099999999999998</t>
         </is>
       </c>
-      <c r="GI6" t="inlineStr">
+      <c r="GJ6" t="inlineStr">
         <is>
           <t>0.2132085283411336</t>
         </is>
       </c>
-      <c r="GJ6" t="inlineStr">
+      <c r="GK6" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="GK6" t="inlineStr">
+      <c r="GL6" t="inlineStr">
         <is>
           <t>-2.466666666666667</t>
         </is>
       </c>
-      <c r="GL6" t="inlineStr">
+      <c r="GM6" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="GM6" t="inlineStr">
+      <c r="GN6" t="inlineStr">
         <is>
           <t>1.333</t>
         </is>
       </c>
-      <c r="GN6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GO6" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -6355,6 +6380,11 @@
         </is>
       </c>
       <c r="GR6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GS6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -6753,383 +6783,383 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
           <t>2026-10-08 00:00:00</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>3.14</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>-1.18</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr"/>
-      <c r="CG7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr"/>
+      <c r="CH7" t="inlineStr">
         <is>
           <t>1,118</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>160355</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>48.0</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>59.67</t>
         </is>
       </c>
-      <c r="CK7" t="n">
+      <c r="CL7" t="n">
         <v>0.58</v>
       </c>
-      <c r="CL7" t="n">
+      <c r="CM7" t="n">
         <v>-0.74</v>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>-5.76</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>58.46</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>58.7</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>56.41</t>
         </is>
       </c>
-      <c r="CS7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>59.86</t>
         </is>
       </c>
-      <c r="CT7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
           <t>2.220446049250313e-16</t>
         </is>
       </c>
-      <c r="CV7" t="inlineStr">
+      <c r="CW7" t="inlineStr">
         <is>
           <t>0.004792879150975704</t>
         </is>
       </c>
-      <c r="CW7" t="inlineStr">
+      <c r="CX7" t="inlineStr">
         <is>
           <t>-0.00211792612673678</t>
         </is>
       </c>
-      <c r="CX7" t="inlineStr">
+      <c r="CY7" t="inlineStr">
         <is>
           <t>0.001669063726273734</t>
         </is>
       </c>
-      <c r="CY7" t="inlineStr">
+      <c r="CZ7" t="inlineStr">
         <is>
           <t>-0.001834269575095582</t>
         </is>
       </c>
-      <c r="CZ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
           <t>-29.02</t>
         </is>
       </c>
-      <c r="DB7" t="n">
+      <c r="DC7" t="n">
         <v>0.15</v>
       </c>
-      <c r="DC7" t="n">
+      <c r="DD7" t="n">
         <v>0.2</v>
       </c>
-      <c r="DD7" t="inlineStr">
+      <c r="DE7" t="inlineStr">
         <is>
           <t>4.25</t>
         </is>
       </c>
-      <c r="DE7" t="inlineStr">
+      <c r="DF7" t="inlineStr">
         <is>
           <t>-95.18</t>
         </is>
       </c>
-      <c r="DF7" t="inlineStr">
+      <c r="DG7" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
-      <c r="DG7" t="inlineStr">
+      <c r="DH7" t="inlineStr">
         <is>
           <t>7429528372.217391</t>
         </is>
       </c>
-      <c r="DH7" t="inlineStr">
+      <c r="DI7" t="inlineStr">
         <is>
           <t>913096038.0</t>
         </is>
       </c>
-      <c r="DI7" t="n">
+      <c r="DJ7" t="n">
         <v>836051353.4</v>
       </c>
-      <c r="DJ7" t="inlineStr">
+      <c r="DK7" t="inlineStr">
         <is>
           <t>1099016073.5</t>
         </is>
       </c>
-      <c r="DK7" t="inlineStr">
+      <c r="DL7" t="inlineStr">
         <is>
           <t>1537638652.2</t>
         </is>
       </c>
-      <c r="DL7" t="n">
+      <c r="DM7" t="n">
         <v>1496862031.52</v>
       </c>
-      <c r="DM7" t="inlineStr">
+      <c r="DN7" t="inlineStr">
         <is>
           <t>2578499982.6</t>
         </is>
       </c>
-      <c r="DN7" t="inlineStr">
+      <c r="DO7" t="inlineStr">
         <is>
           <t>-117106865.7076584</t>
         </is>
       </c>
-      <c r="DO7" t="inlineStr">
+      <c r="DP7" t="inlineStr">
         <is>
           <t>-95966927.62467611</t>
         </is>
       </c>
-      <c r="DP7" t="inlineStr">
+      <c r="DQ7" t="inlineStr">
         <is>
           <t>913096038.0</t>
         </is>
       </c>
-      <c r="DQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="DS7" t="inlineStr">
+      <c r="DT7" t="inlineStr">
         <is>
           <t>2026/09/07</t>
         </is>
       </c>
-      <c r="DT7" t="inlineStr">
+      <c r="DU7" t="inlineStr">
         <is>
           <t>-3.13</t>
         </is>
       </c>
-      <c r="DU7" t="inlineStr">
+      <c r="DV7" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DV7" t="inlineStr">
+      <c r="DW7" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DW7" t="inlineStr">
+      <c r="DX7" t="inlineStr">
         <is>
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="DX7" t="inlineStr">
+      <c r="DY7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY7" t="inlineStr">
+      <c r="DZ7" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="DZ7" t="inlineStr">
+      <c r="EA7" t="inlineStr">
         <is>
           <t>-5.034791190033646</t>
         </is>
       </c>
-      <c r="EA7" t="inlineStr">
+      <c r="EB7" t="inlineStr">
         <is>
           <t>6.457567924179223</t>
         </is>
       </c>
-      <c r="EB7" t="inlineStr">
+      <c r="EC7" t="inlineStr">
         <is>
           <t>6.363949904140926</t>
         </is>
       </c>
-      <c r="EC7" t="inlineStr">
+      <c r="ED7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED7" t="inlineStr">
+      <c r="EE7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE7" t="inlineStr">
+      <c r="EF7" t="inlineStr">
         <is>
           <t>3.31</t>
         </is>
       </c>
-      <c r="EF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
           <t>4.15</t>
         </is>
       </c>
-      <c r="EH7" t="inlineStr">
+      <c r="EI7" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="EI7" t="inlineStr">
+      <c r="EJ7" t="inlineStr">
         <is>
           <t>23.33%</t>
         </is>
       </c>
-      <c r="EJ7" t="inlineStr">
+      <c r="EK7" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="EK7" t="inlineStr">
+      <c r="EL7" t="inlineStr">
         <is>
           <t>73.07</t>
         </is>
       </c>
-      <c r="EL7" t="inlineStr">
+      <c r="EM7" t="inlineStr">
         <is>
           <t>185825</t>
         </is>
       </c>
-      <c r="EM7" t="inlineStr">
+      <c r="EN7" t="inlineStr">
         <is>
           <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
         </is>
       </c>
-      <c r="EN7" t="inlineStr">
+      <c r="EO7" t="inlineStr">
         <is>
           <t>台玻-玻璃陶瓷-上市</t>
         </is>
       </c>
-      <c r="EO7" t="inlineStr">
+      <c r="EP7" t="inlineStr">
         <is>
           <t>玻璃陶瓷平上市</t>
         </is>
       </c>
-      <c r="EP7" t="inlineStr">
+      <c r="EQ7" t="inlineStr">
         <is>
           <t>60.0</t>
         </is>
       </c>
-      <c r="EQ7" t="inlineStr">
+      <c r="ER7" t="inlineStr">
         <is>
           <t>60.0</t>
         </is>
       </c>
-      <c r="ER7" t="inlineStr">
+      <c r="ES7" t="inlineStr">
         <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="ES7" t="inlineStr">
+      <c r="ET7" t="inlineStr">
         <is>
           <t>58.8</t>
         </is>
       </c>
-      <c r="ET7" t="inlineStr">
+      <c r="EU7" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="EU7" t="inlineStr">
+      <c r="EV7" t="inlineStr">
         <is>
           <t>17.77</t>
         </is>
       </c>
-      <c r="EV7" t="inlineStr">
+      <c r="EW7" t="inlineStr">
         <is>
           <t>** 印刷電路板 - 玻璃纖維/玻纖布** 建材營造 - 建材原料</t>
         </is>
       </c>
-      <c r="EW7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX7" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY7" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="EY7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA7" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FA7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB7" t="inlineStr">
         <is>
           <t>0</t>
@@ -7152,14 +7182,14 @@
       </c>
       <c r="FF7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FG7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FG7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FH7" t="inlineStr">
         <is>
           <t>0</t>
@@ -7177,84 +7207,84 @@
       </c>
       <c r="FK7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL7" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL7" t="inlineStr">
+      <c r="FM7" t="inlineStr">
         <is>
           <t>12062.0</t>
         </is>
       </c>
-      <c r="FM7" t="inlineStr">
+      <c r="FN7" t="inlineStr">
         <is>
           <t>9248.0</t>
         </is>
       </c>
-      <c r="FN7" t="inlineStr">
+      <c r="FO7" t="inlineStr">
         <is>
           <t>2813.0</t>
         </is>
       </c>
-      <c r="FO7" t="inlineStr">
+      <c r="FP7" t="inlineStr">
         <is>
           <t>23.33</t>
         </is>
       </c>
-      <c r="FP7" t="inlineStr">
+      <c r="FQ7" t="inlineStr">
         <is>
           <t>1524.0</t>
         </is>
       </c>
-      <c r="FQ7" t="inlineStr">
+      <c r="FR7" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="FR7" t="inlineStr">
+      <c r="FS7" t="inlineStr">
         <is>
           <t>-195.0</t>
         </is>
       </c>
-      <c r="FS7" t="inlineStr">
+      <c r="FT7" t="inlineStr">
         <is>
           <t>1330.0</t>
         </is>
       </c>
-      <c r="FT7" t="inlineStr">
+      <c r="FU7" t="inlineStr">
         <is>
           <t>1267.0</t>
         </is>
       </c>
-      <c r="FU7" t="inlineStr">
+      <c r="FV7" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="FV7" t="inlineStr">
+      <c r="FW7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FW7" t="inlineStr">
+      <c r="FX7" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX7" t="inlineStr">
+      <c r="FY7" t="inlineStr">
         <is>
           <t>0.004999999999999991</t>
         </is>
       </c>
-      <c r="FY7" t="inlineStr">
+      <c r="FZ7" t="inlineStr">
         <is>
           <t>12.88125</t>
         </is>
       </c>
-      <c r="FZ7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GA7" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -7282,49 +7312,49 @@
       </c>
       <c r="GF7" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GG7" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="GG7" t="inlineStr">
+      <c r="GH7" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="GH7" t="inlineStr">
+      <c r="GI7" t="inlineStr">
         <is>
           <t>4.099999999999998</t>
         </is>
       </c>
-      <c r="GI7" t="inlineStr">
+      <c r="GJ7" t="inlineStr">
         <is>
           <t>0.2132085283411336</t>
         </is>
       </c>
-      <c r="GJ7" t="inlineStr">
+      <c r="GK7" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="GK7" t="inlineStr">
+      <c r="GL7" t="inlineStr">
         <is>
           <t>-2.466666666666667</t>
         </is>
       </c>
-      <c r="GL7" t="inlineStr">
+      <c r="GM7" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="GM7" t="inlineStr">
+      <c r="GN7" t="inlineStr">
         <is>
           <t>1.333</t>
         </is>
       </c>
-      <c r="GN7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GO7" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -7341,6 +7371,11 @@
         </is>
       </c>
       <c r="GR7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GS7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -7739,383 +7774,383 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
           <t>2026-10-08 00:00:00</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>4.82</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>2.95</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr"/>
-      <c r="CG8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr">
         <is>
           <t>1,118</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>160355</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>92.0</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>63.19</t>
         </is>
       </c>
-      <c r="CK8" t="n">
+      <c r="CL8" t="n">
         <v>2.46</v>
       </c>
-      <c r="CL8" t="n">
+      <c r="CM8" t="n">
         <v>-0.95</v>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>-6.09</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>58.45999999999999</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>59.02</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>56.32</t>
         </is>
       </c>
-      <c r="CS8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>59.97</t>
         </is>
       </c>
-      <c r="CT8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
           <t>-0.0006837606837607479</t>
         </is>
       </c>
-      <c r="CV8" t="inlineStr">
+      <c r="CW8" t="inlineStr">
         <is>
           <t>0.003607627555402892</t>
         </is>
       </c>
-      <c r="CW8" t="inlineStr">
+      <c r="CX8" t="inlineStr">
         <is>
           <t>-0.0007618725133327064</t>
         </is>
       </c>
-      <c r="CX8" t="inlineStr">
+      <c r="CY8" t="inlineStr">
         <is>
           <t>0.002349297880292589</t>
         </is>
       </c>
-      <c r="CY8" t="inlineStr">
+      <c r="CZ8" t="inlineStr">
         <is>
           <t>-0.001872444892906611</t>
         </is>
       </c>
-      <c r="CZ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
           <t>-33.32</t>
         </is>
       </c>
-      <c r="DB8" t="n">
+      <c r="DC8" t="n">
         <v>0.15</v>
       </c>
-      <c r="DC8" t="n">
+      <c r="DD8" t="n">
         <v>0.22</v>
       </c>
-      <c r="DD8" t="inlineStr">
+      <c r="DE8" t="inlineStr">
         <is>
           <t>4.25</t>
         </is>
       </c>
-      <c r="DE8" t="inlineStr">
+      <c r="DF8" t="inlineStr">
         <is>
           <t>-94.83</t>
         </is>
       </c>
-      <c r="DF8" t="inlineStr">
+      <c r="DG8" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
-      <c r="DG8" t="inlineStr">
+      <c r="DH8" t="inlineStr">
         <is>
           <t>7429528372.217391</t>
         </is>
       </c>
-      <c r="DH8" t="inlineStr">
+      <c r="DI8" t="inlineStr">
         <is>
           <t>1411506215.0</t>
         </is>
       </c>
-      <c r="DI8" t="n">
+      <c r="DJ8" t="n">
         <v>972212204</v>
       </c>
-      <c r="DJ8" t="inlineStr">
+      <c r="DK8" t="inlineStr">
         <is>
           <t>1064434710.2</t>
         </is>
       </c>
-      <c r="DK8" t="inlineStr">
+      <c r="DL8" t="inlineStr">
         <is>
           <t>1565951673.033333</t>
         </is>
       </c>
-      <c r="DL8" t="n">
+      <c r="DM8" t="n">
         <v>1495033587.44</v>
       </c>
-      <c r="DM8" t="inlineStr">
+      <c r="DN8" t="inlineStr">
         <is>
           <t>2612782440.9375</t>
         </is>
       </c>
-      <c r="DN8" t="inlineStr">
+      <c r="DO8" t="inlineStr">
         <is>
           <t>-120950490.8136552</t>
         </is>
       </c>
-      <c r="DO8" t="inlineStr">
+      <c r="DP8" t="inlineStr">
         <is>
           <t>-98842656.74566317</t>
         </is>
       </c>
-      <c r="DP8" t="inlineStr">
+      <c r="DQ8" t="inlineStr">
         <is>
           <t>1411506215.0</t>
         </is>
       </c>
-      <c r="DQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="DS8" t="inlineStr">
+      <c r="DT8" t="inlineStr">
         <is>
           <t>2026/09/07</t>
         </is>
       </c>
-      <c r="DT8" t="inlineStr">
+      <c r="DU8" t="inlineStr">
         <is>
           <t>-1.32</t>
         </is>
       </c>
-      <c r="DU8" t="inlineStr">
+      <c r="DV8" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DV8" t="inlineStr">
+      <c r="DW8" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DW8" t="inlineStr">
+      <c r="DX8" t="inlineStr">
         <is>
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="DX8" t="inlineStr">
+      <c r="DY8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY8" t="inlineStr">
+      <c r="DZ8" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="DZ8" t="inlineStr">
+      <c r="EA8" t="inlineStr">
         <is>
           <t>-5.034791190033646</t>
         </is>
       </c>
-      <c r="EA8" t="inlineStr">
+      <c r="EB8" t="inlineStr">
         <is>
           <t>6.457567924179223</t>
         </is>
       </c>
-      <c r="EB8" t="inlineStr">
+      <c r="EC8" t="inlineStr">
         <is>
           <t>6.363949904140926</t>
         </is>
       </c>
-      <c r="EC8" t="inlineStr">
+      <c r="ED8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED8" t="inlineStr">
+      <c r="EE8" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="EE8" t="inlineStr">
+      <c r="EF8" t="inlineStr">
         <is>
           <t>3.37</t>
         </is>
       </c>
-      <c r="EF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EH8" t="inlineStr">
+        <is>
           <t>4.15</t>
         </is>
       </c>
-      <c r="EH8" t="inlineStr">
+      <c r="EI8" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="EI8" t="inlineStr">
+      <c r="EJ8" t="inlineStr">
         <is>
           <t>23.33%</t>
         </is>
       </c>
-      <c r="EJ8" t="inlineStr">
+      <c r="EK8" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="EK8" t="inlineStr">
+      <c r="EL8" t="inlineStr">
         <is>
           <t>73.07</t>
         </is>
       </c>
-      <c r="EL8" t="inlineStr">
+      <c r="EM8" t="inlineStr">
         <is>
           <t>185825</t>
         </is>
       </c>
-      <c r="EM8" t="inlineStr">
+      <c r="EN8" t="inlineStr">
         <is>
           <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
         </is>
       </c>
-      <c r="EN8" t="inlineStr">
+      <c r="EO8" t="inlineStr">
         <is>
           <t>台玻-玻璃陶瓷-上市</t>
         </is>
       </c>
-      <c r="EO8" t="inlineStr">
+      <c r="EP8" t="inlineStr">
         <is>
           <t>玻璃陶瓷平上市</t>
         </is>
       </c>
-      <c r="EP8" t="inlineStr">
+      <c r="EQ8" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="EQ8" t="inlineStr">
+      <c r="ER8" t="inlineStr">
         <is>
           <t>60.2</t>
         </is>
       </c>
-      <c r="ER8" t="inlineStr">
+      <c r="ES8" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="ES8" t="inlineStr">
+      <c r="ET8" t="inlineStr">
         <is>
           <t>59.9</t>
         </is>
       </c>
-      <c r="ET8" t="inlineStr">
+      <c r="EU8" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="EU8" t="inlineStr">
+      <c r="EV8" t="inlineStr">
         <is>
           <t>17.77</t>
         </is>
       </c>
-      <c r="EV8" t="inlineStr">
+      <c r="EW8" t="inlineStr">
         <is>
           <t>** 印刷電路板 - 玻璃纖維/玻纖布** 建材營造 - 建材原料</t>
         </is>
       </c>
-      <c r="EW8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX8" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EY8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA8" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FA8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB8" t="inlineStr">
         <is>
           <t>0</t>
@@ -8128,24 +8163,24 @@
       </c>
       <c r="FD8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FF8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FG8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FH8" t="inlineStr">
         <is>
           <t>0</t>
@@ -8163,84 +8198,84 @@
       </c>
       <c r="FK8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL8" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL8" t="inlineStr">
+      <c r="FM8" t="inlineStr">
         <is>
           <t>12062.0</t>
         </is>
       </c>
-      <c r="FM8" t="inlineStr">
+      <c r="FN8" t="inlineStr">
         <is>
           <t>9248.0</t>
         </is>
       </c>
-      <c r="FN8" t="inlineStr">
+      <c r="FO8" t="inlineStr">
         <is>
           <t>2813.0</t>
         </is>
       </c>
-      <c r="FO8" t="inlineStr">
+      <c r="FP8" t="inlineStr">
         <is>
           <t>23.33</t>
         </is>
       </c>
-      <c r="FP8" t="inlineStr">
+      <c r="FQ8" t="inlineStr">
         <is>
           <t>1524.0</t>
         </is>
       </c>
-      <c r="FQ8" t="inlineStr">
+      <c r="FR8" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="FR8" t="inlineStr">
+      <c r="FS8" t="inlineStr">
         <is>
           <t>-195.0</t>
         </is>
       </c>
-      <c r="FS8" t="inlineStr">
+      <c r="FT8" t="inlineStr">
         <is>
           <t>1330.0</t>
         </is>
       </c>
-      <c r="FT8" t="inlineStr">
+      <c r="FU8" t="inlineStr">
         <is>
           <t>1267.0</t>
         </is>
       </c>
-      <c r="FU8" t="inlineStr">
+      <c r="FV8" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="FV8" t="inlineStr">
+      <c r="FW8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FW8" t="inlineStr">
+      <c r="FX8" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX8" t="inlineStr">
+      <c r="FY8" t="inlineStr">
         <is>
           <t>0.004999999999999991</t>
         </is>
       </c>
-      <c r="FY8" t="inlineStr">
+      <c r="FZ8" t="inlineStr">
         <is>
           <t>12.88125</t>
         </is>
       </c>
-      <c r="FZ8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GA8" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -8268,49 +8303,49 @@
       </c>
       <c r="GF8" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GG8" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="GG8" t="inlineStr">
+      <c r="GH8" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="GH8" t="inlineStr">
+      <c r="GI8" t="inlineStr">
         <is>
           <t>4.099999999999998</t>
         </is>
       </c>
-      <c r="GI8" t="inlineStr">
+      <c r="GJ8" t="inlineStr">
         <is>
           <t>0.2132085283411336</t>
         </is>
       </c>
-      <c r="GJ8" t="inlineStr">
+      <c r="GK8" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="GK8" t="inlineStr">
+      <c r="GL8" t="inlineStr">
         <is>
           <t>-2.466666666666667</t>
         </is>
       </c>
-      <c r="GL8" t="inlineStr">
+      <c r="GM8" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="GM8" t="inlineStr">
+      <c r="GN8" t="inlineStr">
         <is>
           <t>1.333</t>
         </is>
       </c>
-      <c r="GN8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GO8" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -8327,6 +8362,11 @@
         </is>
       </c>
       <c r="GR8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GS8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -8725,383 +8765,383 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
           <t>2026-10-08 00:00:00</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>-0.87</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr"/>
-      <c r="CG9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr">
         <is>
           <t>1,118</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>160355</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>39.02</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>45.53</t>
         </is>
       </c>
-      <c r="CK9" t="n">
+      <c r="CL9" t="n">
         <v>-1.54</v>
       </c>
-      <c r="CL9" t="n">
+      <c r="CM9" t="n">
         <v>-0.96</v>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>5.12</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>-6.48</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>58.21</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>59.06</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>56.19</t>
         </is>
       </c>
-      <c r="CS9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>60.08</t>
         </is>
       </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
           <t>-0.004085801838610736</t>
         </is>
       </c>
-      <c r="CV9" t="inlineStr">
+      <c r="CW9" t="inlineStr">
         <is>
           <t>-0.001029689377037957</t>
         </is>
       </c>
-      <c r="CW9" t="inlineStr">
+      <c r="CX9" t="inlineStr">
         <is>
           <t>-0.002701561840439015</t>
         </is>
       </c>
-      <c r="CX9" t="inlineStr">
+      <c r="CY9" t="inlineStr">
         <is>
           <t>0.0003560809728131442</t>
         </is>
       </c>
-      <c r="CY9" t="inlineStr">
+      <c r="CZ9" t="inlineStr">
         <is>
           <t>-0.002945599751076</t>
         </is>
       </c>
-      <c r="CZ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
           <t>-85.80</t>
         </is>
       </c>
-      <c r="DB9" t="n">
+      <c r="DC9" t="n">
         <v>0.03</v>
       </c>
-      <c r="DC9" t="n">
+      <c r="DD9" t="n">
         <v>0.24</v>
       </c>
-      <c r="DD9" t="inlineStr">
+      <c r="DE9" t="inlineStr">
         <is>
           <t>4.25</t>
         </is>
       </c>
-      <c r="DE9" t="inlineStr">
+      <c r="DF9" t="inlineStr">
         <is>
           <t>-94.40</t>
         </is>
       </c>
-      <c r="DF9" t="inlineStr">
+      <c r="DG9" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
-      <c r="DG9" t="inlineStr">
+      <c r="DH9" t="inlineStr">
         <is>
           <t>7429528372.217391</t>
         </is>
       </c>
-      <c r="DH9" t="inlineStr">
+      <c r="DI9" t="inlineStr">
         <is>
           <t>460082038.0</t>
         </is>
       </c>
-      <c r="DI9" t="n">
+      <c r="DJ9" t="n">
         <v>923803762.8</v>
       </c>
-      <c r="DJ9" t="inlineStr">
+      <c r="DK9" t="inlineStr">
         <is>
           <t>990715477.8</t>
         </is>
       </c>
-      <c r="DK9" t="inlineStr">
+      <c r="DL9" t="inlineStr">
         <is>
           <t>1577592671.866667</t>
         </is>
       </c>
-      <c r="DL9" t="n">
+      <c r="DM9" t="n">
         <v>1503106536.6</v>
       </c>
-      <c r="DM9" t="inlineStr">
+      <c r="DN9" t="inlineStr">
         <is>
           <t>2650980248.8625</t>
         </is>
       </c>
-      <c r="DN9" t="inlineStr">
+      <c r="DO9" t="inlineStr">
         <is>
           <t>-124970097.0078356</t>
         </is>
       </c>
-      <c r="DO9" t="inlineStr">
+      <c r="DP9" t="inlineStr">
         <is>
           <t>-152821836.7132996</t>
         </is>
       </c>
-      <c r="DP9" t="inlineStr">
+      <c r="DQ9" t="inlineStr">
         <is>
           <t>460082038.0</t>
         </is>
       </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="DS9" t="inlineStr">
+      <c r="DT9" t="inlineStr">
         <is>
           <t>2026/09/07</t>
         </is>
       </c>
-      <c r="DT9" t="inlineStr">
+      <c r="DU9" t="inlineStr">
         <is>
           <t>-5.11</t>
         </is>
       </c>
-      <c r="DU9" t="inlineStr">
+      <c r="DV9" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DV9" t="inlineStr">
+      <c r="DW9" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DW9" t="inlineStr">
+      <c r="DX9" t="inlineStr">
         <is>
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="DX9" t="inlineStr">
+      <c r="DY9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY9" t="inlineStr">
+      <c r="DZ9" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="DZ9" t="inlineStr">
+      <c r="EA9" t="inlineStr">
         <is>
           <t>-5.034791190033646</t>
         </is>
       </c>
-      <c r="EA9" t="inlineStr">
+      <c r="EB9" t="inlineStr">
         <is>
           <t>6.457567924179223</t>
         </is>
       </c>
-      <c r="EB9" t="inlineStr">
+      <c r="EC9" t="inlineStr">
         <is>
           <t>6.363949904140926</t>
         </is>
       </c>
-      <c r="EC9" t="inlineStr">
+      <c r="ED9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED9" t="inlineStr">
+      <c r="EE9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE9" t="inlineStr">
+      <c r="EF9" t="inlineStr">
         <is>
           <t>3.24</t>
         </is>
       </c>
-      <c r="EF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
           <t>4.15</t>
         </is>
       </c>
-      <c r="EH9" t="inlineStr">
+      <c r="EI9" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="EI9" t="inlineStr">
+      <c r="EJ9" t="inlineStr">
         <is>
           <t>23.33%</t>
         </is>
       </c>
-      <c r="EJ9" t="inlineStr">
+      <c r="EK9" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="EK9" t="inlineStr">
+      <c r="EL9" t="inlineStr">
         <is>
           <t>73.07</t>
         </is>
       </c>
-      <c r="EL9" t="inlineStr">
+      <c r="EM9" t="inlineStr">
         <is>
           <t>185825</t>
         </is>
       </c>
-      <c r="EM9" t="inlineStr">
+      <c r="EN9" t="inlineStr">
         <is>
           <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
         </is>
       </c>
-      <c r="EN9" t="inlineStr">
+      <c r="EO9" t="inlineStr">
         <is>
           <t>台玻-玻璃陶瓷-上市</t>
         </is>
       </c>
-      <c r="EO9" t="inlineStr">
+      <c r="EP9" t="inlineStr">
         <is>
           <t>玻璃陶瓷平上市</t>
         </is>
       </c>
-      <c r="EP9" t="inlineStr">
+      <c r="EQ9" t="inlineStr">
         <is>
           <t>58.0</t>
         </is>
       </c>
-      <c r="EQ9" t="inlineStr">
+      <c r="ER9" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="ER9" t="inlineStr">
+      <c r="ES9" t="inlineStr">
         <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="ES9" t="inlineStr">
+      <c r="ET9" t="inlineStr">
         <is>
           <t>57.6</t>
         </is>
       </c>
-      <c r="ET9" t="inlineStr">
+      <c r="EU9" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="EU9" t="inlineStr">
+      <c r="EV9" t="inlineStr">
         <is>
           <t>17.77</t>
         </is>
       </c>
-      <c r="EV9" t="inlineStr">
+      <c r="EW9" t="inlineStr">
         <is>
           <t>** 印刷電路板 - 玻璃纖維/玻纖布** 建材營造 - 建材原料</t>
         </is>
       </c>
-      <c r="EW9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX9" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY9" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="EY9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA9" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FA9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB9" t="inlineStr">
         <is>
           <t>0</t>
@@ -9114,24 +9154,24 @@
       </c>
       <c r="FD9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FF9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FG9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FH9" t="inlineStr">
         <is>
           <t>0</t>
@@ -9149,84 +9189,84 @@
       </c>
       <c r="FK9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL9" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL9" t="inlineStr">
+      <c r="FM9" t="inlineStr">
         <is>
           <t>12062.0</t>
         </is>
       </c>
-      <c r="FM9" t="inlineStr">
+      <c r="FN9" t="inlineStr">
         <is>
           <t>9248.0</t>
         </is>
       </c>
-      <c r="FN9" t="inlineStr">
+      <c r="FO9" t="inlineStr">
         <is>
           <t>2813.0</t>
         </is>
       </c>
-      <c r="FO9" t="inlineStr">
+      <c r="FP9" t="inlineStr">
         <is>
           <t>23.33</t>
         </is>
       </c>
-      <c r="FP9" t="inlineStr">
+      <c r="FQ9" t="inlineStr">
         <is>
           <t>1524.0</t>
         </is>
       </c>
-      <c r="FQ9" t="inlineStr">
+      <c r="FR9" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="FR9" t="inlineStr">
+      <c r="FS9" t="inlineStr">
         <is>
           <t>-195.0</t>
         </is>
       </c>
-      <c r="FS9" t="inlineStr">
+      <c r="FT9" t="inlineStr">
         <is>
           <t>1330.0</t>
         </is>
       </c>
-      <c r="FT9" t="inlineStr">
+      <c r="FU9" t="inlineStr">
         <is>
           <t>1267.0</t>
         </is>
       </c>
-      <c r="FU9" t="inlineStr">
+      <c r="FV9" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="FV9" t="inlineStr">
+      <c r="FW9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FW9" t="inlineStr">
+      <c r="FX9" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX9" t="inlineStr">
+      <c r="FY9" t="inlineStr">
         <is>
           <t>0.004999999999999991</t>
         </is>
       </c>
-      <c r="FY9" t="inlineStr">
+      <c r="FZ9" t="inlineStr">
         <is>
           <t>12.88125</t>
         </is>
       </c>
-      <c r="FZ9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GA9" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -9254,49 +9294,49 @@
       </c>
       <c r="GF9" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GG9" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="GG9" t="inlineStr">
+      <c r="GH9" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="GH9" t="inlineStr">
+      <c r="GI9" t="inlineStr">
         <is>
           <t>4.099999999999998</t>
         </is>
       </c>
-      <c r="GI9" t="inlineStr">
+      <c r="GJ9" t="inlineStr">
         <is>
           <t>0.2132085283411336</t>
         </is>
       </c>
-      <c r="GJ9" t="inlineStr">
+      <c r="GK9" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="GK9" t="inlineStr">
+      <c r="GL9" t="inlineStr">
         <is>
           <t>-2.466666666666667</t>
         </is>
       </c>
-      <c r="GL9" t="inlineStr">
+      <c r="GM9" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="GM9" t="inlineStr">
+      <c r="GN9" t="inlineStr">
         <is>
           <t>1.333</t>
         </is>
       </c>
-      <c r="GN9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GO9" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -9313,6 +9353,11 @@
         </is>
       </c>
       <c r="GR9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GS9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -9711,383 +9756,383 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
           <t>2026-10-08 00:00:00</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>1.63</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>3.18</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr"/>
-      <c r="CG10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr"/>
+      <c r="CH10" t="inlineStr">
         <is>
           <t>1,118</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>160355</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>58.54</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>55.28</t>
         </is>
       </c>
-      <c r="CK10" t="n">
+      <c r="CL10" t="n">
         <v>-0.58</v>
       </c>
-      <c r="CL10" t="n">
+      <c r="CM10" t="n">
         <v>-0.82</v>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>5.44</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>-6.79</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>58.73999999999999</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>58.27</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>59.22</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>56.17</t>
         </is>
       </c>
-      <c r="CS10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>60.26</t>
         </is>
       </c>
-      <c r="CT10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
           <t>-0.0003403675970049536</t>
         </is>
       </c>
-      <c r="CV10" t="inlineStr">
+      <c r="CW10" t="inlineStr">
         <is>
           <t>-0.00205514642918303</t>
         </is>
       </c>
-      <c r="CW10" t="inlineStr">
+      <c r="CX10" t="inlineStr">
         <is>
           <t>-0.0006749346157091107</t>
         </is>
       </c>
-      <c r="CX10" t="inlineStr">
+      <c r="CY10" t="inlineStr">
         <is>
           <t>-0.001173688047943156</t>
         </is>
       </c>
-      <c r="CY10" t="inlineStr">
+      <c r="CZ10" t="inlineStr">
         <is>
           <t>-0.00260688756245675</t>
         </is>
       </c>
-      <c r="CZ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
           <t>-57.25</t>
         </is>
       </c>
-      <c r="DB10" t="n">
+      <c r="DC10" t="n">
         <v>0.12</v>
       </c>
-      <c r="DC10" t="n">
+      <c r="DD10" t="n">
         <v>0.29</v>
       </c>
-      <c r="DD10" t="inlineStr">
+      <c r="DE10" t="inlineStr">
         <is>
           <t>4.25</t>
         </is>
       </c>
-      <c r="DE10" t="inlineStr">
+      <c r="DF10" t="inlineStr">
         <is>
           <t>-93.19</t>
         </is>
       </c>
-      <c r="DF10" t="inlineStr">
+      <c r="DG10" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
-      <c r="DG10" t="inlineStr">
+      <c r="DH10" t="inlineStr">
         <is>
           <t>7429528372.217391</t>
         </is>
       </c>
-      <c r="DH10" t="inlineStr">
+      <c r="DI10" t="inlineStr">
         <is>
           <t>464349189.0</t>
         </is>
       </c>
-      <c r="DI10" t="n">
+      <c r="DJ10" t="n">
         <v>1223840761.4</v>
       </c>
-      <c r="DJ10" t="inlineStr">
+      <c r="DK10" t="inlineStr">
         <is>
           <t>1013338249.0</t>
         </is>
       </c>
-      <c r="DK10" t="inlineStr">
+      <c r="DL10" t="inlineStr">
         <is>
           <t>1611987982.833333</t>
         </is>
       </c>
-      <c r="DL10" t="n">
+      <c r="DM10" t="n">
         <v>1533541700.16</v>
       </c>
-      <c r="DM10" t="inlineStr">
+      <c r="DN10" t="inlineStr">
         <is>
           <t>2698659312.1</t>
         </is>
       </c>
-      <c r="DN10" t="inlineStr">
+      <c r="DO10" t="inlineStr">
         <is>
           <t>-119906144.3341149</t>
         </is>
       </c>
-      <c r="DO10" t="inlineStr">
+      <c r="DP10" t="inlineStr">
         <is>
           <t>-122538723.5344481</t>
         </is>
       </c>
-      <c r="DP10" t="inlineStr">
+      <c r="DQ10" t="inlineStr">
         <is>
           <t>464349189.0</t>
         </is>
       </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="DS10" t="inlineStr">
+      <c r="DT10" t="inlineStr">
         <is>
           <t>2026/09/07</t>
         </is>
       </c>
-      <c r="DT10" t="inlineStr">
+      <c r="DU10" t="inlineStr">
         <is>
           <t>-3.79</t>
         </is>
       </c>
-      <c r="DU10" t="inlineStr">
+      <c r="DV10" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DV10" t="inlineStr">
+      <c r="DW10" t="inlineStr">
         <is>
           <t>台玻</t>
         </is>
       </c>
-      <c r="DW10" t="inlineStr">
+      <c r="DX10" t="inlineStr">
         <is>
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="DX10" t="inlineStr">
+      <c r="DY10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY10" t="inlineStr">
+      <c r="DZ10" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="DZ10" t="inlineStr">
+      <c r="EA10" t="inlineStr">
         <is>
           <t>-5.034791190033646</t>
         </is>
       </c>
-      <c r="EA10" t="inlineStr">
+      <c r="EB10" t="inlineStr">
         <is>
           <t>6.457567924179223</t>
         </is>
       </c>
-      <c r="EB10" t="inlineStr">
+      <c r="EC10" t="inlineStr">
         <is>
           <t>6.363949904140926</t>
         </is>
       </c>
-      <c r="EC10" t="inlineStr">
+      <c r="ED10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED10" t="inlineStr">
+      <c r="EE10" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE10" t="inlineStr">
+      <c r="EF10" t="inlineStr">
         <is>
           <t>3.29</t>
         </is>
       </c>
-      <c r="EF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EG10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
           <t>4.15</t>
         </is>
       </c>
-      <c r="EH10" t="inlineStr">
+      <c r="EI10" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="EI10" t="inlineStr">
+      <c r="EJ10" t="inlineStr">
         <is>
           <t>23.33%</t>
         </is>
       </c>
-      <c r="EJ10" t="inlineStr">
+      <c r="EK10" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="EK10" t="inlineStr">
+      <c r="EL10" t="inlineStr">
         <is>
           <t>73.07</t>
         </is>
       </c>
-      <c r="EL10" t="inlineStr">
+      <c r="EM10" t="inlineStr">
         <is>
           <t>185825</t>
         </is>
       </c>
-      <c r="EM10" t="inlineStr">
+      <c r="EN10" t="inlineStr">
         <is>
           <t>平板玻璃59.63%、玻璃纖維31.31%、玻璃器皿9.06% (2025年)</t>
         </is>
       </c>
-      <c r="EN10" t="inlineStr">
+      <c r="EO10" t="inlineStr">
         <is>
           <t>台玻-玻璃陶瓷-上市</t>
         </is>
       </c>
-      <c r="EO10" t="inlineStr">
+      <c r="EP10" t="inlineStr">
         <is>
           <t>玻璃陶瓷平上市</t>
         </is>
       </c>
-      <c r="EP10" t="inlineStr">
+      <c r="EQ10" t="inlineStr">
         <is>
           <t>57.5</t>
         </is>
       </c>
-      <c r="EQ10" t="inlineStr">
+      <c r="ER10" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="ER10" t="inlineStr">
+      <c r="ES10" t="inlineStr">
         <is>
           <t>56.6</t>
         </is>
       </c>
-      <c r="ES10" t="inlineStr">
+      <c r="ET10" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="ET10" t="inlineStr">
+      <c r="EU10" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="EU10" t="inlineStr">
+      <c r="EV10" t="inlineStr">
         <is>
           <t>17.77</t>
         </is>
       </c>
-      <c r="EV10" t="inlineStr">
+      <c r="EW10" t="inlineStr">
         <is>
           <t>** 印刷電路板 - 玻璃纖維/玻纖布** 建材營造 - 建材原料</t>
         </is>
       </c>
-      <c r="EW10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX10" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EY10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA10" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FA10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB10" t="inlineStr">
         <is>
           <t>0</t>
@@ -10100,24 +10145,24 @@
       </c>
       <c r="FD10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FF10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FG10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FG10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FH10" t="inlineStr">
         <is>
           <t>0</t>
@@ -10135,84 +10180,84 @@
       </c>
       <c r="FK10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL10" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL10" t="inlineStr">
+      <c r="FM10" t="inlineStr">
         <is>
           <t>12062.0</t>
         </is>
       </c>
-      <c r="FM10" t="inlineStr">
+      <c r="FN10" t="inlineStr">
         <is>
           <t>9248.0</t>
         </is>
       </c>
-      <c r="FN10" t="inlineStr">
+      <c r="FO10" t="inlineStr">
         <is>
           <t>2813.0</t>
         </is>
       </c>
-      <c r="FO10" t="inlineStr">
+      <c r="FP10" t="inlineStr">
         <is>
           <t>23.33</t>
         </is>
       </c>
-      <c r="FP10" t="inlineStr">
+      <c r="FQ10" t="inlineStr">
         <is>
           <t>1524.0</t>
         </is>
       </c>
-      <c r="FQ10" t="inlineStr">
+      <c r="FR10" t="inlineStr">
         <is>
           <t>12.64%</t>
         </is>
       </c>
-      <c r="FR10" t="inlineStr">
+      <c r="FS10" t="inlineStr">
         <is>
           <t>-195.0</t>
         </is>
       </c>
-      <c r="FS10" t="inlineStr">
+      <c r="FT10" t="inlineStr">
         <is>
           <t>1330.0</t>
         </is>
       </c>
-      <c r="FT10" t="inlineStr">
+      <c r="FU10" t="inlineStr">
         <is>
           <t>1267.0</t>
         </is>
       </c>
-      <c r="FU10" t="inlineStr">
+      <c r="FV10" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="FV10" t="inlineStr">
+      <c r="FW10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="FW10" t="inlineStr">
+      <c r="FX10" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX10" t="inlineStr">
+      <c r="FY10" t="inlineStr">
         <is>
           <t>0.004999999999999991</t>
         </is>
       </c>
-      <c r="FY10" t="inlineStr">
+      <c r="FZ10" t="inlineStr">
         <is>
           <t>12.88125</t>
         </is>
       </c>
-      <c r="FZ10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GA10" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -10240,49 +10285,49 @@
       </c>
       <c r="GF10" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GG10" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="GG10" t="inlineStr">
+      <c r="GH10" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="GH10" t="inlineStr">
+      <c r="GI10" t="inlineStr">
         <is>
           <t>4.099999999999998</t>
         </is>
       </c>
-      <c r="GI10" t="inlineStr">
+      <c r="GJ10" t="inlineStr">
         <is>
           <t>0.2132085283411336</t>
         </is>
       </c>
-      <c r="GJ10" t="inlineStr">
+      <c r="GK10" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="GK10" t="inlineStr">
+      <c r="GL10" t="inlineStr">
         <is>
           <t>-2.466666666666667</t>
         </is>
       </c>
-      <c r="GL10" t="inlineStr">
+      <c r="GM10" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="GM10" t="inlineStr">
+      <c r="GN10" t="inlineStr">
         <is>
           <t>1.333</t>
         </is>
       </c>
-      <c r="GN10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="GO10" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -10299,6 +10344,11 @@
         </is>
       </c>
       <c r="GR10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="GS10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
